--- a/data/reports/pe-pass2-enrichment-2026-05-11.xlsx
+++ b/data/reports/pe-pass2-enrichment-2026-05-11.xlsx
@@ -9,9 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enrichment" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specs (Draft)" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Enrichment'!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Specs (Draft)'!$A$1:$T$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,8 +130,14 @@
       <color rgb="0015803D"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="009CA3AF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -201,6 +209,16 @@
         <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001D4ED8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9FAFB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -228,7 +246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -316,6 +334,30 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -14624,4 +14666,9817 @@
   <autoFilter ref="A1:S1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T158"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>handle</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F1" s="30" t="inlineStr">
+        <is>
+          <t>draft_manufacturer</t>
+        </is>
+      </c>
+      <c r="G1" s="30" t="inlineStr">
+        <is>
+          <t>draft_product_line</t>
+        </is>
+      </c>
+      <c r="H1" s="30" t="inlineStr">
+        <is>
+          <t>draft_model_codes</t>
+        </is>
+      </c>
+      <c r="I1" s="30" t="inlineStr">
+        <is>
+          <t>draft_dimensions</t>
+        </is>
+      </c>
+      <c r="J1" s="30" t="inlineStr">
+        <is>
+          <t>draft_weight</t>
+        </is>
+      </c>
+      <c r="K1" s="30" t="inlineStr">
+        <is>
+          <t>draft_weight_capacity</t>
+        </is>
+      </c>
+      <c r="L1" s="30" t="inlineStr">
+        <is>
+          <t>draft_materials</t>
+        </is>
+      </c>
+      <c r="M1" s="30" t="inlineStr">
+        <is>
+          <t>draft_finishes_available</t>
+        </is>
+      </c>
+      <c r="N1" s="30" t="inlineStr">
+        <is>
+          <t>draft_key_features</t>
+        </is>
+      </c>
+      <c r="O1" s="30" t="inlineStr">
+        <is>
+          <t>draft_certifications</t>
+        </is>
+      </c>
+      <c r="P1" s="30" t="inlineStr">
+        <is>
+          <t>draft_warranty</t>
+        </is>
+      </c>
+      <c r="Q1" s="30" t="inlineStr">
+        <is>
+          <t>draft_country_of_manufacture</t>
+        </is>
+      </c>
+      <c r="R1" s="31" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="S1" s="18" t="inlineStr">
+        <is>
+          <t>steve_approve</t>
+        </is>
+      </c>
+      <c r="T1" s="18" t="inlineStr">
+        <is>
+          <t>steve_notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="32" t="inlineStr">
+        <is>
+          <t>adapt-high-back-synchro-tilter-mvl11724</t>
+        </is>
+      </c>
+      <c r="B2" s="32" t="inlineStr">
+        <is>
+          <t>Adapt | high back synchro-tilter — MVL11724</t>
+        </is>
+      </c>
+      <c r="C2" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E2" s="32" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F2" s="33" t="inlineStr"/>
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t>Adapt</t>
+        </is>
+      </c>
+      <c r="H2" s="23" t="inlineStr">
+        <is>
+          <t>MVL11724</t>
+        </is>
+      </c>
+      <c r="I2" s="33" t="inlineStr"/>
+      <c r="J2" s="33" t="inlineStr"/>
+      <c r="K2" s="33" t="inlineStr"/>
+      <c r="L2" s="23" t="inlineStr">
+        <is>
+          <t>mesh, nylon, glass</t>
+        </is>
+      </c>
+      <c r="M2" s="33" t="inlineStr"/>
+      <c r="N2" s="33" t="inlineStr"/>
+      <c r="O2" s="33" t="inlineStr"/>
+      <c r="P2" s="33" t="inlineStr"/>
+      <c r="Q2" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R2" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S2" s="35" t="inlineStr"/>
+      <c r="T2" s="25" t="inlineStr"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="27" t="inlineStr">
+        <is>
+          <t>amigo-mesh-chair-otg10900blk</t>
+        </is>
+      </c>
+      <c r="B3" s="27" t="inlineStr">
+        <is>
+          <t>Amigo mesh chair — OTG10900BLK</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D3" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E3" s="27" t="inlineStr">
+        <is>
+          <t>179.99</t>
+        </is>
+      </c>
+      <c r="F3" s="33" t="inlineStr"/>
+      <c r="G3" s="23" t="inlineStr">
+        <is>
+          <t>Amigo mesh chair</t>
+        </is>
+      </c>
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t>OTG10900BLK</t>
+        </is>
+      </c>
+      <c r="I3" s="33" t="inlineStr"/>
+      <c r="J3" s="33" t="inlineStr"/>
+      <c r="K3" s="33" t="inlineStr"/>
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric, plastic</t>
+        </is>
+      </c>
+      <c r="M3" s="33" t="inlineStr"/>
+      <c r="N3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enhance your workspace with the LB Air-Flow Mesh Tilter Chair in sleek black; Low-back chair design in black ; Pneumatic seat height adjustment for personalized comfort </t>
+        </is>
+      </c>
+      <c r="O3" s="33" t="inlineStr"/>
+      <c r="P3" s="33" t="inlineStr"/>
+      <c r="Q3" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R3" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S3" s="35" t="inlineStr"/>
+      <c r="T3" s="25" t="inlineStr"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>armless-low-back-stacking-chair-mvl2748</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>Armless low back stacking chair — MVL2748</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>139.99</t>
+        </is>
+      </c>
+      <c r="F4" s="33" t="inlineStr"/>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Armless low back stacking chair</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>MVL2748</t>
+        </is>
+      </c>
+      <c r="I4" s="33" t="inlineStr"/>
+      <c r="J4" s="33" t="inlineStr"/>
+      <c r="K4" s="33" t="inlineStr"/>
+      <c r="L4" s="23" t="inlineStr">
+        <is>
+          <t>steel, upholstered</t>
+        </is>
+      </c>
+      <c r="M4" s="33" t="inlineStr"/>
+      <c r="N4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MVL2748 Minto | Armless Low Back Stacking Chair Stacking chair Fully upholstered </t>
+        </is>
+      </c>
+      <c r="O4" s="33" t="inlineStr"/>
+      <c r="P4" s="33" t="inlineStr"/>
+      <c r="Q4" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R4" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S4" s="35" t="inlineStr"/>
+      <c r="T4" s="25" t="inlineStr"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>ashmont-medium-back-management-tilter-mvl2781</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Ashmont | medium back management tilter — MVL2781</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>479.99</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="inlineStr"/>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>Ashmont</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>MVL2781</t>
+        </is>
+      </c>
+      <c r="I5" s="33" t="inlineStr"/>
+      <c r="J5" s="33" t="inlineStr"/>
+      <c r="K5" s="33" t="inlineStr"/>
+      <c r="L5" s="33" t="inlineStr"/>
+      <c r="M5" s="33" t="inlineStr"/>
+      <c r="N5" s="23" t="inlineStr">
+        <is>
+          <t>MVL2781 Ashmont | Medium Back Management Tilter Medium back tilter Deep, soft cus</t>
+        </is>
+      </c>
+      <c r="O5" s="33" t="inlineStr"/>
+      <c r="P5" s="33" t="inlineStr"/>
+      <c r="Q5" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R5" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S5" s="35" t="inlineStr"/>
+      <c r="T5" s="25" t="inlineStr"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>avro-350m-heavy-duty-multi-tilter-chairs-mvl11716</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>Avro 350M heavy duty multi-tilter chairs — MVL11716</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>699.99</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr"/>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>Avro</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>MVL11716</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>26 x 27 x 38.5"</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t>42 lbs</t>
+        </is>
+      </c>
+      <c r="K6" s="33" t="inlineStr"/>
+      <c r="L6" s="33" t="inlineStr"/>
+      <c r="M6" s="33" t="inlineStr"/>
+      <c r="N6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pneumatic seat height adjustment ; Seat depth adjustment ; Independent seat and back angle adjustment </t>
+        </is>
+      </c>
+      <c r="O6" s="33" t="inlineStr"/>
+      <c r="P6" s="33" t="inlineStr"/>
+      <c r="Q6" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R6" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S6" s="35" t="inlineStr"/>
+      <c r="T6" s="25" t="inlineStr"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>basics-chevron-junior-operator-chair-mvl2363-7-1</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Basics chevron junior operator chair — MVL2363-7</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>259.99</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr"/>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Basics chevron junior operator chair</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>MVL2363-7</t>
+        </is>
+      </c>
+      <c r="I7" s="33" t="inlineStr"/>
+      <c r="J7" s="33" t="inlineStr"/>
+      <c r="K7" s="33" t="inlineStr"/>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="M7" s="33" t="inlineStr"/>
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pneumatic seat height adjustment ; Adjustable back angle ; Back height adjustment </t>
+        </is>
+      </c>
+      <c r="O7" s="33" t="inlineStr"/>
+      <c r="P7" s="33" t="inlineStr"/>
+      <c r="Q7" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R7" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S7" s="35" t="inlineStr"/>
+      <c r="T7" s="25" t="inlineStr"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>basics-comfort-time-ultra-multi-tilter-big-tall-chair</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Basics comfort-time ultra multi-tilter big &amp; tall chair</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>599.99</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="inlineStr"/>
+      <c r="G8" s="33" t="inlineStr"/>
+      <c r="H8" s="33" t="inlineStr"/>
+      <c r="I8" s="33" t="inlineStr"/>
+      <c r="J8" s="33" t="inlineStr"/>
+      <c r="K8" s="33" t="inlineStr"/>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="M8" s="33" t="inlineStr"/>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Specifically intended for users of above average height and/or weight ; Pneumatic seat height adjustment ; Seat height adjustment </t>
+        </is>
+      </c>
+      <c r="O8" s="33" t="inlineStr"/>
+      <c r="P8" s="33" t="inlineStr"/>
+      <c r="Q8" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R8" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S8" s="35" t="inlineStr"/>
+      <c r="T8" s="25" t="inlineStr"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>basics-ergo-boss-executie-back-multi-tilter-chairs-bao28703</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Basics ergo boss executie back multi-tilter chairs — BAO28703</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>749.99</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="inlineStr"/>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>BAO28703</t>
+        </is>
+      </c>
+      <c r="I9" s="33" t="inlineStr"/>
+      <c r="J9" s="33" t="inlineStr"/>
+      <c r="K9" s="33" t="inlineStr"/>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="M9" s="33" t="inlineStr"/>
+      <c r="N9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chair is made with Fusion Fabric, offering a stylish and comfortable addition to </t>
+        </is>
+      </c>
+      <c r="O9" s="33" t="inlineStr"/>
+      <c r="P9" s="33" t="inlineStr"/>
+      <c r="Q9" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R9" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S9" s="35" t="inlineStr"/>
+      <c r="T9" s="25" t="inlineStr"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>basics-obusforme-elite-heavy-duty-multi-tilter-chair-ts2770-3-1</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>ObusForme Basics elite heavy duty multi-tilter chair — TS2770-3</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>899.99</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>ObusForme</t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="inlineStr"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>TS2770-3</t>
+        </is>
+      </c>
+      <c r="I10" s="33" t="inlineStr"/>
+      <c r="J10" s="33" t="inlineStr"/>
+      <c r="K10" s="33" t="inlineStr"/>
+      <c r="L10" s="33" t="inlineStr"/>
+      <c r="M10" s="33" t="inlineStr"/>
+      <c r="N10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basics® ObusForme® Elite Heavy Duty Multi-Tilter Chairs ; Soft Descent™ pneumatic seat height adjustment ; Seat depth adjustment </t>
+        </is>
+      </c>
+      <c r="O10" s="33" t="inlineStr"/>
+      <c r="P10" s="33" t="inlineStr"/>
+      <c r="Q10" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R10" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S10" s="35" t="inlineStr"/>
+      <c r="T10" s="25" t="inlineStr"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>basics-preto-swivel-tilt-chair-1</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Basics preto swivel tilt chair</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>169.99</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr"/>
+      <c r="G11" s="33" t="inlineStr"/>
+      <c r="H11" s="33" t="inlineStr"/>
+      <c r="I11" s="33" t="inlineStr"/>
+      <c r="J11" s="33" t="inlineStr"/>
+      <c r="K11" s="33" t="inlineStr"/>
+      <c r="L11" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric</t>
+        </is>
+      </c>
+      <c r="M11" s="33" t="inlineStr"/>
+      <c r="N11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basics® Preto Swivel Tilt Chair ; Pneumatic seat height adjustment ; Fixed Lumbar Support </t>
+        </is>
+      </c>
+      <c r="O11" s="33" t="inlineStr"/>
+      <c r="P11" s="33" t="inlineStr"/>
+      <c r="Q11" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R11" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S11" s="35" t="inlineStr"/>
+      <c r="T11" s="25" t="inlineStr"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>beta-armless-posture-task-drafting-stool-mvl2718</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>Beta | armless posture task drafting stool — MVL2718</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>309.99</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr"/>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t>MVL2718</t>
+        </is>
+      </c>
+      <c r="I12" s="33" t="inlineStr"/>
+      <c r="J12" s="33" t="inlineStr"/>
+      <c r="K12" s="33" t="inlineStr"/>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t>chrome</t>
+        </is>
+      </c>
+      <c r="M12" s="33" t="inlineStr"/>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t>Posture task mechanism Infinite back angle and back height adjustment Thick, soft</t>
+        </is>
+      </c>
+      <c r="O12" s="33" t="inlineStr"/>
+      <c r="P12" s="33" t="inlineStr"/>
+      <c r="Q12" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R12" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S12" s="35" t="inlineStr"/>
+      <c r="T12" s="25" t="inlineStr"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>bolt-mesh-back-tilter-otg11510b</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Bolt | mesh back tilter — OTG11510B</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>289.99</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr"/>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>Bolt</t>
+        </is>
+      </c>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t>OTG11510B</t>
+        </is>
+      </c>
+      <c r="I13" s="33" t="inlineStr"/>
+      <c r="J13" s="33" t="inlineStr"/>
+      <c r="K13" s="33" t="inlineStr"/>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric, upholstered</t>
+        </is>
+      </c>
+      <c r="M13" s="33" t="inlineStr"/>
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t>Bolt | Mesh Back Tilter Tilter mechanism Breathable mesh back, upholstered seat U</t>
+        </is>
+      </c>
+      <c r="O13" s="33" t="inlineStr"/>
+      <c r="P13" s="33" t="inlineStr"/>
+      <c r="Q13" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R13" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S13" s="35" t="inlineStr"/>
+      <c r="T13" s="25" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>chair-black-steel-frame-3</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>Chair - black steel frame</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>357.0</t>
+        </is>
+      </c>
+      <c r="F14" s="33" t="inlineStr"/>
+      <c r="G14" s="33" t="inlineStr"/>
+      <c r="H14" s="33" t="inlineStr"/>
+      <c r="I14" s="33" t="inlineStr"/>
+      <c r="J14" s="33" t="inlineStr"/>
+      <c r="K14" s="33" t="inlineStr"/>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric, polyurethane, steel</t>
+        </is>
+      </c>
+      <c r="M14" s="33" t="inlineStr"/>
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item Code: GLBOTG11340 Multi-purpose guest/nesting chairs feature a flip up seat </t>
+        </is>
+      </c>
+      <c r="O14" s="33" t="inlineStr"/>
+      <c r="P14" s="23" t="inlineStr">
+        <is>
+          <t>Lifetime warranty</t>
+        </is>
+      </c>
+      <c r="Q14" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R14" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S14" s="35" t="inlineStr"/>
+      <c r="T14" s="25" t="inlineStr"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>cobalt-medium-back-tilter-mvl2785</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Cobalt | medium back tilter — MVL2785</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
+        <is>
+          <t>299.99</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr"/>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>Cobalt</t>
+        </is>
+      </c>
+      <c r="H15" s="23" t="inlineStr">
+        <is>
+          <t>MVL2785</t>
+        </is>
+      </c>
+      <c r="I15" s="33" t="inlineStr"/>
+      <c r="J15" s="33" t="inlineStr"/>
+      <c r="K15" s="33" t="inlineStr"/>
+      <c r="L15" s="33" t="inlineStr"/>
+      <c r="M15" s="33" t="inlineStr"/>
+      <c r="N15" s="23" t="inlineStr">
+        <is>
+          <t>MVL2785 Cobalt | Medium Back Tilter Tilter mechanism Height adjustable T-arms wit</t>
+        </is>
+      </c>
+      <c r="O15" s="33" t="inlineStr"/>
+      <c r="P15" s="33" t="inlineStr"/>
+      <c r="Q15" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R15" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S15" s="35" t="inlineStr"/>
+      <c r="T15" s="25" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>drift-seating</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>Drift seating</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>1499.0</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr"/>
+      <c r="G16" s="33" t="inlineStr"/>
+      <c r="H16" s="33" t="inlineStr"/>
+      <c r="I16" s="33" t="inlineStr"/>
+      <c r="J16" s="33" t="inlineStr"/>
+      <c r="K16" s="33" t="inlineStr"/>
+      <c r="L16" s="23" t="inlineStr">
+        <is>
+          <t>fabric, leather, wood</t>
+        </is>
+      </c>
+      <c r="M16" s="33" t="inlineStr"/>
+      <c r="N16" s="23" t="inlineStr">
+        <is>
+          <t>Drift™ Change is the constant that each new generation brings to the table</t>
+        </is>
+      </c>
+      <c r="O16" s="33" t="inlineStr"/>
+      <c r="P16" s="33" t="inlineStr"/>
+      <c r="Q16" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R16" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S16" s="35" t="inlineStr"/>
+      <c r="T16" s="25" t="inlineStr"/>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>elora-multi-tilter-high-back-chair-black-baomvl1893</t>
+        </is>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>Elora multi-tilter high back chair black — BAOMVL1893</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
+        <is>
+          <t>599.99</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr"/>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>Elora multi-tilter high back chair black</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>BAOMVL1893</t>
+        </is>
+      </c>
+      <c r="I17" s="33" t="inlineStr"/>
+      <c r="J17" s="33" t="inlineStr"/>
+      <c r="K17" s="33" t="inlineStr"/>
+      <c r="L17" s="23" t="inlineStr">
+        <is>
+          <t>mesh</t>
+        </is>
+      </c>
+      <c r="M17" s="33" t="inlineStr"/>
+      <c r="N17" s="23" t="inlineStr">
+        <is>
+          <t>Multi-tilt feature makes the chair versatile and suitable for any setting Task Ch</t>
+        </is>
+      </c>
+      <c r="O17" s="33" t="inlineStr"/>
+      <c r="P17" s="33" t="inlineStr"/>
+      <c r="Q17" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R17" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S17" s="35" t="inlineStr"/>
+      <c r="T17" s="25" t="inlineStr"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>extended-high-back-tilter-otg11359-carleton</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>Extended high back tilter OTG11359 carleton</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>319.99</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr"/>
+      <c r="G18" s="33" t="inlineStr"/>
+      <c r="H18" s="33" t="inlineStr"/>
+      <c r="I18" s="33" t="inlineStr"/>
+      <c r="J18" s="33" t="inlineStr"/>
+      <c r="K18" s="33" t="inlineStr"/>
+      <c r="L18" s="23" t="inlineStr">
+        <is>
+          <t>polyester, upholstered</t>
+        </is>
+      </c>
+      <c r="M18" s="33" t="inlineStr"/>
+      <c r="N18" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OTG11359 Carleton | Extended High Back Tilter ​​​​​​A classic looking management </t>
+        </is>
+      </c>
+      <c r="O18" s="33" t="inlineStr"/>
+      <c r="P18" s="33" t="inlineStr"/>
+      <c r="Q18" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R18" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S18" s="35" t="inlineStr"/>
+      <c r="T18" s="25" t="inlineStr"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>extended-high-back-wide-deep-seat-multi-tilt-bao27513</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Extended high back wide &amp; deep seat multi tilt — BAO27513</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>824.98</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr"/>
+      <c r="G19" s="33" t="inlineStr"/>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>BAO27513</t>
+        </is>
+      </c>
+      <c r="I19" s="33" t="inlineStr"/>
+      <c r="J19" s="33" t="inlineStr"/>
+      <c r="K19" s="33" t="inlineStr"/>
+      <c r="L19" s="23" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="M19" s="33" t="inlineStr"/>
+      <c r="N19" s="23" t="inlineStr">
+        <is>
+          <t>High Back Leather, Luxhide Task chairs feature a sleek and functional design, pro</t>
+        </is>
+      </c>
+      <c r="O19" s="33" t="inlineStr"/>
+      <c r="P19" s="33" t="inlineStr"/>
+      <c r="Q19" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R19" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S19" s="35" t="inlineStr"/>
+      <c r="T19" s="25" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>finch-armless-stacking-armchair-mvl11704</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Finch | armless stacking armchair — MVL11704</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>179.99</t>
+        </is>
+      </c>
+      <c r="F20" s="33" t="inlineStr"/>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>Finch</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>MVL11704</t>
+        </is>
+      </c>
+      <c r="I20" s="33" t="inlineStr"/>
+      <c r="J20" s="33" t="inlineStr"/>
+      <c r="K20" s="33" t="inlineStr"/>
+      <c r="L20" s="23" t="inlineStr">
+        <is>
+          <t>steel, plastic</t>
+        </is>
+      </c>
+      <c r="M20" s="33" t="inlineStr"/>
+      <c r="N20" s="23" t="inlineStr">
+        <is>
+          <t>MVL11704 Finch | Armless Stacking Armchair Oval tube steel frame available in mon</t>
+        </is>
+      </c>
+      <c r="O20" s="23" t="inlineStr">
+        <is>
+          <t>GREENGUARD</t>
+        </is>
+      </c>
+      <c r="P20" s="23" t="inlineStr">
+        <is>
+          <t>Lifetime warranty</t>
+        </is>
+      </c>
+      <c r="Q20" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R20" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S20" s="35" t="inlineStr"/>
+      <c r="T20" s="25" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>format-high-back-weight-sensing-synchro-tilter-mesh-seat-and-back-mvl3197-copy</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Format+ | high back weight sensing synchro-tilter, mesh seat and back</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>469.99</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G21" s="33" t="inlineStr"/>
+      <c r="H21" s="33" t="inlineStr"/>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>24.5 x 24 x 41.5"</t>
+        </is>
+      </c>
+      <c r="J21" s="23" t="inlineStr">
+        <is>
+          <t>52 lbs</t>
+        </is>
+      </c>
+      <c r="K21" s="33" t="inlineStr"/>
+      <c r="L21" s="23" t="inlineStr">
+        <is>
+          <t>mesh, nylon, glass</t>
+        </is>
+      </c>
+      <c r="M21" s="33" t="inlineStr"/>
+      <c r="N21" s="23" t="inlineStr">
+        <is>
+          <t>Designed for the modern workspace Format+™ is an ergonomic chair that combines ad; Black Seat Mesh - Black Specifications Dimensions: 24</t>
+        </is>
+      </c>
+      <c r="O21" s="33" t="inlineStr"/>
+      <c r="P21" s="33" t="inlineStr"/>
+      <c r="Q21" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R21" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S21" s="35" t="inlineStr"/>
+      <c r="T21" s="25" t="inlineStr"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>full-time-chair-mvl2900</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>Full time chair — MVL2900</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>389.95</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr"/>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>Full time chair</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>MVL2900</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>24.5 x 25 x 41"</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>56 lbs</t>
+        </is>
+      </c>
+      <c r="K22" s="33" t="inlineStr"/>
+      <c r="L22" s="33" t="inlineStr"/>
+      <c r="M22" s="33" t="inlineStr"/>
+      <c r="N22" s="23" t="inlineStr">
+        <is>
+          <t>MVL2900 Full-Time | Medium Back Multi-Tilter Experience maximum comfort and suppo; Time chair – designed to revolutionize your workspace and boost your productivity</t>
+        </is>
+      </c>
+      <c r="O22" s="33" t="inlineStr"/>
+      <c r="P22" s="33" t="inlineStr"/>
+      <c r="Q22" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R22" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S22" s="35" t="inlineStr"/>
+      <c r="T22" s="25" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>global-accord-back-knee-tilter-chair-1</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>Global Accord back knee tilter chair</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>769.99</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G23" s="33" t="inlineStr"/>
+      <c r="H23" s="33" t="inlineStr"/>
+      <c r="I23" s="33" t="inlineStr"/>
+      <c r="J23" s="33" t="inlineStr"/>
+      <c r="K23" s="33" t="inlineStr"/>
+      <c r="L23" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric, leather, vinyl, aluminum, upholstered</t>
+        </is>
+      </c>
+      <c r="M23" s="33" t="inlineStr"/>
+      <c r="N23" s="23" t="inlineStr">
+        <is>
+          <t>This award-winning series features classic styling with a finely detailed polishe</t>
+        </is>
+      </c>
+      <c r="O23" s="33" t="inlineStr"/>
+      <c r="P23" s="33" t="inlineStr"/>
+      <c r="Q23" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R23" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S23" s="35" t="inlineStr"/>
+      <c r="T23" s="25" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>global-accord-mesh-back-tilter</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>Global Accord mesh back tilter</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>749.99</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G24" s="33" t="inlineStr"/>
+      <c r="H24" s="33" t="inlineStr"/>
+      <c r="I24" s="33" t="inlineStr"/>
+      <c r="J24" s="33" t="inlineStr"/>
+      <c r="K24" s="33" t="inlineStr"/>
+      <c r="L24" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric, leather, vinyl, aluminum, upholstered</t>
+        </is>
+      </c>
+      <c r="M24" s="33" t="inlineStr"/>
+      <c r="N24" s="33" t="inlineStr"/>
+      <c r="O24" s="33" t="inlineStr"/>
+      <c r="P24" s="33" t="inlineStr"/>
+      <c r="Q24" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R24" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S24" s="35" t="inlineStr"/>
+      <c r="T24" s="25" t="inlineStr"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="27" t="inlineStr">
+        <is>
+          <t>global-obusforme-elite-multi-tilter-chair-high-back</t>
+        </is>
+      </c>
+      <c r="B25" s="27" t="inlineStr">
+        <is>
+          <t>ObusForme Global elite multi-tilter chair high back</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
+        <is>
+          <t>689.99</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G25" s="33" t="inlineStr"/>
+      <c r="H25" s="33" t="inlineStr"/>
+      <c r="I25" s="33" t="inlineStr"/>
+      <c r="J25" s="33" t="inlineStr"/>
+      <c r="K25" s="33" t="inlineStr"/>
+      <c r="L25" s="33" t="inlineStr"/>
+      <c r="M25" s="33" t="inlineStr"/>
+      <c r="N25" s="23" t="inlineStr">
+        <is>
+          <t>The streamlined design of the task chair enhances any environment with a modern t</t>
+        </is>
+      </c>
+      <c r="O25" s="33" t="inlineStr"/>
+      <c r="P25" s="33" t="inlineStr"/>
+      <c r="Q25" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R25" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S25" s="35" t="inlineStr"/>
+      <c r="T25" s="25" t="inlineStr"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>ibex-drafting-task-stool-mvl2808</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>Ibex drafting task stool — MVL2808</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>599.99</t>
+        </is>
+      </c>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>Ibex drafting task stool</t>
+        </is>
+      </c>
+      <c r="H26" s="23" t="inlineStr">
+        <is>
+          <t>MVL2808</t>
+        </is>
+      </c>
+      <c r="I26" s="33" t="inlineStr"/>
+      <c r="J26" s="33" t="inlineStr"/>
+      <c r="K26" s="33" t="inlineStr"/>
+      <c r="L26" s="23" t="inlineStr">
+        <is>
+          <t>fabric, leather, chrome</t>
+        </is>
+      </c>
+      <c r="M26" s="33" t="inlineStr"/>
+      <c r="N26" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pneumatic seat height adjustment ; Seat range from 23” to 33” ; Height adjustable arms with durable self-skinned urethane arm caps </t>
+        </is>
+      </c>
+      <c r="O26" s="33" t="inlineStr"/>
+      <c r="P26" s="33" t="inlineStr"/>
+      <c r="Q26" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R26" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S26" s="35" t="inlineStr"/>
+      <c r="T26" s="25" t="inlineStr"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>ibex-mesh-back-drafting-stool-task-chair-with-arms</t>
+        </is>
+      </c>
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Ibex mesh back drafting stool task chair with arms</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
+        <is>
+          <t>499.99</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G27" s="33" t="inlineStr"/>
+      <c r="H27" s="33" t="inlineStr"/>
+      <c r="I27" s="33" t="inlineStr"/>
+      <c r="J27" s="33" t="inlineStr"/>
+      <c r="K27" s="33" t="inlineStr"/>
+      <c r="L27" s="23" t="inlineStr">
+        <is>
+          <t>mesh, chrome, upholstered</t>
+        </is>
+      </c>
+      <c r="M27" s="33" t="inlineStr"/>
+      <c r="N27" s="23" t="inlineStr">
+        <is>
+          <t>MVL2808 Ibex | Upholstered Seat &amp; Mesh Back Drafting Task Chair with Arms Elevate; Black (MS69) Seat Available in all Grade 1 seating textiles (previously MVL2808F)</t>
+        </is>
+      </c>
+      <c r="O27" s="33" t="inlineStr"/>
+      <c r="P27" s="33" t="inlineStr"/>
+      <c r="Q27" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R27" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S27" s="35" t="inlineStr"/>
+      <c r="T27" s="25" t="inlineStr"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>ibex-mesh-seat-back-armless-drafting-chair-mvl2827</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>Ibex | mesh seat &amp; back armless drafting chair — MVL2827</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>529.99</t>
+        </is>
+      </c>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>Ibex</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
+        <is>
+          <t>MVL2827</t>
+        </is>
+      </c>
+      <c r="I28" s="33" t="inlineStr"/>
+      <c r="J28" s="33" t="inlineStr"/>
+      <c r="K28" s="33" t="inlineStr"/>
+      <c r="L28" s="23" t="inlineStr">
+        <is>
+          <t>mesh, chrome</t>
+        </is>
+      </c>
+      <c r="M28" s="33" t="inlineStr"/>
+      <c r="N28" s="23" t="inlineStr">
+        <is>
+          <t>Elevate your office experience with our Ibex chair, meticulously designed to prov</t>
+        </is>
+      </c>
+      <c r="O28" s="33" t="inlineStr"/>
+      <c r="P28" s="33" t="inlineStr"/>
+      <c r="Q28" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R28" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S28" s="35" t="inlineStr"/>
+      <c r="T28" s="25" t="inlineStr"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>ibex-synchro-tilter-chairs-mvl2801</t>
+        </is>
+      </c>
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Ibex synchro-tilter chairs — MVL2801</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E29" s="27" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="inlineStr">
+        <is>
+          <t>Ibex synchro-tilter chairs</t>
+        </is>
+      </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>MVL2801</t>
+        </is>
+      </c>
+      <c r="I29" s="33" t="inlineStr"/>
+      <c r="J29" s="33" t="inlineStr"/>
+      <c r="K29" s="33" t="inlineStr"/>
+      <c r="L29" s="33" t="inlineStr"/>
+      <c r="M29" s="33" t="inlineStr"/>
+      <c r="N29" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pneumatic seat height adjustment ; Seat range from 16-1/2” to 20-1/2” ; Back tilts 2 degrees for every 1 degree the seat tilts </t>
+        </is>
+      </c>
+      <c r="O29" s="33" t="inlineStr"/>
+      <c r="P29" s="33" t="inlineStr"/>
+      <c r="Q29" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R29" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S29" s="35" t="inlineStr"/>
+      <c r="T29" s="25" t="inlineStr"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>ibex-upholstered-seat-back-guest-chair-mvl2819-1</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>Ibex | upholstered seat &amp; back guest chair — MVL2819</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>353.87</t>
+        </is>
+      </c>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>Ibex</t>
+        </is>
+      </c>
+      <c r="H30" s="23" t="inlineStr">
+        <is>
+          <t>MVL2819</t>
+        </is>
+      </c>
+      <c r="I30" s="33" t="inlineStr"/>
+      <c r="J30" s="33" t="inlineStr"/>
+      <c r="K30" s="33" t="inlineStr"/>
+      <c r="L30" s="23" t="inlineStr">
+        <is>
+          <t>upholstered</t>
+        </is>
+      </c>
+      <c r="M30" s="33" t="inlineStr"/>
+      <c r="N30" s="23" t="inlineStr">
+        <is>
+          <t>MVL2819 Ibex | Upholstered Seat &amp; Back Guest Chair Elevate your office experience</t>
+        </is>
+      </c>
+      <c r="O30" s="33" t="inlineStr"/>
+      <c r="P30" s="33" t="inlineStr"/>
+      <c r="Q30" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R30" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S30" s="35" t="inlineStr"/>
+      <c r="T30" s="25" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="27" t="inlineStr">
+        <is>
+          <t>ibex-upholstered-seat-mesh-back-tilter-chair-mvl2801</t>
+        </is>
+      </c>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Ibex upholstered seat &amp; mesh back tilter chair — MVL2804</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E31" s="27" t="inlineStr">
+        <is>
+          <t>379.99</t>
+        </is>
+      </c>
+      <c r="F31" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G31" s="33" t="inlineStr"/>
+      <c r="H31" s="23" t="inlineStr">
+        <is>
+          <t>MVL2804</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>26 x 26.5 x 38.5"</t>
+        </is>
+      </c>
+      <c r="J31" s="23" t="inlineStr">
+        <is>
+          <t>49 lbs</t>
+        </is>
+      </c>
+      <c r="K31" s="33" t="inlineStr"/>
+      <c r="L31" s="23" t="inlineStr">
+        <is>
+          <t>mesh, upholstered</t>
+        </is>
+      </c>
+      <c r="M31" s="33" t="inlineStr"/>
+      <c r="N31" s="23" t="inlineStr">
+        <is>
+          <t>Ibex | Upholstered Seat &amp; Mesh Back Tilter Elevate your office experience with Ib; Black (MS69) Seat Available in all Grade 1 seating textiles (previously MVL2801F)</t>
+        </is>
+      </c>
+      <c r="O31" s="33" t="inlineStr"/>
+      <c r="P31" s="33" t="inlineStr"/>
+      <c r="Q31" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R31" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S31" s="35" t="inlineStr"/>
+      <c r="T31" s="25" t="inlineStr"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>kneeling-chair-kcm1420</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>Kneeling chair — KCM1420</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>179.99</t>
+        </is>
+      </c>
+      <c r="F32" s="33" t="inlineStr"/>
+      <c r="G32" s="23" t="inlineStr">
+        <is>
+          <t>Kneeling chair</t>
+        </is>
+      </c>
+      <c r="H32" s="23" t="inlineStr">
+        <is>
+          <t>KCM1420</t>
+        </is>
+      </c>
+      <c r="I32" s="33" t="inlineStr"/>
+      <c r="J32" s="33" t="inlineStr"/>
+      <c r="K32" s="23" t="inlineStr">
+        <is>
+          <t>200 lbs</t>
+        </is>
+      </c>
+      <c r="L32" s="23" t="inlineStr">
+        <is>
+          <t>fabric, foam</t>
+        </is>
+      </c>
+      <c r="M32" s="33" t="inlineStr"/>
+      <c r="N32" s="23" t="inlineStr">
+        <is>
+          <t>This adjustable kneeling chair is specially designed to relieve spinal strain</t>
+        </is>
+      </c>
+      <c r="O32" s="33" t="inlineStr"/>
+      <c r="P32" s="23" t="inlineStr">
+        <is>
+          <t>Limited Warranty</t>
+        </is>
+      </c>
+      <c r="Q32" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R32" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S32" s="35" t="inlineStr"/>
+      <c r="T32" s="25" t="inlineStr"/>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>knight-lightweight-tilter-chair-otg11360</t>
+        </is>
+      </c>
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Knight lightweight tilter chair — OTG11360</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>279.99</t>
+        </is>
+      </c>
+      <c r="F33" s="33" t="inlineStr"/>
+      <c r="G33" s="23" t="inlineStr">
+        <is>
+          <t>Knight lightweight tilter chair</t>
+        </is>
+      </c>
+      <c r="H33" s="23" t="inlineStr">
+        <is>
+          <t>OTG11360</t>
+        </is>
+      </c>
+      <c r="I33" s="33" t="inlineStr"/>
+      <c r="J33" s="33" t="inlineStr"/>
+      <c r="K33" s="33" t="inlineStr"/>
+      <c r="L33" s="23" t="inlineStr">
+        <is>
+          <t>mesh</t>
+        </is>
+      </c>
+      <c r="M33" s="33" t="inlineStr"/>
+      <c r="N33" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Offices to Go® Knight Lightweight Tilter Chair ; Upright tilt lock ; Fixed loop arms </t>
+        </is>
+      </c>
+      <c r="O33" s="33" t="inlineStr"/>
+      <c r="P33" s="33" t="inlineStr"/>
+      <c r="Q33" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R33" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S33" s="35" t="inlineStr"/>
+      <c r="T33" s="25" t="inlineStr"/>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>kody-mesh-chair-otg13110</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>Kody mesh chair — OTG13110</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="inlineStr">
+        <is>
+          <t>319.99</t>
+        </is>
+      </c>
+      <c r="F34" s="33" t="inlineStr"/>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>Kody mesh chair</t>
+        </is>
+      </c>
+      <c r="H34" s="23" t="inlineStr">
+        <is>
+          <t>OTG13110</t>
+        </is>
+      </c>
+      <c r="I34" s="33" t="inlineStr"/>
+      <c r="J34" s="33" t="inlineStr"/>
+      <c r="K34" s="33" t="inlineStr"/>
+      <c r="L34" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric</t>
+        </is>
+      </c>
+      <c r="M34" s="33" t="inlineStr"/>
+      <c r="N34" s="23" t="inlineStr">
+        <is>
+          <t>Kody | High back synchro-tilter Perfectly suited for any workspace, Kody combines</t>
+        </is>
+      </c>
+      <c r="O34" s="33" t="inlineStr"/>
+      <c r="P34" s="33" t="inlineStr"/>
+      <c r="Q34" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R34" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S34" s="35" t="inlineStr"/>
+      <c r="T34" s="25" t="inlineStr"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>kylie-multi-purpose-stacking-chair-cadet-otg11355c</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>Kylie | multi-purpose stacking chair - cadet — OTG11355C</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>159.99</t>
+        </is>
+      </c>
+      <c r="F35" s="33" t="inlineStr"/>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>Kylie</t>
+        </is>
+      </c>
+      <c r="H35" s="23" t="inlineStr">
+        <is>
+          <t>OTG11355C</t>
+        </is>
+      </c>
+      <c r="I35" s="33" t="inlineStr"/>
+      <c r="J35" s="23" t="inlineStr">
+        <is>
+          <t>9.5 lbs</t>
+        </is>
+      </c>
+      <c r="K35" s="33" t="inlineStr"/>
+      <c r="L35" s="23" t="inlineStr">
+        <is>
+          <t>polypropylene, plastic</t>
+        </is>
+      </c>
+      <c r="M35" s="33" t="inlineStr"/>
+      <c r="N35" s="23" t="inlineStr">
+        <is>
+          <t>OTG11355C Lightweight multi-purpose stacking chairs</t>
+        </is>
+      </c>
+      <c r="O35" s="23" t="inlineStr">
+        <is>
+          <t>GREENGUARD</t>
+        </is>
+      </c>
+      <c r="P35" s="23" t="inlineStr">
+        <is>
+          <t>Lifetime warranty</t>
+        </is>
+      </c>
+      <c r="Q35" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R35" s="37" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="S35" s="35" t="inlineStr"/>
+      <c r="T35" s="25" t="inlineStr"/>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>marlee-midback-chair-bonded-leather-mvl11722</t>
+        </is>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>Marlee midback chair bonded leather — MVL11722</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E36" s="32" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F36" s="33" t="inlineStr"/>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>Marlee midback chair bonded leather</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr">
+        <is>
+          <t>MVL11722</t>
+        </is>
+      </c>
+      <c r="I36" s="33" t="inlineStr"/>
+      <c r="J36" s="33" t="inlineStr"/>
+      <c r="K36" s="33" t="inlineStr"/>
+      <c r="L36" s="23" t="inlineStr">
+        <is>
+          <t>nylon, glass, upholstered</t>
+        </is>
+      </c>
+      <c r="M36" s="33" t="inlineStr"/>
+      <c r="N36" s="23" t="inlineStr">
+        <is>
+          <t>MVL11722 Marlee | Medium Back Synchro-Tilter Discover the perfect blend of comfor</t>
+        </is>
+      </c>
+      <c r="O36" s="33" t="inlineStr"/>
+      <c r="P36" s="33" t="inlineStr"/>
+      <c r="Q36" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R36" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S36" s="35" t="inlineStr"/>
+      <c r="T36" s="25" t="inlineStr"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>mesh-chair-java-otg10902</t>
+        </is>
+      </c>
+      <c r="B37" s="27" t="inlineStr">
+        <is>
+          <t>Mesh chair java — OTG10902</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>249.99</t>
+        </is>
+      </c>
+      <c r="F37" s="33" t="inlineStr"/>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>Mesh chair java</t>
+        </is>
+      </c>
+      <c r="H37" s="23" t="inlineStr">
+        <is>
+          <t>OTG10902</t>
+        </is>
+      </c>
+      <c r="I37" s="33" t="inlineStr"/>
+      <c r="J37" s="33" t="inlineStr"/>
+      <c r="K37" s="33" t="inlineStr"/>
+      <c r="L37" s="23" t="inlineStr">
+        <is>
+          <t>mesh</t>
+        </is>
+      </c>
+      <c r="M37" s="33" t="inlineStr"/>
+      <c r="N37" s="23" t="inlineStr">
+        <is>
+          <t>OTG10902 Java | High Back Tilter Tilter mechanism Durable rear shroud Upright pos</t>
+        </is>
+      </c>
+      <c r="O37" s="33" t="inlineStr"/>
+      <c r="P37" s="33" t="inlineStr"/>
+      <c r="Q37" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R37" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S37" s="35" t="inlineStr"/>
+      <c r="T37" s="25" t="inlineStr"/>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>minto-low-back-stacking-armchair-mvl2747</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>Minto | low back stacking armchair — MVL2747</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E38" s="32" t="inlineStr">
+        <is>
+          <t>158.9</t>
+        </is>
+      </c>
+      <c r="F38" s="33" t="inlineStr"/>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>Minto</t>
+        </is>
+      </c>
+      <c r="H38" s="23" t="inlineStr">
+        <is>
+          <t>MVL2747</t>
+        </is>
+      </c>
+      <c r="I38" s="33" t="inlineStr"/>
+      <c r="J38" s="33" t="inlineStr"/>
+      <c r="K38" s="33" t="inlineStr"/>
+      <c r="L38" s="23" t="inlineStr">
+        <is>
+          <t>polypropylene, steel, upholstered</t>
+        </is>
+      </c>
+      <c r="M38" s="33" t="inlineStr"/>
+      <c r="N38" s="23" t="inlineStr">
+        <is>
+          <t>Minto | Low Back Stacking Armchair Fully upholstered seat and back Stacking armch</t>
+        </is>
+      </c>
+      <c r="O38" s="33" t="inlineStr"/>
+      <c r="P38" s="33" t="inlineStr"/>
+      <c r="Q38" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R38" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S38" s="35" t="inlineStr"/>
+      <c r="T38" s="25" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>mobile-folding-chair-storage-cart-3</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="inlineStr">
+        <is>
+          <t>Mobile folding chair storage cart</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D39" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>298.71</t>
+        </is>
+      </c>
+      <c r="F39" s="33" t="inlineStr"/>
+      <c r="G39" s="33" t="inlineStr"/>
+      <c r="H39" s="33" t="inlineStr"/>
+      <c r="I39" s="33" t="inlineStr"/>
+      <c r="J39" s="33" t="inlineStr"/>
+      <c r="K39" s="33" t="inlineStr"/>
+      <c r="L39" s="23" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="M39" s="33" t="inlineStr"/>
+      <c r="N39" s="23" t="inlineStr">
+        <is>
+          <t>Convenient storage and transport of Toughlite folding chairs Heavy duty locking c; FC6 chairs or 26 TLT-FCB6 chairs (TLT-FCB6 chairs stack in alternating directions; CCART Manufacturer Website Address : http://www</t>
+        </is>
+      </c>
+      <c r="O39" s="33" t="inlineStr"/>
+      <c r="P39" s="23" t="inlineStr">
+        <is>
+          <t>Limited Warranty</t>
+        </is>
+      </c>
+      <c r="Q39" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R39" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S39" s="35" t="inlineStr"/>
+      <c r="T39" s="25" t="inlineStr"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>mvl11860-stradic-mesh-back-tilter</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>MVL11860 stradic | mesh back tilter</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E40" s="32" t="inlineStr">
+        <is>
+          <t>349.99</t>
+        </is>
+      </c>
+      <c r="F40" s="33" t="inlineStr"/>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>MVL11860 stradic</t>
+        </is>
+      </c>
+      <c r="H40" s="33" t="inlineStr"/>
+      <c r="I40" s="33" t="inlineStr"/>
+      <c r="J40" s="33" t="inlineStr"/>
+      <c r="K40" s="33" t="inlineStr"/>
+      <c r="L40" s="23" t="inlineStr">
+        <is>
+          <t>mesh</t>
+        </is>
+      </c>
+      <c r="M40" s="33" t="inlineStr"/>
+      <c r="N40" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stradic | Mesh Back Tilter Tilter mechanism Upright tilt-lock Air-flow mesh back </t>
+        </is>
+      </c>
+      <c r="O40" s="33" t="inlineStr"/>
+      <c r="P40" s="33" t="inlineStr"/>
+      <c r="Q40" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R40" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S40" s="35" t="inlineStr"/>
+      <c r="T40" s="25" t="inlineStr"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>mvl2732-annapolis-high-back-luxhide-tilter</t>
+        </is>
+      </c>
+      <c r="B41" s="27" t="inlineStr">
+        <is>
+          <t>MVL2732 annapolis | high back luxhide tilter</t>
+        </is>
+      </c>
+      <c r="C41" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D41" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>219.99</t>
+        </is>
+      </c>
+      <c r="F41" s="33" t="inlineStr"/>
+      <c r="G41" s="23" t="inlineStr">
+        <is>
+          <t>MVL2732 annapolis</t>
+        </is>
+      </c>
+      <c r="H41" s="33" t="inlineStr"/>
+      <c r="I41" s="33" t="inlineStr"/>
+      <c r="J41" s="33" t="inlineStr"/>
+      <c r="K41" s="33" t="inlineStr"/>
+      <c r="L41" s="23" t="inlineStr">
+        <is>
+          <t>leather, nylon, upholstered</t>
+        </is>
+      </c>
+      <c r="M41" s="33" t="inlineStr"/>
+      <c r="N41" s="23" t="inlineStr">
+        <is>
+          <t>MVL2732 Annapolis | High Back Luxhide Tilter Tilter mechanism Upright position ti</t>
+        </is>
+      </c>
+      <c r="O41" s="33" t="inlineStr"/>
+      <c r="P41" s="33" t="inlineStr"/>
+      <c r="Q41" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R41" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S41" s="35" t="inlineStr"/>
+      <c r="T41" s="25" t="inlineStr"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>mvl2786-yoho-armless-low-back-task-chair</t>
+        </is>
+      </c>
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>MVL2786 yoho | armless low back task chair</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E42" s="32" t="inlineStr">
+        <is>
+          <t>239.99</t>
+        </is>
+      </c>
+      <c r="F42" s="33" t="inlineStr"/>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>MVL2786 yoho</t>
+        </is>
+      </c>
+      <c r="H42" s="33" t="inlineStr"/>
+      <c r="I42" s="33" t="inlineStr"/>
+      <c r="J42" s="33" t="inlineStr"/>
+      <c r="K42" s="33" t="inlineStr"/>
+      <c r="L42" s="23" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="M42" s="33" t="inlineStr"/>
+      <c r="N42" s="23" t="inlineStr">
+        <is>
+          <t>MVL2786 Yoho | Armless Low Back Task Chair Low back task chair Seat depth adjustm; MVL2784 Dual wheel carpet casters Available in Bonded Leather Stocked in Black</t>
+        </is>
+      </c>
+      <c r="O42" s="33" t="inlineStr"/>
+      <c r="P42" s="33" t="inlineStr"/>
+      <c r="Q42" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R42" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S42" s="35" t="inlineStr"/>
+      <c r="T42" s="25" t="inlineStr"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="27" t="inlineStr">
+        <is>
+          <t>mvl3101-avro-mesh-back-synchro-tilter-chair</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
+        <is>
+          <t>MVL3101 avro mesh back synchro-tilter chair</t>
+        </is>
+      </c>
+      <c r="C43" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D43" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E43" s="27" t="inlineStr">
+        <is>
+          <t>469.99</t>
+        </is>
+      </c>
+      <c r="F43" s="33" t="inlineStr"/>
+      <c r="G43" s="33" t="inlineStr"/>
+      <c r="H43" s="33" t="inlineStr"/>
+      <c r="I43" s="23" t="inlineStr">
+        <is>
+          <t>26 x 27 x 38.5"</t>
+        </is>
+      </c>
+      <c r="J43" s="23" t="inlineStr">
+        <is>
+          <t>42 lbs</t>
+        </is>
+      </c>
+      <c r="K43" s="33" t="inlineStr"/>
+      <c r="L43" s="23" t="inlineStr">
+        <is>
+          <t>mesh, upholstered</t>
+        </is>
+      </c>
+      <c r="M43" s="33" t="inlineStr"/>
+      <c r="N43" s="23" t="inlineStr">
+        <is>
+          <t>MVL3101 Avro | Upholstered Seat &amp; Mesh Back Synchro-Tilter Synchro-tilt mechanism</t>
+        </is>
+      </c>
+      <c r="O43" s="33" t="inlineStr"/>
+      <c r="P43" s="33" t="inlineStr"/>
+      <c r="Q43" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R43" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S43" s="35" t="inlineStr"/>
+      <c r="T43" s="25" t="inlineStr"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>mvl3103-avro-upholstered-seat-mesh-back-multi-tilter</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>MVL3103 avro | upholstered seat &amp; mesh back multi-tilter</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E44" s="32" t="inlineStr">
+        <is>
+          <t>499.99</t>
+        </is>
+      </c>
+      <c r="F44" s="33" t="inlineStr"/>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>MVL3103 avro</t>
+        </is>
+      </c>
+      <c r="H44" s="33" t="inlineStr"/>
+      <c r="I44" s="33" t="inlineStr"/>
+      <c r="J44" s="33" t="inlineStr"/>
+      <c r="K44" s="33" t="inlineStr"/>
+      <c r="L44" s="23" t="inlineStr">
+        <is>
+          <t>mesh, upholstered</t>
+        </is>
+      </c>
+      <c r="M44" s="33" t="inlineStr"/>
+      <c r="N44" s="23" t="inlineStr">
+        <is>
+          <t>MVL3103 Avro | Upholstered Seat &amp; Mesh Back Multi-Tilter Multi-tilt mechanism Air</t>
+        </is>
+      </c>
+      <c r="O44" s="33" t="inlineStr"/>
+      <c r="P44" s="33" t="inlineStr"/>
+      <c r="Q44" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R44" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S44" s="35" t="inlineStr"/>
+      <c r="T44" s="25" t="inlineStr"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>obusforme-comfort-medium-back-chair-fabric-1241-3-copy</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
+        <is>
+          <t>ObusForme Comfort medium back chair — 1241-3</t>
+        </is>
+      </c>
+      <c r="C45" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D45" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E45" s="27" t="inlineStr">
+        <is>
+          <t>645.99</t>
+        </is>
+      </c>
+      <c r="F45" s="23" t="inlineStr">
+        <is>
+          <t>ObusForme</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>ObusForme Comfort medium back chair</t>
+        </is>
+      </c>
+      <c r="H45" s="33" t="inlineStr"/>
+      <c r="I45" s="33" t="inlineStr"/>
+      <c r="J45" s="33" t="inlineStr"/>
+      <c r="K45" s="33" t="inlineStr"/>
+      <c r="L45" s="23" t="inlineStr">
+        <is>
+          <t>aluminum, nylon</t>
+        </is>
+      </c>
+      <c r="M45" s="33" t="inlineStr"/>
+      <c r="N45" s="33" t="inlineStr"/>
+      <c r="O45" s="33" t="inlineStr"/>
+      <c r="P45" s="33" t="inlineStr"/>
+      <c r="Q45" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R45" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S45" s="35" t="inlineStr"/>
+      <c r="T45" s="25" t="inlineStr"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>obusforme-comfort-medium-back-chair-fabric-1241-3-copy-1</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>ObusForme Comfort medium back chair 1261-3 schukra</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E46" s="32" t="inlineStr">
+        <is>
+          <t>749.99</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>ObusForme</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="inlineStr">
+        <is>
+          <t>ObusForme Comfort medium back chair</t>
+        </is>
+      </c>
+      <c r="H46" s="33" t="inlineStr"/>
+      <c r="I46" s="33" t="inlineStr"/>
+      <c r="J46" s="33" t="inlineStr"/>
+      <c r="K46" s="33" t="inlineStr"/>
+      <c r="L46" s="23" t="inlineStr">
+        <is>
+          <t>aluminum, nylon</t>
+        </is>
+      </c>
+      <c r="M46" s="33" t="inlineStr"/>
+      <c r="N46" s="33" t="inlineStr"/>
+      <c r="O46" s="33" t="inlineStr"/>
+      <c r="P46" s="33" t="inlineStr"/>
+      <c r="Q46" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R46" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S46" s="35" t="inlineStr"/>
+      <c r="T46" s="25" t="inlineStr"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="27" t="inlineStr">
+        <is>
+          <t>obusforme-elite-multi-tilter-chair-medium-back</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
+        <is>
+          <t>ObusForme Elite multi-tilter medium back chair</t>
+        </is>
+      </c>
+      <c r="C47" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D47" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E47" s="27" t="inlineStr">
+        <is>
+          <t>669.99</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>ObusForme</t>
+        </is>
+      </c>
+      <c r="G47" s="33" t="inlineStr"/>
+      <c r="H47" s="33" t="inlineStr"/>
+      <c r="I47" s="33" t="inlineStr"/>
+      <c r="J47" s="33" t="inlineStr"/>
+      <c r="K47" s="33" t="inlineStr"/>
+      <c r="L47" s="23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="M47" s="33" t="inlineStr"/>
+      <c r="N47" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basics® ObusForme® Elite Multi-Tilter Chairs ; This chair is designed to provide optimal ergonomic benefits, making it perfect f; Soft Descent™ pneumatic seat height adjustment </t>
+        </is>
+      </c>
+      <c r="O47" s="33" t="inlineStr"/>
+      <c r="P47" s="33" t="inlineStr"/>
+      <c r="Q47" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R47" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S47" s="35" t="inlineStr"/>
+      <c r="T47" s="25" t="inlineStr"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>offices-to-go-ashmont-tilter-chair-1</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>Offices to Go ® ashmont tilter chair</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E48" s="32" t="inlineStr">
+        <is>
+          <t>499.99</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G48" s="33" t="inlineStr"/>
+      <c r="H48" s="33" t="inlineStr"/>
+      <c r="I48" s="33" t="inlineStr"/>
+      <c r="J48" s="33" t="inlineStr"/>
+      <c r="K48" s="33" t="inlineStr"/>
+      <c r="L48" s="23" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="M48" s="33" t="inlineStr"/>
+      <c r="N48" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deep, soft cushions on seat and back ; Pneumatic seat height adjustment ; Seat range from 16” to 20” </t>
+        </is>
+      </c>
+      <c r="O48" s="33" t="inlineStr"/>
+      <c r="P48" s="33" t="inlineStr"/>
+      <c r="Q48" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R48" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S48" s="35" t="inlineStr"/>
+      <c r="T48" s="25" t="inlineStr"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="27" t="inlineStr">
+        <is>
+          <t>offices-to-go-chair-2</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
+        <is>
+          <t>Offices to Go Chair</t>
+        </is>
+      </c>
+      <c r="C49" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D49" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E49" s="27" t="inlineStr">
+        <is>
+          <t>321.0</t>
+        </is>
+      </c>
+      <c r="F49" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G49" s="33" t="inlineStr"/>
+      <c r="H49" s="33" t="inlineStr"/>
+      <c r="I49" s="33" t="inlineStr"/>
+      <c r="J49" s="33" t="inlineStr"/>
+      <c r="K49" s="33" t="inlineStr"/>
+      <c r="L49" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric, steel</t>
+        </is>
+      </c>
+      <c r="M49" s="33" t="inlineStr"/>
+      <c r="N49" s="23" t="inlineStr">
+        <is>
+          <t>Category Reception, Side &amp; Guest Chairs Manufacturer Global Upholstery Co</t>
+        </is>
+      </c>
+      <c r="O49" s="33" t="inlineStr"/>
+      <c r="P49" s="23" t="inlineStr">
+        <is>
+          <t>Lifetime warranty</t>
+        </is>
+      </c>
+      <c r="Q49" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R49" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S49" s="35" t="inlineStr"/>
+      <c r="T49" s="25" t="inlineStr"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>otg10740-masi-high-back-tilter</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>OTG10740 masi | high back tilter</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E50" s="32" t="inlineStr">
+        <is>
+          <t>319.99</t>
+        </is>
+      </c>
+      <c r="F50" s="33" t="inlineStr"/>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>OTG10740 masi</t>
+        </is>
+      </c>
+      <c r="H50" s="33" t="inlineStr"/>
+      <c r="I50" s="23" t="inlineStr">
+        <is>
+          <t>24.62 x 27 x 47.5"</t>
+        </is>
+      </c>
+      <c r="J50" s="23" t="inlineStr">
+        <is>
+          <t>33 lbs</t>
+        </is>
+      </c>
+      <c r="K50" s="33" t="inlineStr"/>
+      <c r="L50" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric, nylon, polyester, upholstered</t>
+        </is>
+      </c>
+      <c r="M50" s="33" t="inlineStr"/>
+      <c r="N50" s="23" t="inlineStr">
+        <is>
+          <t>OTG10740 Masi | High Back Tilter Transform your office with Masi; Black Seat Black Polyester Specifications Dimensions: 24</t>
+        </is>
+      </c>
+      <c r="O50" s="33" t="inlineStr"/>
+      <c r="P50" s="33" t="inlineStr"/>
+      <c r="Q50" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R50" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S50" s="35" t="inlineStr"/>
+      <c r="T50" s="25" t="inlineStr"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>otg3915-centro-guest-chair</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
+        <is>
+          <t>OTG3915 centro guest chair</t>
+        </is>
+      </c>
+      <c r="C51" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>249.99</t>
+        </is>
+      </c>
+      <c r="F51" s="33" t="inlineStr"/>
+      <c r="G51" s="33" t="inlineStr"/>
+      <c r="H51" s="33" t="inlineStr"/>
+      <c r="I51" s="33" t="inlineStr"/>
+      <c r="J51" s="33" t="inlineStr"/>
+      <c r="K51" s="33" t="inlineStr"/>
+      <c r="L51" s="23" t="inlineStr">
+        <is>
+          <t>leather, steel, upholstered</t>
+        </is>
+      </c>
+      <c r="M51" s="33" t="inlineStr"/>
+      <c r="N51" s="23" t="inlineStr">
+        <is>
+          <t>OTG3915 Centro | Guest Chair Four-legged multi-purpose design Generous proportion</t>
+        </is>
+      </c>
+      <c r="O51" s="33" t="inlineStr"/>
+      <c r="P51" s="33" t="inlineStr"/>
+      <c r="Q51" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R51" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S51" s="35" t="inlineStr"/>
+      <c r="T51" s="25" t="inlineStr"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>pacific-high-back-tilter</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>Pacific high back tilter — MVL11870</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E52" s="32" t="inlineStr">
+        <is>
+          <t>369.99</t>
+        </is>
+      </c>
+      <c r="F52" s="33" t="inlineStr"/>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>Pacific high back tilter</t>
+        </is>
+      </c>
+      <c r="H52" s="23" t="inlineStr">
+        <is>
+          <t>MVL11870</t>
+        </is>
+      </c>
+      <c r="I52" s="33" t="inlineStr"/>
+      <c r="J52" s="33" t="inlineStr"/>
+      <c r="K52" s="33" t="inlineStr"/>
+      <c r="L52" s="33" t="inlineStr"/>
+      <c r="M52" s="33" t="inlineStr"/>
+      <c r="N52" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Easily adjust the seat height to find your perfect position, reducing strain and </t>
+        </is>
+      </c>
+      <c r="O52" s="33" t="inlineStr"/>
+      <c r="P52" s="33" t="inlineStr"/>
+      <c r="Q52" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R52" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S52" s="35" t="inlineStr"/>
+      <c r="T52" s="25" t="inlineStr"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
+        <is>
+          <t>regalia-task-mesh-chair-otg10892</t>
+        </is>
+      </c>
+      <c r="B53" s="27" t="inlineStr">
+        <is>
+          <t>Regalia task mesh chair — OTG10892</t>
+        </is>
+      </c>
+      <c r="C53" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E53" s="27" t="inlineStr">
+        <is>
+          <t>369.99</t>
+        </is>
+      </c>
+      <c r="F53" s="33" t="inlineStr"/>
+      <c r="G53" s="23" t="inlineStr">
+        <is>
+          <t>Regalia task mesh chair</t>
+        </is>
+      </c>
+      <c r="H53" s="23" t="inlineStr">
+        <is>
+          <t>OTG10892</t>
+        </is>
+      </c>
+      <c r="I53" s="33" t="inlineStr"/>
+      <c r="J53" s="33" t="inlineStr"/>
+      <c r="K53" s="33" t="inlineStr"/>
+      <c r="L53" s="33" t="inlineStr"/>
+      <c r="M53" s="33" t="inlineStr"/>
+      <c r="N53" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium Back Multi Function; Medium back design ; Pneumatic seat height adjustment </t>
+        </is>
+      </c>
+      <c r="O53" s="33" t="inlineStr"/>
+      <c r="P53" s="33" t="inlineStr"/>
+      <c r="Q53" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R53" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S53" s="35" t="inlineStr"/>
+      <c r="T53" s="25" t="inlineStr"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>sonic-armless-counter-stool-polypropylene-seat-back-6558cs</t>
+        </is>
+      </c>
+      <c r="B54" s="32" t="inlineStr">
+        <is>
+          <t>Sonic armless counter stool, polypropylene seat &amp; back (6558cs) — 6558CS</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E54" s="32" t="inlineStr">
+        <is>
+          <t>200.5</t>
+        </is>
+      </c>
+      <c r="F54" s="33" t="inlineStr"/>
+      <c r="G54" s="33" t="inlineStr"/>
+      <c r="H54" s="33" t="inlineStr"/>
+      <c r="I54" s="33" t="inlineStr"/>
+      <c r="J54" s="33" t="inlineStr"/>
+      <c r="K54" s="33" t="inlineStr"/>
+      <c r="L54" s="33" t="inlineStr"/>
+      <c r="M54" s="33" t="inlineStr"/>
+      <c r="N54" s="23" t="inlineStr">
+        <is>
+          <t>Counter Height Chair Counter Height: 36"</t>
+        </is>
+      </c>
+      <c r="O54" s="33" t="inlineStr"/>
+      <c r="P54" s="33" t="inlineStr"/>
+      <c r="Q54" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R54" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S54" s="35" t="inlineStr"/>
+      <c r="T54" s="25" t="inlineStr"/>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
+        <is>
+          <t>sparrow-otg10920-guest-chair</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>Sparrow OTG10920 guest chair</t>
+        </is>
+      </c>
+      <c r="C55" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D55" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E55" s="27" t="inlineStr">
+        <is>
+          <t>159.99</t>
+        </is>
+      </c>
+      <c r="F55" s="33" t="inlineStr"/>
+      <c r="G55" s="33" t="inlineStr"/>
+      <c r="H55" s="33" t="inlineStr"/>
+      <c r="I55" s="33" t="inlineStr"/>
+      <c r="J55" s="33" t="inlineStr"/>
+      <c r="K55" s="33" t="inlineStr"/>
+      <c r="L55" s="23" t="inlineStr">
+        <is>
+          <t>mesh, steel, upholstered</t>
+        </is>
+      </c>
+      <c r="M55" s="33" t="inlineStr"/>
+      <c r="N55" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Offices to Go® Sparrow Guest Chair ; Four leg steel base ; Stacks 4 high on the floor </t>
+        </is>
+      </c>
+      <c r="O55" s="33" t="inlineStr"/>
+      <c r="P55" s="33" t="inlineStr"/>
+      <c r="Q55" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R55" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S55" s="35" t="inlineStr"/>
+      <c r="T55" s="25" t="inlineStr"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>stacking-chair-duet-glb6621</t>
+        </is>
+      </c>
+      <c r="B56" s="32" t="inlineStr">
+        <is>
+          <t>Stacking chair duet — GLB6621</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E56" s="32" t="inlineStr">
+        <is>
+          <t>169.99</t>
+        </is>
+      </c>
+      <c r="F56" s="33" t="inlineStr"/>
+      <c r="G56" s="23" t="inlineStr">
+        <is>
+          <t>Stacking chair duet</t>
+        </is>
+      </c>
+      <c r="H56" s="23" t="inlineStr">
+        <is>
+          <t>GLB6621</t>
+        </is>
+      </c>
+      <c r="I56" s="33" t="inlineStr"/>
+      <c r="J56" s="33" t="inlineStr"/>
+      <c r="K56" s="33" t="inlineStr"/>
+      <c r="L56" s="23" t="inlineStr">
+        <is>
+          <t>polypropylene, steel, chrome, nylon, glass, upholstered</t>
+        </is>
+      </c>
+      <c r="M56" s="33" t="inlineStr"/>
+      <c r="N56" s="23" t="inlineStr">
+        <is>
+          <t>Frame is made from durable solid steel rod available in chrome only</t>
+        </is>
+      </c>
+      <c r="O56" s="33" t="inlineStr"/>
+      <c r="P56" s="33" t="inlineStr"/>
+      <c r="Q56" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R56" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S56" s="35" t="inlineStr"/>
+      <c r="T56" s="25" t="inlineStr"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>the-erin-armless-chair-wood-legs-gc36530</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>The erin armless chair, wood legs (gc36530) — GC36530</t>
+        </is>
+      </c>
+      <c r="C57" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D57" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E57" s="27" t="inlineStr">
+        <is>
+          <t>899.99</t>
+        </is>
+      </c>
+      <c r="F57" s="33" t="inlineStr"/>
+      <c r="G57" s="33" t="inlineStr"/>
+      <c r="H57" s="23" t="inlineStr">
+        <is>
+          <t>GC36530</t>
+        </is>
+      </c>
+      <c r="I57" s="33" t="inlineStr"/>
+      <c r="J57" s="33" t="inlineStr"/>
+      <c r="K57" s="33" t="inlineStr"/>
+      <c r="L57" s="33" t="inlineStr"/>
+      <c r="M57" s="33" t="inlineStr"/>
+      <c r="N57" s="23" t="inlineStr">
+        <is>
+          <t>Erin™ From boutique hotels to spa retreats, the rich experiences that designers c</t>
+        </is>
+      </c>
+      <c r="O57" s="33" t="inlineStr"/>
+      <c r="P57" s="33" t="inlineStr"/>
+      <c r="Q57" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R57" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S57" s="35" t="inlineStr"/>
+      <c r="T57" s="25" t="inlineStr"/>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>trent-tilter-chair-high-back-bonded-leather-2717-4</t>
+        </is>
+      </c>
+      <c r="B58" s="32" t="inlineStr">
+        <is>
+          <t>Trent tilter chair high back bonded leather — 2717-4</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E58" s="32" t="inlineStr">
+        <is>
+          <t>217.99</t>
+        </is>
+      </c>
+      <c r="F58" s="33" t="inlineStr"/>
+      <c r="G58" s="33" t="inlineStr"/>
+      <c r="H58" s="33" t="inlineStr"/>
+      <c r="I58" s="33" t="inlineStr"/>
+      <c r="J58" s="33" t="inlineStr"/>
+      <c r="K58" s="33" t="inlineStr"/>
+      <c r="L58" s="23" t="inlineStr">
+        <is>
+          <t>leather</t>
+        </is>
+      </c>
+      <c r="M58" s="33" t="inlineStr"/>
+      <c r="N58" s="23" t="inlineStr">
+        <is>
+          <t>Trent Tilter Chair High Back Bonded Leather Luxhide Black Pneumatic Seat Height T</t>
+        </is>
+      </c>
+      <c r="O58" s="33" t="inlineStr"/>
+      <c r="P58" s="33" t="inlineStr"/>
+      <c r="Q58" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R58" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S58" s="35" t="inlineStr"/>
+      <c r="T58" s="25" t="inlineStr"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="27" t="inlineStr">
+        <is>
+          <t>tritek-7472-3-chair</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>Tritek 7472-3 chair</t>
+        </is>
+      </c>
+      <c r="C59" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D59" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E59" s="27" t="inlineStr">
+        <is>
+          <t>849.99</t>
+        </is>
+      </c>
+      <c r="F59" s="33" t="inlineStr"/>
+      <c r="G59" s="23" t="inlineStr">
+        <is>
+          <t>Tritek</t>
+        </is>
+      </c>
+      <c r="H59" s="33" t="inlineStr"/>
+      <c r="I59" s="33" t="inlineStr"/>
+      <c r="J59" s="33" t="inlineStr"/>
+      <c r="K59" s="33" t="inlineStr"/>
+      <c r="L59" s="33" t="inlineStr"/>
+      <c r="M59" s="33" t="inlineStr"/>
+      <c r="N59" s="33" t="inlineStr"/>
+      <c r="O59" s="33" t="inlineStr"/>
+      <c r="P59" s="33" t="inlineStr"/>
+      <c r="Q59" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R59" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S59" s="35" t="inlineStr"/>
+      <c r="T59" s="25" t="inlineStr"/>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>ultra-armless-high-back-tilter-mvl11732</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="inlineStr">
+        <is>
+          <t>Ultra | armless high back tilter — MVL11732</t>
+        </is>
+      </c>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E60" s="32" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F60" s="33" t="inlineStr"/>
+      <c r="G60" s="23" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="H60" s="23" t="inlineStr">
+        <is>
+          <t>MVL11732</t>
+        </is>
+      </c>
+      <c r="I60" s="33" t="inlineStr"/>
+      <c r="J60" s="33" t="inlineStr"/>
+      <c r="K60" s="33" t="inlineStr"/>
+      <c r="L60" s="23" t="inlineStr">
+        <is>
+          <t>leather, chrome, upholstered</t>
+        </is>
+      </c>
+      <c r="M60" s="33" t="inlineStr"/>
+      <c r="N60" s="23" t="inlineStr">
+        <is>
+          <t>MVL11732 Tilter mechanism Upright position tilt lock Chrome base Dual wheel carpe</t>
+        </is>
+      </c>
+      <c r="O60" s="33" t="inlineStr"/>
+      <c r="P60" s="33" t="inlineStr"/>
+      <c r="Q60" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R60" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S60" s="35" t="inlineStr"/>
+      <c r="T60" s="25" t="inlineStr"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="27" t="inlineStr">
+        <is>
+          <t>ultra-medium-back-guest-chair-with-arms-mvl11742</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>Ultra | medium back guest chair with arms — MVL11742</t>
+        </is>
+      </c>
+      <c r="C61" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D61" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E61" s="27" t="inlineStr">
+        <is>
+          <t>447.99</t>
+        </is>
+      </c>
+      <c r="F61" s="33" t="inlineStr"/>
+      <c r="G61" s="23" t="inlineStr">
+        <is>
+          <t>Ultra</t>
+        </is>
+      </c>
+      <c r="H61" s="23" t="inlineStr">
+        <is>
+          <t>MVL11742</t>
+        </is>
+      </c>
+      <c r="I61" s="33" t="inlineStr"/>
+      <c r="J61" s="33" t="inlineStr"/>
+      <c r="K61" s="33" t="inlineStr"/>
+      <c r="L61" s="23" t="inlineStr">
+        <is>
+          <t>vinyl, steel, chrome, upholstered</t>
+        </is>
+      </c>
+      <c r="M61" s="33" t="inlineStr"/>
+      <c r="N61" s="23" t="inlineStr">
+        <is>
+          <t>MVL11742 Ultra | Medium Back Guest Chair with Arms Cantilever style base Welded s; MVL11733 Can be upholstered in LuxPlus vinyl</t>
+        </is>
+      </c>
+      <c r="O61" s="33" t="inlineStr"/>
+      <c r="P61" s="33" t="inlineStr"/>
+      <c r="Q61" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R61" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S61" s="35" t="inlineStr"/>
+      <c r="T61" s="25" t="inlineStr"/>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="32" t="inlineStr">
+        <is>
+          <t>yoho-medium-back-task-chair-mvl2778</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="inlineStr">
+        <is>
+          <t>Yoho | medium back task chair — MVL2778</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E62" s="32" t="inlineStr">
+        <is>
+          <t>369.99</t>
+        </is>
+      </c>
+      <c r="F62" s="33" t="inlineStr"/>
+      <c r="G62" s="23" t="inlineStr">
+        <is>
+          <t>Yoho</t>
+        </is>
+      </c>
+      <c r="H62" s="23" t="inlineStr">
+        <is>
+          <t>MVL2778</t>
+        </is>
+      </c>
+      <c r="I62" s="23" t="inlineStr">
+        <is>
+          <t>24.5 x 24.5 x 38"</t>
+        </is>
+      </c>
+      <c r="J62" s="23" t="inlineStr">
+        <is>
+          <t>32 lbs</t>
+        </is>
+      </c>
+      <c r="K62" s="33" t="inlineStr"/>
+      <c r="L62" s="33" t="inlineStr"/>
+      <c r="M62" s="33" t="inlineStr"/>
+      <c r="N62" s="23" t="inlineStr">
+        <is>
+          <t>MVL2778 Yoho | Medium Back Task Chair Canadian made task chairs Thick cushion com</t>
+        </is>
+      </c>
+      <c r="O62" s="23" t="inlineStr">
+        <is>
+          <t>GREENGUARD</t>
+        </is>
+      </c>
+      <c r="P62" s="33" t="inlineStr"/>
+      <c r="Q62" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R62" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S62" s="35" t="inlineStr"/>
+      <c r="T62" s="25" t="inlineStr"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>zune-tilter-chair-black-fabric-seat-plastic-mesh-back-medium-back-otg11751b</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>Zune tilter chair - black fabric seat - plastic, mesh back - medium back — OTG11751B</t>
+        </is>
+      </c>
+      <c r="C63" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D63" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E63" s="27" t="inlineStr">
+        <is>
+          <t>239.99</t>
+        </is>
+      </c>
+      <c r="F63" s="33" t="inlineStr"/>
+      <c r="G63" s="33" t="inlineStr"/>
+      <c r="H63" s="23" t="inlineStr">
+        <is>
+          <t>OTG11751B</t>
+        </is>
+      </c>
+      <c r="I63" s="33" t="inlineStr"/>
+      <c r="J63" s="33" t="inlineStr"/>
+      <c r="K63" s="33" t="inlineStr"/>
+      <c r="L63" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric, leather, plastic, upholstered</t>
+        </is>
+      </c>
+      <c r="M63" s="33" t="inlineStr"/>
+      <c r="N63" s="23" t="inlineStr">
+        <is>
+          <t>Mesh, plastic back shroud with modern slat design</t>
+        </is>
+      </c>
+      <c r="O63" s="33" t="inlineStr"/>
+      <c r="P63" s="33" t="inlineStr"/>
+      <c r="Q63" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R63" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S63" s="35" t="inlineStr"/>
+      <c r="T63" s="25" t="inlineStr"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>desk-shell-5-sizes</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="inlineStr">
+        <is>
+          <t>Desk shell (5 sizes) — 5 sizes</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E64" s="32" t="inlineStr">
+        <is>
+          <t>429.99</t>
+        </is>
+      </c>
+      <c r="F64" s="33" t="inlineStr"/>
+      <c r="G64" s="33" t="inlineStr"/>
+      <c r="H64" s="33" t="inlineStr"/>
+      <c r="I64" s="33" t="inlineStr"/>
+      <c r="J64" s="33" t="inlineStr"/>
+      <c r="K64" s="33" t="inlineStr"/>
+      <c r="L64" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M64" s="33" t="inlineStr"/>
+      <c r="N64" s="23" t="inlineStr">
+        <is>
+          <t>Simple and modular components combining classic design, quality and value to supp</t>
+        </is>
+      </c>
+      <c r="O64" s="33" t="inlineStr"/>
+      <c r="P64" s="33" t="inlineStr"/>
+      <c r="Q64" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R64" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S64" s="35" t="inlineStr"/>
+      <c r="T64" s="25" t="inlineStr"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
+        <is>
+          <t>desk-single-pedestal</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>Desk single pedestal</t>
+        </is>
+      </c>
+      <c r="C65" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D65" s="27" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E65" s="27" t="inlineStr">
+        <is>
+          <t>699.99</t>
+        </is>
+      </c>
+      <c r="F65" s="33" t="inlineStr"/>
+      <c r="G65" s="33" t="inlineStr"/>
+      <c r="H65" s="33" t="inlineStr"/>
+      <c r="I65" s="33" t="inlineStr"/>
+      <c r="J65" s="33" t="inlineStr"/>
+      <c r="K65" s="33" t="inlineStr"/>
+      <c r="L65" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M65" s="33" t="inlineStr"/>
+      <c r="N65" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEWLAND | SINGLE PEDESTAL DESK Newland - simple and modular components combining </t>
+        </is>
+      </c>
+      <c r="O65" s="33" t="inlineStr"/>
+      <c r="P65" s="33" t="inlineStr"/>
+      <c r="Q65" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R65" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S65" s="35" t="inlineStr"/>
+      <c r="T65" s="25" t="inlineStr"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="32" t="inlineStr">
+        <is>
+          <t>desk-single-pedestal-1</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="inlineStr">
+        <is>
+          <t>Newland | double pedestal desk</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E66" s="32" t="inlineStr">
+        <is>
+          <t>949.99</t>
+        </is>
+      </c>
+      <c r="F66" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G66" s="23" t="inlineStr">
+        <is>
+          <t>Newland</t>
+        </is>
+      </c>
+      <c r="H66" s="33" t="inlineStr"/>
+      <c r="I66" s="33" t="inlineStr"/>
+      <c r="J66" s="33" t="inlineStr"/>
+      <c r="K66" s="33" t="inlineStr"/>
+      <c r="L66" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M66" s="33" t="inlineStr"/>
+      <c r="N66" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEWLAND | DOUBLE PEDESTAL DESK Newland - simple and modular components combining </t>
+        </is>
+      </c>
+      <c r="O66" s="33" t="inlineStr"/>
+      <c r="P66" s="33" t="inlineStr"/>
+      <c r="Q66" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R66" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S66" s="35" t="inlineStr"/>
+      <c r="T66" s="25" t="inlineStr"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
+        <is>
+          <t>electric-dual-monitor-height-adjustable-standing-desk-workstation-dc450</t>
+        </is>
+      </c>
+      <c r="B67" s="27" t="inlineStr">
+        <is>
+          <t>Electric dual monitor height adjustable standing desk workstation — DC450</t>
+        </is>
+      </c>
+      <c r="C67" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D67" s="27" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E67" s="27" t="inlineStr">
+        <is>
+          <t>749.99</t>
+        </is>
+      </c>
+      <c r="F67" s="33" t="inlineStr"/>
+      <c r="G67" s="33" t="inlineStr"/>
+      <c r="H67" s="23" t="inlineStr">
+        <is>
+          <t>DC450</t>
+        </is>
+      </c>
+      <c r="I67" s="33" t="inlineStr"/>
+      <c r="J67" s="33" t="inlineStr"/>
+      <c r="K67" s="33" t="inlineStr"/>
+      <c r="L67" s="23" t="inlineStr">
+        <is>
+          <t>steel, aluminum, wood, laminate</t>
+        </is>
+      </c>
+      <c r="M67" s="33" t="inlineStr"/>
+      <c r="N67" s="23" t="inlineStr">
+        <is>
+          <t>Built to fit your needs and keep your equipment safe and organized Allows a maxim; Perfect in size to make viewing extremely comfortable</t>
+        </is>
+      </c>
+      <c r="O67" s="33" t="inlineStr"/>
+      <c r="P67" s="33" t="inlineStr"/>
+      <c r="Q67" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R67" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S67" s="35" t="inlineStr"/>
+      <c r="T67" s="25" t="inlineStr"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>innovations-l-shape-desk-with-hutch</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="inlineStr">
+        <is>
+          <t>Innovations l-shape desk with hutch</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E68" s="32" t="inlineStr">
+        <is>
+          <t>1699.99</t>
+        </is>
+      </c>
+      <c r="F68" s="33" t="inlineStr"/>
+      <c r="G68" s="33" t="inlineStr"/>
+      <c r="H68" s="33" t="inlineStr"/>
+      <c r="I68" s="33" t="inlineStr"/>
+      <c r="J68" s="33" t="inlineStr"/>
+      <c r="K68" s="33" t="inlineStr"/>
+      <c r="L68" s="33" t="inlineStr"/>
+      <c r="M68" s="33" t="inlineStr"/>
+      <c r="N68" s="23" t="inlineStr">
+        <is>
+          <t>Size: 71" x 71" Requires Assembly In Stock Tack Board not included</t>
+        </is>
+      </c>
+      <c r="O68" s="33" t="inlineStr"/>
+      <c r="P68" s="33" t="inlineStr"/>
+      <c r="Q68" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R68" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S68" s="35" t="inlineStr"/>
+      <c r="T68" s="25" t="inlineStr"/>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="27" t="inlineStr">
+        <is>
+          <t>innovations-suite</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="inlineStr">
+        <is>
+          <t>Innovations suite</t>
+        </is>
+      </c>
+      <c r="C69" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D69" s="27" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E69" s="27" t="inlineStr">
+        <is>
+          <t>4175.0</t>
+        </is>
+      </c>
+      <c r="F69" s="33" t="inlineStr"/>
+      <c r="G69" s="33" t="inlineStr"/>
+      <c r="H69" s="33" t="inlineStr"/>
+      <c r="I69" s="23" t="inlineStr">
+        <is>
+          <t>90 x 24 x 66"</t>
+        </is>
+      </c>
+      <c r="J69" s="33" t="inlineStr"/>
+      <c r="K69" s="33" t="inlineStr"/>
+      <c r="L69" s="23" t="inlineStr">
+        <is>
+          <t>steel, wood, glass</t>
+        </is>
+      </c>
+      <c r="M69" s="33" t="inlineStr"/>
+      <c r="N69" s="23" t="inlineStr">
+        <is>
+          <t>Description Heavy Duty 3-stage steel frame design Actuator system with synchroniz</t>
+        </is>
+      </c>
+      <c r="O69" s="33" t="inlineStr"/>
+      <c r="P69" s="33" t="inlineStr"/>
+      <c r="Q69" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R69" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S69" s="35" t="inlineStr"/>
+      <c r="T69" s="25" t="inlineStr"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="32" t="inlineStr">
+        <is>
+          <t>innovations-u-shape-suite</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="inlineStr">
+        <is>
+          <t>Innovations u-shape suite</t>
+        </is>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E70" s="32" t="inlineStr">
+        <is>
+          <t>3299.99</t>
+        </is>
+      </c>
+      <c r="F70" s="33" t="inlineStr"/>
+      <c r="G70" s="33" t="inlineStr"/>
+      <c r="H70" s="33" t="inlineStr"/>
+      <c r="I70" s="33" t="inlineStr"/>
+      <c r="J70" s="33" t="inlineStr"/>
+      <c r="K70" s="33" t="inlineStr"/>
+      <c r="L70" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M70" s="33" t="inlineStr"/>
+      <c r="N70" s="23" t="inlineStr">
+        <is>
+          <t>Includes INV-B7248CMB Corner Module Desk INV-2436RSBR INV-2472SH INV-FPUF Return ; INV-2236LFX Lateral File INV-B7248CMD with INV-B4872CMD INV-2237STC INV-3672H INV</t>
+        </is>
+      </c>
+      <c r="O70" s="33" t="inlineStr"/>
+      <c r="P70" s="33" t="inlineStr"/>
+      <c r="Q70" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R70" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S70" s="35" t="inlineStr"/>
+      <c r="T70" s="25" t="inlineStr"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="27" t="inlineStr">
+        <is>
+          <t>l-shape-desk-set-72x72</t>
+        </is>
+      </c>
+      <c r="B71" s="27" t="inlineStr">
+        <is>
+          <t>L-shape desk set 72"x72" bbf/ff innovations — 72"x72"</t>
+        </is>
+      </c>
+      <c r="C71" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D71" s="27" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E71" s="27" t="inlineStr">
+        <is>
+          <t>1499.99</t>
+        </is>
+      </c>
+      <c r="F71" s="33" t="inlineStr"/>
+      <c r="G71" s="23" t="inlineStr">
+        <is>
+          <t>L-shape desk set</t>
+        </is>
+      </c>
+      <c r="H71" s="33" t="inlineStr"/>
+      <c r="I71" s="33" t="inlineStr"/>
+      <c r="J71" s="33" t="inlineStr"/>
+      <c r="K71" s="33" t="inlineStr"/>
+      <c r="L71" s="23" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="M71" s="33" t="inlineStr"/>
+      <c r="N71" s="33" t="inlineStr"/>
+      <c r="O71" s="33" t="inlineStr"/>
+      <c r="P71" s="33" t="inlineStr"/>
+      <c r="Q71" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R71" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S71" s="35" t="inlineStr"/>
+      <c r="T71" s="25" t="inlineStr"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="32" t="inlineStr">
+        <is>
+          <t>offices-to-go-newland-u-shaped-suites-nlp406</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="inlineStr">
+        <is>
+          <t>Offices to Go ® newland™ u-shaped suites — NLP406</t>
+        </is>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>2369.99</t>
+        </is>
+      </c>
+      <c r="F72" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G72" s="33" t="inlineStr"/>
+      <c r="H72" s="23" t="inlineStr">
+        <is>
+          <t>NLP406</t>
+        </is>
+      </c>
+      <c r="I72" s="33" t="inlineStr"/>
+      <c r="J72" s="33" t="inlineStr"/>
+      <c r="K72" s="33" t="inlineStr"/>
+      <c r="L72" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M72" s="33" t="inlineStr"/>
+      <c r="N72" s="23" t="inlineStr">
+        <is>
+          <t>Offices to Go® Newland™ U-Shaped Suites with Height Adjustable Desk Features L-sh</t>
+        </is>
+      </c>
+      <c r="O72" s="33" t="inlineStr"/>
+      <c r="P72" s="33" t="inlineStr"/>
+      <c r="Q72" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R72" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S72" s="35" t="inlineStr"/>
+      <c r="T72" s="25" t="inlineStr"/>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>sit-stand-adjustable-desk-riser-32-wide</t>
+        </is>
+      </c>
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>Sit stand adjustable desk riser 32" wide — 32"</t>
+        </is>
+      </c>
+      <c r="C73" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D73" s="27" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E73" s="27" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F73" s="33" t="inlineStr"/>
+      <c r="G73" s="23" t="inlineStr">
+        <is>
+          <t>Sit stand adjustable desk riser</t>
+        </is>
+      </c>
+      <c r="H73" s="33" t="inlineStr"/>
+      <c r="I73" s="33" t="inlineStr"/>
+      <c r="J73" s="23" t="inlineStr">
+        <is>
+          <t>35.27 lbs</t>
+        </is>
+      </c>
+      <c r="K73" s="33" t="inlineStr"/>
+      <c r="L73" s="33" t="inlineStr"/>
+      <c r="M73" s="33" t="inlineStr"/>
+      <c r="N73" s="23" t="inlineStr">
+        <is>
+          <t>EVR 20% greater Enhanced Vertical Range - rises up to 16; Includes full size 24” x 11; Gas shocks lift up to 30 lbs</t>
+        </is>
+      </c>
+      <c r="O73" s="33" t="inlineStr"/>
+      <c r="P73" s="33" t="inlineStr"/>
+      <c r="Q73" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R73" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S73" s="35" t="inlineStr"/>
+      <c r="T73" s="25" t="inlineStr"/>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="32" t="inlineStr">
+        <is>
+          <t>sit-stand-fellowes-lotus-dual-arm-not-included</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="inlineStr">
+        <is>
+          <t>Sit stand fellowes lotus (dual arm not included)</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E74" s="32" t="inlineStr">
+        <is>
+          <t>672.99</t>
+        </is>
+      </c>
+      <c r="F74" s="33" t="inlineStr"/>
+      <c r="G74" s="33" t="inlineStr"/>
+      <c r="H74" s="33" t="inlineStr"/>
+      <c r="I74" s="33" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr"/>
+      <c r="K74" s="33" t="inlineStr"/>
+      <c r="L74" s="33" t="inlineStr"/>
+      <c r="M74" s="33" t="inlineStr"/>
+      <c r="N74" s="23" t="inlineStr">
+        <is>
+          <t>The Lotus™ Sit-Stand Workstation makes it effortless to add movement to your work</t>
+        </is>
+      </c>
+      <c r="O74" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA</t>
+        </is>
+      </c>
+      <c r="P74" s="33" t="inlineStr"/>
+      <c r="Q74" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R74" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S74" s="35" t="inlineStr"/>
+      <c r="T74" s="25" t="inlineStr"/>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>u-shaped-suite-with-rectangular-island</t>
+        </is>
+      </c>
+      <c r="B75" s="27" t="inlineStr">
+        <is>
+          <t>"u" shaped suite with rectangular island — NLP324</t>
+        </is>
+      </c>
+      <c r="C75" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D75" s="27" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E75" s="27" t="inlineStr">
+        <is>
+          <t>1956.67</t>
+        </is>
+      </c>
+      <c r="F75" s="33" t="inlineStr"/>
+      <c r="G75" s="33" t="inlineStr"/>
+      <c r="H75" s="23" t="inlineStr">
+        <is>
+          <t>NLP324</t>
+        </is>
+      </c>
+      <c r="I75" s="33" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr"/>
+      <c r="K75" s="33" t="inlineStr"/>
+      <c r="L75" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M75" s="33" t="inlineStr"/>
+      <c r="N75" s="23" t="inlineStr">
+        <is>
+          <t>NLP121 "U" SHAPED SUITE WITH RECTANGULAR ISLAND - 72"W X 102"D Simple and modular</t>
+        </is>
+      </c>
+      <c r="O75" s="33" t="inlineStr"/>
+      <c r="P75" s="33" t="inlineStr"/>
+      <c r="Q75" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R75" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S75" s="35" t="inlineStr"/>
+      <c r="T75" s="25" t="inlineStr"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="32" t="inlineStr">
+        <is>
+          <t>zira-workstation-3-person</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="inlineStr">
+        <is>
+          <t>Zira workstation 3 person</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E76" s="32" t="inlineStr">
+        <is>
+          <t>8779.99</t>
+        </is>
+      </c>
+      <c r="F76" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G76" s="23" t="inlineStr">
+        <is>
+          <t>Zira workstation</t>
+        </is>
+      </c>
+      <c r="H76" s="33" t="inlineStr"/>
+      <c r="I76" s="33" t="inlineStr"/>
+      <c r="J76" s="33" t="inlineStr"/>
+      <c r="K76" s="33" t="inlineStr"/>
+      <c r="L76" s="33" t="inlineStr"/>
+      <c r="M76" s="33" t="inlineStr"/>
+      <c r="N76" s="23" t="inlineStr">
+        <is>
+          <t>Floor Space: 6' x 24' Includes all product shown</t>
+        </is>
+      </c>
+      <c r="O76" s="33" t="inlineStr"/>
+      <c r="P76" s="33" t="inlineStr"/>
+      <c r="Q76" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R76" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S76" s="35" t="inlineStr"/>
+      <c r="T76" s="25" t="inlineStr"/>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="27" t="inlineStr">
+        <is>
+          <t>2-drawer-legal-width-vertical-file</t>
+        </is>
+      </c>
+      <c r="B77" s="27" t="inlineStr">
+        <is>
+          <t>2 drawer legal width vertical file — 2 drawer</t>
+        </is>
+      </c>
+      <c r="C77" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D77" s="27" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E77" s="27" t="inlineStr">
+        <is>
+          <t>329.99</t>
+        </is>
+      </c>
+      <c r="F77" s="33" t="inlineStr"/>
+      <c r="G77" s="33" t="inlineStr"/>
+      <c r="H77" s="33" t="inlineStr"/>
+      <c r="I77" s="23" t="inlineStr">
+        <is>
+          <t>18.15 x 25 x 29"</t>
+        </is>
+      </c>
+      <c r="J77" s="23" t="inlineStr">
+        <is>
+          <t>67 lbs</t>
+        </is>
+      </c>
+      <c r="K77" s="33" t="inlineStr"/>
+      <c r="L77" s="33" t="inlineStr"/>
+      <c r="M77" s="33" t="inlineStr"/>
+      <c r="N77" s="33" t="inlineStr"/>
+      <c r="O77" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA; ANSI</t>
+        </is>
+      </c>
+      <c r="P77" s="33" t="inlineStr"/>
+      <c r="Q77" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R77" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S77" s="35" t="inlineStr"/>
+      <c r="T77" s="25" t="inlineStr"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="32" t="inlineStr">
+        <is>
+          <t>bookcase</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="inlineStr">
+        <is>
+          <t>Bookcase</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E78" s="32" t="inlineStr">
+        <is>
+          <t>269.99</t>
+        </is>
+      </c>
+      <c r="F78" s="33" t="inlineStr"/>
+      <c r="G78" s="33" t="inlineStr"/>
+      <c r="H78" s="33" t="inlineStr"/>
+      <c r="I78" s="33" t="inlineStr"/>
+      <c r="J78" s="33" t="inlineStr"/>
+      <c r="K78" s="33" t="inlineStr"/>
+      <c r="L78" s="33" t="inlineStr"/>
+      <c r="M78" s="33" t="inlineStr"/>
+      <c r="N78" s="23" t="inlineStr">
+        <is>
+          <t>Features2 fixed shelf 1 adjustable shelf 1" construction Optional bookcase door s</t>
+        </is>
+      </c>
+      <c r="O78" s="33" t="inlineStr"/>
+      <c r="P78" s="33" t="inlineStr"/>
+      <c r="Q78" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R78" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S78" s="35" t="inlineStr"/>
+      <c r="T78" s="25" t="inlineStr"/>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="27" t="inlineStr">
+        <is>
+          <t>bookcase-1-shelf-32-wide-x-72-high</t>
+        </is>
+      </c>
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>Bookcase - 1" shelf 32" wide x 72" high — 72"</t>
+        </is>
+      </c>
+      <c r="C79" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D79" s="27" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E79" s="27" t="inlineStr">
+        <is>
+          <t>380.54</t>
+        </is>
+      </c>
+      <c r="F79" s="33" t="inlineStr"/>
+      <c r="G79" s="23" t="inlineStr">
+        <is>
+          <t>Bookcase</t>
+        </is>
+      </c>
+      <c r="H79" s="33" t="inlineStr"/>
+      <c r="I79" s="33" t="inlineStr"/>
+      <c r="J79" s="33" t="inlineStr"/>
+      <c r="K79" s="33" t="inlineStr"/>
+      <c r="L79" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M79" s="33" t="inlineStr"/>
+      <c r="N79" s="23" t="inlineStr">
+        <is>
+          <t>Bookcase Attractively designed well-suited book storage solution An excellent cho</t>
+        </is>
+      </c>
+      <c r="O79" s="33" t="inlineStr"/>
+      <c r="P79" s="33" t="inlineStr"/>
+      <c r="Q79" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R79" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S79" s="35" t="inlineStr"/>
+      <c r="T79" s="25" t="inlineStr"/>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="32" t="inlineStr">
+        <is>
+          <t>bookcase-with-closed-lower-storage</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="inlineStr">
+        <is>
+          <t>Bookcase with closed lower storage</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E80" s="32" t="inlineStr">
+        <is>
+          <t>449.99</t>
+        </is>
+      </c>
+      <c r="F80" s="33" t="inlineStr"/>
+      <c r="G80" s="33" t="inlineStr"/>
+      <c r="H80" s="33" t="inlineStr"/>
+      <c r="I80" s="33" t="inlineStr"/>
+      <c r="J80" s="33" t="inlineStr"/>
+      <c r="K80" s="33" t="inlineStr"/>
+      <c r="L80" s="33" t="inlineStr"/>
+      <c r="M80" s="33" t="inlineStr"/>
+      <c r="N80" s="23" t="inlineStr">
+        <is>
+          <t>Made in Canada 10 Size options Lock included Arrives Assembled Many colour choice</t>
+        </is>
+      </c>
+      <c r="O80" s="33" t="inlineStr"/>
+      <c r="P80" s="33" t="inlineStr"/>
+      <c r="Q80" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R80" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S80" s="35" t="inlineStr"/>
+      <c r="T80" s="25" t="inlineStr"/>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="27" t="inlineStr">
+        <is>
+          <t>heartwood-mobile-pedestal-bf</t>
+        </is>
+      </c>
+      <c r="B81" s="27" t="inlineStr">
+        <is>
+          <t>Heartwood mobile pedestal bf</t>
+        </is>
+      </c>
+      <c r="C81" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D81" s="27" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E81" s="27" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F81" s="23" t="inlineStr">
+        <is>
+          <t>Heartwood Manufacturing</t>
+        </is>
+      </c>
+      <c r="G81" s="33" t="inlineStr"/>
+      <c r="H81" s="33" t="inlineStr"/>
+      <c r="I81" s="33" t="inlineStr"/>
+      <c r="J81" s="33" t="inlineStr"/>
+      <c r="K81" s="33" t="inlineStr"/>
+      <c r="L81" s="33" t="inlineStr"/>
+      <c r="M81" s="33" t="inlineStr"/>
+      <c r="N81" s="23" t="inlineStr">
+        <is>
+          <t>Features full carton box/file all drawers lock includes pencil tray heavy duty ca</t>
+        </is>
+      </c>
+      <c r="O81" s="33" t="inlineStr"/>
+      <c r="P81" s="33" t="inlineStr"/>
+      <c r="Q81" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R81" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S81" s="35" t="inlineStr"/>
+      <c r="T81" s="25" t="inlineStr"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="32" t="inlineStr">
+        <is>
+          <t>kensington-ac12-security-charging-cabinet</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>Kensington AC12 security charging cabinet</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E82" s="32" t="inlineStr">
+        <is>
+          <t>1725.89</t>
+        </is>
+      </c>
+      <c r="F82" s="33" t="inlineStr"/>
+      <c r="G82" s="33" t="inlineStr"/>
+      <c r="H82" s="33" t="inlineStr"/>
+      <c r="I82" s="33" t="inlineStr"/>
+      <c r="J82" s="33" t="inlineStr"/>
+      <c r="K82" s="33" t="inlineStr"/>
+      <c r="L82" s="33" t="inlineStr"/>
+      <c r="M82" s="33" t="inlineStr"/>
+      <c r="N82" s="23" t="inlineStr">
+        <is>
+          <t>Store, charge and secure devices overnight; Universal Device - 4 Casters - x 16; Black - For 12 Devices</t>
+        </is>
+      </c>
+      <c r="O82" s="33" t="inlineStr"/>
+      <c r="P82" s="33" t="inlineStr"/>
+      <c r="Q82" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R82" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S82" s="35" t="inlineStr"/>
+      <c r="T82" s="25" t="inlineStr"/>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="27" t="inlineStr">
+        <is>
+          <t>large-fire-water-safe-13-x-16-x-19-black-2</t>
+        </is>
+      </c>
+      <c r="B83" s="27" t="inlineStr">
+        <is>
+          <t>Large fire/water safe 13" x 16" x 19" - black — 13" x 16" x 19"</t>
+        </is>
+      </c>
+      <c r="C83" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D83" s="27" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E83" s="27" t="inlineStr">
+        <is>
+          <t>369.89</t>
+        </is>
+      </c>
+      <c r="F83" s="33" t="inlineStr"/>
+      <c r="G83" s="33" t="inlineStr"/>
+      <c r="H83" s="33" t="inlineStr"/>
+      <c r="I83" s="33" t="inlineStr"/>
+      <c r="J83" s="33" t="inlineStr"/>
+      <c r="K83" s="33" t="inlineStr"/>
+      <c r="L83" s="33" t="inlineStr"/>
+      <c r="M83" s="33" t="inlineStr"/>
+      <c r="N83" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category Safes Manufacturer Sentry Group Manufacturer Ref SFW082DTB Brand Sentry </t>
+        </is>
+      </c>
+      <c r="O83" s="33" t="inlineStr"/>
+      <c r="P83" s="33" t="inlineStr"/>
+      <c r="Q83" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R83" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S83" s="35" t="inlineStr"/>
+      <c r="T83" s="25" t="inlineStr"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="32" t="inlineStr">
+        <is>
+          <t>mobile-drawer-unit-with-locks-inv-mpuf</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="inlineStr">
+        <is>
+          <t>Mobile drawer unit with locks inv-mpuf</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E84" s="32" t="inlineStr">
+        <is>
+          <t>499.99</t>
+        </is>
+      </c>
+      <c r="F84" s="33" t="inlineStr"/>
+      <c r="G84" s="33" t="inlineStr"/>
+      <c r="H84" s="33" t="inlineStr"/>
+      <c r="I84" s="33" t="inlineStr"/>
+      <c r="J84" s="33" t="inlineStr"/>
+      <c r="K84" s="33" t="inlineStr"/>
+      <c r="L84" s="33" t="inlineStr"/>
+      <c r="M84" s="33" t="inlineStr"/>
+      <c r="N84" s="23" t="inlineStr">
+        <is>
+          <t>MOBILE PEDESTAL - FULL CARTON BOX / BOX / FILE</t>
+        </is>
+      </c>
+      <c r="O84" s="33" t="inlineStr"/>
+      <c r="P84" s="33" t="inlineStr"/>
+      <c r="Q84" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R84" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S84" s="35" t="inlineStr"/>
+      <c r="T84" s="25" t="inlineStr"/>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="27" t="inlineStr">
+        <is>
+          <t>newland-16w-box-box-file-mobile-pedestal-nlmp23bbf</t>
+        </is>
+      </c>
+      <c r="B85" s="27" t="inlineStr">
+        <is>
+          <t>Newland | 16"w box/box/file mobile pedestal — NLMP23BBF</t>
+        </is>
+      </c>
+      <c r="C85" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D85" s="27" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E85" s="27" t="inlineStr">
+        <is>
+          <t>589.99</t>
+        </is>
+      </c>
+      <c r="F85" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G85" s="23" t="inlineStr">
+        <is>
+          <t>Newland</t>
+        </is>
+      </c>
+      <c r="H85" s="23" t="inlineStr">
+        <is>
+          <t>NLMP23BBF</t>
+        </is>
+      </c>
+      <c r="I85" s="33" t="inlineStr"/>
+      <c r="J85" s="33" t="inlineStr"/>
+      <c r="K85" s="33" t="inlineStr"/>
+      <c r="L85" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M85" s="33" t="inlineStr"/>
+      <c r="N85" s="23" t="inlineStr">
+        <is>
+          <t>NLMP23BBF Newland | 16"W Box/Box/File Mobile Pedestal Newland - simple and modula</t>
+        </is>
+      </c>
+      <c r="O85" s="33" t="inlineStr"/>
+      <c r="P85" s="33" t="inlineStr"/>
+      <c r="Q85" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R85" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S85" s="35" t="inlineStr"/>
+      <c r="T85" s="25" t="inlineStr"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="32" t="inlineStr">
+        <is>
+          <t>newland-bookcases-assembled</t>
+        </is>
+      </c>
+      <c r="B86" s="32" t="inlineStr">
+        <is>
+          <t>Newland bookcases (assembled)</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D86" s="32" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E86" s="32" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F86" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G86" s="33" t="inlineStr"/>
+      <c r="H86" s="33" t="inlineStr"/>
+      <c r="I86" s="33" t="inlineStr"/>
+      <c r="J86" s="33" t="inlineStr"/>
+      <c r="K86" s="33" t="inlineStr"/>
+      <c r="L86" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M86" s="33" t="inlineStr"/>
+      <c r="N86" s="23" t="inlineStr">
+        <is>
+          <t>Thermally fused laminate One fixed shelf, 3 adjustable shelves 1" thick top and e</t>
+        </is>
+      </c>
+      <c r="O86" s="33" t="inlineStr"/>
+      <c r="P86" s="33" t="inlineStr"/>
+      <c r="Q86" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R86" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S86" s="35" t="inlineStr"/>
+      <c r="T86" s="25" t="inlineStr"/>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="27" t="inlineStr">
+        <is>
+          <t>pedestal-file-file-with-or-without-wheels</t>
+        </is>
+      </c>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>Pedestal - file/file (with or without wheels)</t>
+        </is>
+      </c>
+      <c r="C87" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D87" s="27" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E87" s="27" t="inlineStr">
+        <is>
+          <t>419.99</t>
+        </is>
+      </c>
+      <c r="F87" s="33" t="inlineStr"/>
+      <c r="G87" s="33" t="inlineStr"/>
+      <c r="H87" s="33" t="inlineStr"/>
+      <c r="I87" s="33" t="inlineStr"/>
+      <c r="J87" s="33" t="inlineStr"/>
+      <c r="K87" s="33" t="inlineStr"/>
+      <c r="L87" s="33" t="inlineStr"/>
+      <c r="M87" s="33" t="inlineStr"/>
+      <c r="N87" s="23" t="inlineStr">
+        <is>
+          <t>To be used under a worksurface</t>
+        </is>
+      </c>
+      <c r="O87" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA; ANSI</t>
+        </is>
+      </c>
+      <c r="P87" s="33" t="inlineStr"/>
+      <c r="Q87" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R87" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S87" s="35" t="inlineStr"/>
+      <c r="T87" s="25" t="inlineStr"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="32" t="inlineStr">
+        <is>
+          <t>sentry-safe-security-safe-with-electronic-lock-4</t>
+        </is>
+      </c>
+      <c r="B88" s="32" t="inlineStr">
+        <is>
+          <t>Sentry safe security safe with electronic lock</t>
+        </is>
+      </c>
+      <c r="C88" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D88" s="32" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E88" s="32" t="inlineStr">
+        <is>
+          <t>359.99</t>
+        </is>
+      </c>
+      <c r="F88" s="33" t="inlineStr"/>
+      <c r="G88" s="33" t="inlineStr"/>
+      <c r="H88" s="33" t="inlineStr"/>
+      <c r="I88" s="33" t="inlineStr"/>
+      <c r="J88" s="33" t="inlineStr"/>
+      <c r="K88" s="33" t="inlineStr"/>
+      <c r="L88" s="23" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="M88" s="33" t="inlineStr"/>
+      <c r="N88" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Category Safes Manufacturer Sentry Group Manufacturer Ref X125 Brand Sentry Safe </t>
+        </is>
+      </c>
+      <c r="O88" s="33" t="inlineStr"/>
+      <c r="P88" s="33" t="inlineStr"/>
+      <c r="Q88" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R88" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S88" s="35" t="inlineStr"/>
+      <c r="T88" s="25" t="inlineStr"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="27" t="inlineStr">
+        <is>
+          <t>wardrobe-storage-cabinet-htwlevsr7218</t>
+        </is>
+      </c>
+      <c r="B89" s="27" t="inlineStr">
+        <is>
+          <t>Wardrobe / storage cabinet — HTWLEVSR7218</t>
+        </is>
+      </c>
+      <c r="C89" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D89" s="27" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E89" s="27" t="inlineStr">
+        <is>
+          <t>629.99</t>
+        </is>
+      </c>
+      <c r="F89" s="33" t="inlineStr"/>
+      <c r="G89" s="33" t="inlineStr"/>
+      <c r="H89" s="23" t="inlineStr">
+        <is>
+          <t>HTWLEVSR7218</t>
+        </is>
+      </c>
+      <c r="I89" s="23" t="inlineStr">
+        <is>
+          <t>17.75 x 23.75 x 71.5"</t>
+        </is>
+      </c>
+      <c r="J89" s="33" t="inlineStr"/>
+      <c r="K89" s="33" t="inlineStr"/>
+      <c r="L89" s="33" t="inlineStr"/>
+      <c r="M89" s="33" t="inlineStr"/>
+      <c r="N89" s="23" t="inlineStr">
+        <is>
+          <t>Wardrobe / Storage Cabinet 17</t>
+        </is>
+      </c>
+      <c r="O89" s="33" t="inlineStr"/>
+      <c r="P89" s="33" t="inlineStr"/>
+      <c r="Q89" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R89" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S89" s="35" t="inlineStr"/>
+      <c r="T89" s="25" t="inlineStr"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="32" t="inlineStr">
+        <is>
+          <t>coffee-table-1</t>
+        </is>
+      </c>
+      <c r="B90" s="32" t="inlineStr">
+        <is>
+          <t>Coffee table</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D90" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E90" s="32" t="inlineStr">
+        <is>
+          <t>359.99</t>
+        </is>
+      </c>
+      <c r="F90" s="33" t="inlineStr"/>
+      <c r="G90" s="33" t="inlineStr"/>
+      <c r="H90" s="33" t="inlineStr"/>
+      <c r="I90" s="33" t="inlineStr"/>
+      <c r="J90" s="33" t="inlineStr"/>
+      <c r="K90" s="33" t="inlineStr"/>
+      <c r="L90" s="23" t="inlineStr">
+        <is>
+          <t>steel, laminate</t>
+        </is>
+      </c>
+      <c r="M90" s="33" t="inlineStr"/>
+      <c r="N90" s="23" t="inlineStr">
+        <is>
+          <t>Made in Canada 1" Laminated Top Steel Legs</t>
+        </is>
+      </c>
+      <c r="O90" s="33" t="inlineStr"/>
+      <c r="P90" s="33" t="inlineStr"/>
+      <c r="Q90" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R90" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S90" s="35" t="inlineStr"/>
+      <c r="T90" s="25" t="inlineStr"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="27" t="inlineStr">
+        <is>
+          <t>folding-table-24-x-48-1</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>Folding table — 24" x 48"</t>
+        </is>
+      </c>
+      <c r="C91" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D91" s="27" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E91" s="27" t="inlineStr">
+        <is>
+          <t>125.29</t>
+        </is>
+      </c>
+      <c r="F91" s="33" t="inlineStr"/>
+      <c r="G91" s="23" t="inlineStr">
+        <is>
+          <t>Folding table</t>
+        </is>
+      </c>
+      <c r="H91" s="33" t="inlineStr"/>
+      <c r="I91" s="33" t="inlineStr"/>
+      <c r="J91" s="33" t="inlineStr"/>
+      <c r="K91" s="33" t="inlineStr"/>
+      <c r="L91" s="23" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="M91" s="33" t="inlineStr"/>
+      <c r="N91" s="23" t="inlineStr">
+        <is>
+          <t>Specifications UNSPSC Code : 56101519 Application/usage : Indoor Assembly Require</t>
+        </is>
+      </c>
+      <c r="O91" s="33" t="inlineStr"/>
+      <c r="P91" s="33" t="inlineStr"/>
+      <c r="Q91" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R91" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S91" s="35" t="inlineStr"/>
+      <c r="T91" s="25" t="inlineStr"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="32" t="inlineStr">
+        <is>
+          <t>folding-table-36-bt36-resin</t>
+        </is>
+      </c>
+      <c r="B92" s="32" t="inlineStr">
+        <is>
+          <t>Folding table 36" BT36 resin — 36"</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D92" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E92" s="32" t="inlineStr">
+        <is>
+          <t>149.99</t>
+        </is>
+      </c>
+      <c r="F92" s="33" t="inlineStr"/>
+      <c r="G92" s="23" t="inlineStr">
+        <is>
+          <t>Folding table</t>
+        </is>
+      </c>
+      <c r="H92" s="33" t="inlineStr"/>
+      <c r="I92" s="33" t="inlineStr"/>
+      <c r="J92" s="33" t="inlineStr"/>
+      <c r="K92" s="33" t="inlineStr"/>
+      <c r="L92" s="23" t="inlineStr">
+        <is>
+          <t>steel, powder coat</t>
+        </is>
+      </c>
+      <c r="M92" s="33" t="inlineStr"/>
+      <c r="N92" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEATURES SPECS 36” Square Resin Table ; Durable construction ; Light weight sleek design </t>
+        </is>
+      </c>
+      <c r="O92" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA</t>
+        </is>
+      </c>
+      <c r="P92" s="33" t="inlineStr"/>
+      <c r="Q92" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R92" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S92" s="35" t="inlineStr"/>
+      <c r="T92" s="25" t="inlineStr"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="27" t="inlineStr">
+        <is>
+          <t>freefit-benching-height-adjustable-176w-x-62-5d-ffhab506-2</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>Freefit benching height adjustable 176"w x 62.5"d (ffhab506) — FFHAB506</t>
+        </is>
+      </c>
+      <c r="C93" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D93" s="27" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E93" s="27" t="inlineStr">
+        <is>
+          <t>13333.0</t>
+        </is>
+      </c>
+      <c r="F93" s="33" t="inlineStr"/>
+      <c r="G93" s="23" t="inlineStr">
+        <is>
+          <t>Freefit benching height adjustable</t>
+        </is>
+      </c>
+      <c r="H93" s="23" t="inlineStr">
+        <is>
+          <t>FFHAB506</t>
+        </is>
+      </c>
+      <c r="I93" s="33" t="inlineStr"/>
+      <c r="J93" s="33" t="inlineStr"/>
+      <c r="K93" s="33" t="inlineStr"/>
+      <c r="L93" s="33" t="inlineStr"/>
+      <c r="M93" s="33" t="inlineStr"/>
+      <c r="N93" s="23" t="inlineStr">
+        <is>
+          <t>FreeFit height adjustable tables support healthier spaces</t>
+        </is>
+      </c>
+      <c r="O93" s="33" t="inlineStr"/>
+      <c r="P93" s="33" t="inlineStr"/>
+      <c r="Q93" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R93" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S93" s="35" t="inlineStr"/>
+      <c r="T93" s="25" t="inlineStr"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="32" t="inlineStr">
+        <is>
+          <t>hdl-5-resin-folding-table-granite-rectangle-dove-white-pebble-top-powder-coated-base-60-table-top-length-x-30-table-top-width-29-height-1</t>
+        </is>
+      </c>
+      <c r="B94" s="32" t="inlineStr">
+        <is>
+          <t>Hdl 5' resin folding table - granite rectangle, dove white pebble top - powder coated base - 60" table top length x 30" table top width - 29" height — 29"</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D94" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E94" s="32" t="inlineStr">
+        <is>
+          <t>143.87</t>
+        </is>
+      </c>
+      <c r="F94" s="33" t="inlineStr"/>
+      <c r="G94" s="23" t="inlineStr">
+        <is>
+          <t>Hdl</t>
+        </is>
+      </c>
+      <c r="H94" s="33" t="inlineStr"/>
+      <c r="I94" s="33" t="inlineStr"/>
+      <c r="J94" s="33" t="inlineStr"/>
+      <c r="K94" s="33" t="inlineStr"/>
+      <c r="L94" s="23" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="M94" s="33" t="inlineStr"/>
+      <c r="N94" s="23" t="inlineStr">
+        <is>
+          <t>Weatherproof design allows safe use both indoors and outdoors High-impact, polyet</t>
+        </is>
+      </c>
+      <c r="O94" s="33" t="inlineStr"/>
+      <c r="P94" s="33" t="inlineStr"/>
+      <c r="Q94" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R94" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S94" s="35" t="inlineStr"/>
+      <c r="T94" s="25" t="inlineStr"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
+        <is>
+          <t>management-u-shaped-suite-with-3-stage-height-adjustable-table-nlp410</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>Management "u" shaped suite with 3-stage height adjustable table — NLP410</t>
+        </is>
+      </c>
+      <c r="C95" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D95" s="27" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E95" s="27" t="inlineStr">
+        <is>
+          <t>2769.99</t>
+        </is>
+      </c>
+      <c r="F95" s="33" t="inlineStr"/>
+      <c r="G95" s="33" t="inlineStr"/>
+      <c r="H95" s="23" t="inlineStr">
+        <is>
+          <t>NLP410</t>
+        </is>
+      </c>
+      <c r="I95" s="33" t="inlineStr"/>
+      <c r="J95" s="33" t="inlineStr"/>
+      <c r="K95" s="33" t="inlineStr"/>
+      <c r="L95" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M95" s="33" t="inlineStr"/>
+      <c r="N95" s="23" t="inlineStr">
+        <is>
+          <t>NLP410 Newland | Management "U" Shaped Suite with 3-Stage Height Adjustable Table</t>
+        </is>
+      </c>
+      <c r="O95" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA; Greenguard; ANSI</t>
+        </is>
+      </c>
+      <c r="P95" s="23" t="inlineStr">
+        <is>
+          <t>Lifetime warranty</t>
+        </is>
+      </c>
+      <c r="Q95" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R95" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S95" s="35" t="inlineStr"/>
+      <c r="T95" s="25" t="inlineStr"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="32" t="inlineStr">
+        <is>
+          <t>offices-to-go-ionic-table-36-x-36-x-29-material-metal-base-finish-absolute-acajou-black-base-sandtex-1</t>
+        </is>
+      </c>
+      <c r="B96" s="32" t="inlineStr">
+        <is>
+          <t>Offices to Go Ionic table - 36" x 36" x 29" - material: metal base - finish: absolute acajou, black base, sandtex — 36" x 36" x 29"</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D96" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E96" s="32" t="inlineStr">
+        <is>
+          <t>379.99</t>
+        </is>
+      </c>
+      <c r="F96" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G96" s="23" t="inlineStr">
+        <is>
+          <t>Offices to Go Ionic table</t>
+        </is>
+      </c>
+      <c r="H96" s="33" t="inlineStr"/>
+      <c r="I96" s="23" t="inlineStr">
+        <is>
+          <t>36 x 36 x 29"</t>
+        </is>
+      </c>
+      <c r="J96" s="33" t="inlineStr"/>
+      <c r="K96" s="33" t="inlineStr"/>
+      <c r="L96" s="23" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="M96" s="33" t="inlineStr"/>
+      <c r="N96" s="23" t="inlineStr">
+        <is>
+          <t>Category Cafeteria &amp; Breakroom Tables Manufacturer Global Upholstery Co</t>
+        </is>
+      </c>
+      <c r="O96" s="33" t="inlineStr"/>
+      <c r="P96" s="33" t="inlineStr"/>
+      <c r="Q96" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R96" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S96" s="35" t="inlineStr"/>
+      <c r="T96" s="25" t="inlineStr"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="27" t="inlineStr">
+        <is>
+          <t>round-table-42</t>
+        </is>
+      </c>
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>Round table — 42</t>
+        </is>
+      </c>
+      <c r="C97" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D97" s="27" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E97" s="27" t="inlineStr">
+        <is>
+          <t>449.0</t>
+        </is>
+      </c>
+      <c r="F97" s="33" t="inlineStr"/>
+      <c r="G97" s="23" t="inlineStr">
+        <is>
+          <t>Round table</t>
+        </is>
+      </c>
+      <c r="H97" s="33" t="inlineStr"/>
+      <c r="I97" s="33" t="inlineStr"/>
+      <c r="J97" s="33" t="inlineStr"/>
+      <c r="K97" s="33" t="inlineStr"/>
+      <c r="L97" s="33" t="inlineStr"/>
+      <c r="M97" s="33" t="inlineStr"/>
+      <c r="N97" s="23" t="inlineStr">
+        <is>
+          <t>Round table with an X-Base Available in 8 colours 1" Thick top and base 42" Round</t>
+        </is>
+      </c>
+      <c r="O97" s="33" t="inlineStr"/>
+      <c r="P97" s="33" t="inlineStr"/>
+      <c r="Q97" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R97" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S97" s="35" t="inlineStr"/>
+      <c r="T97" s="25" t="inlineStr"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="32" t="inlineStr">
+        <is>
+          <t>zira-conference-table-9-sizes</t>
+        </is>
+      </c>
+      <c r="B98" s="32" t="inlineStr">
+        <is>
+          <t>Zira conference table — 9 sizes</t>
+        </is>
+      </c>
+      <c r="C98" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D98" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E98" s="32" t="inlineStr">
+        <is>
+          <t>2499.0</t>
+        </is>
+      </c>
+      <c r="F98" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G98" s="23" t="inlineStr">
+        <is>
+          <t>Zira conference table</t>
+        </is>
+      </c>
+      <c r="H98" s="33" t="inlineStr"/>
+      <c r="I98" s="33" t="inlineStr"/>
+      <c r="J98" s="33" t="inlineStr"/>
+      <c r="K98" s="33" t="inlineStr"/>
+      <c r="L98" s="33" t="inlineStr"/>
+      <c r="M98" s="33" t="inlineStr"/>
+      <c r="N98" s="23" t="inlineStr">
+        <is>
+          <t>Item Code: Conference Table is a perfect addition to an office where style, comfo</t>
+        </is>
+      </c>
+      <c r="O98" s="33" t="inlineStr"/>
+      <c r="P98" s="33" t="inlineStr"/>
+      <c r="Q98" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R98" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S98" s="35" t="inlineStr"/>
+      <c r="T98" s="25" t="inlineStr"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="27" t="inlineStr">
+        <is>
+          <t>installation475</t>
+        </is>
+      </c>
+      <c r="B99" s="27" t="inlineStr">
+        <is>
+          <t>Installation475</t>
+        </is>
+      </c>
+      <c r="C99" s="27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D99" s="27" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E99" s="27" t="inlineStr">
+        <is>
+          <t>475.0</t>
+        </is>
+      </c>
+      <c r="F99" s="33" t="inlineStr"/>
+      <c r="G99" s="33" t="inlineStr"/>
+      <c r="H99" s="33" t="inlineStr"/>
+      <c r="I99" s="33" t="inlineStr"/>
+      <c r="J99" s="33" t="inlineStr"/>
+      <c r="K99" s="33" t="inlineStr"/>
+      <c r="L99" s="33" t="inlineStr"/>
+      <c r="M99" s="33" t="inlineStr"/>
+      <c r="N99" s="23" t="inlineStr">
+        <is>
+          <t>Price includes Delivery &amp; Installation</t>
+        </is>
+      </c>
+      <c r="O99" s="33" t="inlineStr"/>
+      <c r="P99" s="33" t="inlineStr"/>
+      <c r="Q99" s="33" t="inlineStr"/>
+      <c r="R99" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S99" s="35" t="inlineStr"/>
+      <c r="T99" s="25" t="inlineStr"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="32" t="inlineStr">
+        <is>
+          <t>fellowes-array-ceiling-ac2-air-purifier</t>
+        </is>
+      </c>
+      <c r="B100" s="32" t="inlineStr">
+        <is>
+          <t>Fellowes array ceiling AC2 air purifier</t>
+        </is>
+      </c>
+      <c r="C100" s="32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D100" s="32" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E100" s="32" t="inlineStr">
+        <is>
+          <t>5800.0</t>
+        </is>
+      </c>
+      <c r="F100" s="33" t="inlineStr"/>
+      <c r="G100" s="33" t="inlineStr"/>
+      <c r="H100" s="33" t="inlineStr"/>
+      <c r="I100" s="33" t="inlineStr"/>
+      <c r="J100" s="33" t="inlineStr"/>
+      <c r="K100" s="33" t="inlineStr"/>
+      <c r="L100" s="33" t="inlineStr"/>
+      <c r="M100" s="33" t="inlineStr"/>
+      <c r="N100" s="23" t="inlineStr">
+        <is>
+          <t>Array® Ceiling AC2 Air Purifier Dual 3-in-1 filter is 99</t>
+        </is>
+      </c>
+      <c r="O100" s="33" t="inlineStr"/>
+      <c r="P100" s="23" t="inlineStr">
+        <is>
+          <t>5-year warranty</t>
+        </is>
+      </c>
+      <c r="Q100" s="33" t="inlineStr"/>
+      <c r="R100" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S100" s="35" t="inlineStr"/>
+      <c r="T100" s="25" t="inlineStr"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="27" t="inlineStr">
+        <is>
+          <t>fellowes-array-recess-ar-air-purifier-1</t>
+        </is>
+      </c>
+      <c r="B101" s="27" t="inlineStr">
+        <is>
+          <t>Fellowes array recess ar air purifier</t>
+        </is>
+      </c>
+      <c r="C101" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D101" s="27" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E101" s="27" t="inlineStr">
+        <is>
+          <t>3929.0</t>
+        </is>
+      </c>
+      <c r="F101" s="33" t="inlineStr"/>
+      <c r="G101" s="33" t="inlineStr"/>
+      <c r="H101" s="33" t="inlineStr"/>
+      <c r="I101" s="33" t="inlineStr"/>
+      <c r="J101" s="33" t="inlineStr"/>
+      <c r="K101" s="33" t="inlineStr"/>
+      <c r="L101" s="33" t="inlineStr"/>
+      <c r="M101" s="33" t="inlineStr"/>
+      <c r="N101" s="23" t="inlineStr">
+        <is>
+          <t>Fellowes 3-in-1 filter (prefilter, carbon and H13 True HEPA filtration) is 99</t>
+        </is>
+      </c>
+      <c r="O101" s="33" t="inlineStr"/>
+      <c r="P101" s="23" t="inlineStr">
+        <is>
+          <t>5-year warranty</t>
+        </is>
+      </c>
+      <c r="Q101" s="33" t="inlineStr"/>
+      <c r="R101" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S101" s="35" t="inlineStr"/>
+      <c r="T101" s="25" t="inlineStr"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="32" t="inlineStr">
+        <is>
+          <t>fellowes-array-wall-stand-air-purification</t>
+        </is>
+      </c>
+      <c r="B102" s="32" t="inlineStr">
+        <is>
+          <t>Fellowes array wall &amp; stand air purification</t>
+        </is>
+      </c>
+      <c r="C102" s="32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D102" s="32" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E102" s="32" t="inlineStr">
+        <is>
+          <t>3150.0</t>
+        </is>
+      </c>
+      <c r="F102" s="33" t="inlineStr"/>
+      <c r="G102" s="33" t="inlineStr"/>
+      <c r="H102" s="33" t="inlineStr"/>
+      <c r="I102" s="33" t="inlineStr"/>
+      <c r="J102" s="33" t="inlineStr"/>
+      <c r="K102" s="33" t="inlineStr"/>
+      <c r="L102" s="33" t="inlineStr"/>
+      <c r="M102" s="33" t="inlineStr"/>
+      <c r="N102" s="23" t="inlineStr">
+        <is>
+          <t>Array® Wall AW1 &amp; AW2 Air Purifiers 3-stage filtration is 99</t>
+        </is>
+      </c>
+      <c r="O102" s="33" t="inlineStr"/>
+      <c r="P102" s="23" t="inlineStr">
+        <is>
+          <t>5-year warranty</t>
+        </is>
+      </c>
+      <c r="Q102" s="33" t="inlineStr"/>
+      <c r="R102" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S102" s="35" t="inlineStr"/>
+      <c r="T102" s="25" t="inlineStr"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="27" t="inlineStr">
+        <is>
+          <t>fellowes-lotus-dual-monitor-arm-kit-2-display-s-supported27-arm-only-fel8042901</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>Fellowes lotus dual monitor arm kit - 2 display(s) supported27" (arm only) — FEL8042901</t>
+        </is>
+      </c>
+      <c r="C103" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D103" s="27" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E103" s="27" t="inlineStr">
+        <is>
+          <t>146.89</t>
+        </is>
+      </c>
+      <c r="F103" s="33" t="inlineStr"/>
+      <c r="G103" s="23" t="inlineStr">
+        <is>
+          <t>Fellowes lotus dual monitor arm kit</t>
+        </is>
+      </c>
+      <c r="H103" s="23" t="inlineStr">
+        <is>
+          <t>FEL8042901</t>
+        </is>
+      </c>
+      <c r="I103" s="33" t="inlineStr"/>
+      <c r="J103" s="33" t="inlineStr"/>
+      <c r="K103" s="33" t="inlineStr"/>
+      <c r="L103" s="33" t="inlineStr"/>
+      <c r="M103" s="33" t="inlineStr"/>
+      <c r="N103" s="23" t="inlineStr">
+        <is>
+          <t>Lotus™ Dual Monitor Arm Kit Easy to mount via grommet hole allowing for quick set</t>
+        </is>
+      </c>
+      <c r="O103" s="33" t="inlineStr"/>
+      <c r="P103" s="23" t="inlineStr">
+        <is>
+          <t>Limited Warranty</t>
+        </is>
+      </c>
+      <c r="Q103" s="33" t="inlineStr"/>
+      <c r="R103" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S103" s="35" t="inlineStr"/>
+      <c r="T103" s="25" t="inlineStr"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="32" t="inlineStr">
+        <is>
+          <t>otg-mobile-foot-kit-pack-of-2</t>
+        </is>
+      </c>
+      <c r="B104" s="32" t="inlineStr">
+        <is>
+          <t>Otg | mobile foot kit - pack of 2</t>
+        </is>
+      </c>
+      <c r="C104" s="32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D104" s="32" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E104" s="32" t="inlineStr">
+        <is>
+          <t>169.99</t>
+        </is>
+      </c>
+      <c r="F104" s="33" t="inlineStr"/>
+      <c r="G104" s="23" t="inlineStr">
+        <is>
+          <t>Otg</t>
+        </is>
+      </c>
+      <c r="H104" s="33" t="inlineStr"/>
+      <c r="I104" s="33" t="inlineStr"/>
+      <c r="J104" s="33" t="inlineStr"/>
+      <c r="K104" s="33" t="inlineStr"/>
+      <c r="L104" s="33" t="inlineStr"/>
+      <c r="M104" s="33" t="inlineStr"/>
+      <c r="N104" s="23" t="inlineStr">
+        <is>
+          <t>OTG | Mobile Foot Kit - Pack of 2 Sold &amp; Priced in pairs Use to create a mobile d</t>
+        </is>
+      </c>
+      <c r="O104" s="33" t="inlineStr"/>
+      <c r="P104" s="33" t="inlineStr"/>
+      <c r="Q104" s="33" t="inlineStr"/>
+      <c r="R104" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S104" s="35" t="inlineStr"/>
+      <c r="T104" s="25" t="inlineStr"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="27" t="inlineStr">
+        <is>
+          <t>otg-panels</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>Otg panels</t>
+        </is>
+      </c>
+      <c r="C105" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D105" s="27" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E105" s="27" t="inlineStr">
+        <is>
+          <t>439.99</t>
+        </is>
+      </c>
+      <c r="F105" s="33" t="inlineStr"/>
+      <c r="G105" s="33" t="inlineStr"/>
+      <c r="H105" s="33" t="inlineStr"/>
+      <c r="I105" s="33" t="inlineStr"/>
+      <c r="J105" s="33" t="inlineStr"/>
+      <c r="K105" s="33" t="inlineStr"/>
+      <c r="L105" s="23" t="inlineStr">
+        <is>
+          <t>fabric, aluminum, upholstered</t>
+        </is>
+      </c>
+      <c r="M105" s="33" t="inlineStr"/>
+      <c r="N105" s="23" t="inlineStr">
+        <is>
+          <t>OTG | Panel - Fabric Top and Bottom An innovative and economical tool for creatin</t>
+        </is>
+      </c>
+      <c r="O105" s="33" t="inlineStr"/>
+      <c r="P105" s="33" t="inlineStr"/>
+      <c r="Q105" s="33" t="inlineStr"/>
+      <c r="R105" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S105" s="35" t="inlineStr"/>
+      <c r="T105" s="25" t="inlineStr"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="32" t="inlineStr">
+        <is>
+          <t>otgma2-dual-monitor-arm</t>
+        </is>
+      </c>
+      <c r="B106" s="32" t="inlineStr">
+        <is>
+          <t>OTGMA2 dual monitor arm</t>
+        </is>
+      </c>
+      <c r="C106" s="32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D106" s="32" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E106" s="32" t="inlineStr">
+        <is>
+          <t>159.99</t>
+        </is>
+      </c>
+      <c r="F106" s="33" t="inlineStr"/>
+      <c r="G106" s="33" t="inlineStr"/>
+      <c r="H106" s="33" t="inlineStr"/>
+      <c r="I106" s="33" t="inlineStr"/>
+      <c r="J106" s="33" t="inlineStr"/>
+      <c r="K106" s="33" t="inlineStr"/>
+      <c r="L106" s="33" t="inlineStr"/>
+      <c r="M106" s="33" t="inlineStr"/>
+      <c r="N106" s="23" t="inlineStr">
+        <is>
+          <t>OTGMA2 Dual Monitor Arm can be used as single or double monitor arm height adjust</t>
+        </is>
+      </c>
+      <c r="O106" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA; ANSI</t>
+        </is>
+      </c>
+      <c r="P106" s="33" t="inlineStr"/>
+      <c r="Q106" s="33" t="inlineStr"/>
+      <c r="R106" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S106" s="35" t="inlineStr"/>
+      <c r="T106" s="25" t="inlineStr"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>rollamat-for-carpet-carpeted-floor-53-x-45-3</t>
+        </is>
+      </c>
+      <c r="B107" s="27" t="inlineStr">
+        <is>
+          <t>Rollamat for carpet - carpeted floor — 53" x 45"</t>
+        </is>
+      </c>
+      <c r="C107" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D107" s="27" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E107" s="27" t="inlineStr">
+        <is>
+          <t>306.0</t>
+        </is>
+      </c>
+      <c r="F107" s="33" t="inlineStr"/>
+      <c r="G107" s="23" t="inlineStr">
+        <is>
+          <t>Rollamat for carpet - carpeted floor</t>
+        </is>
+      </c>
+      <c r="H107" s="33" t="inlineStr"/>
+      <c r="I107" s="33" t="inlineStr"/>
+      <c r="J107" s="33" t="inlineStr"/>
+      <c r="K107" s="33" t="inlineStr"/>
+      <c r="L107" s="23" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="M107" s="33" t="inlineStr"/>
+      <c r="N107" s="23" t="inlineStr">
+        <is>
+          <t>Category Carpet Chair Mats Manufacturer Deflecto, LLC Manufacturer Ref CM15233 Br</t>
+        </is>
+      </c>
+      <c r="O107" s="23" t="inlineStr">
+        <is>
+          <t>Greenguard</t>
+        </is>
+      </c>
+      <c r="P107" s="23" t="inlineStr">
+        <is>
+          <t>Lifetime warranty</t>
+        </is>
+      </c>
+      <c r="Q107" s="33" t="inlineStr"/>
+      <c r="R107" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S107" s="35" t="inlineStr"/>
+      <c r="T107" s="25" t="inlineStr"/>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="32" t="inlineStr">
+        <is>
+          <t>part-time-armless-task-chair-mvl2836</t>
+        </is>
+      </c>
+      <c r="B108" s="32" t="inlineStr">
+        <is>
+          <t>Part-Time | Armless Task Chair MVL2836</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D108" s="32" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E108" s="32" t="inlineStr">
+        <is>
+          <t>249.99</t>
+        </is>
+      </c>
+      <c r="F108" s="33" t="inlineStr"/>
+      <c r="G108" s="23" t="inlineStr">
+        <is>
+          <t>Part-Time</t>
+        </is>
+      </c>
+      <c r="H108" s="33" t="inlineStr"/>
+      <c r="I108" s="33" t="inlineStr"/>
+      <c r="J108" s="33" t="inlineStr"/>
+      <c r="K108" s="33" t="inlineStr"/>
+      <c r="L108" s="33" t="inlineStr"/>
+      <c r="M108" s="33" t="inlineStr"/>
+      <c r="N108" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Part-Time | Armless Task Chair Part-Time series is a collection of office chairs </t>
+        </is>
+      </c>
+      <c r="O108" s="33" t="inlineStr"/>
+      <c r="P108" s="33" t="inlineStr"/>
+      <c r="Q108" s="33" t="inlineStr"/>
+      <c r="R108" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S108" s="35" t="inlineStr"/>
+      <c r="T108" s="25" t="inlineStr"/>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="27" t="inlineStr">
+        <is>
+          <t>shoptech-097-pc1000</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>Shoptech 097– — PC1000</t>
+        </is>
+      </c>
+      <c r="C109" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D109" s="27" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E109" s="27" t="inlineStr">
+        <is>
+          <t>394.0</t>
+        </is>
+      </c>
+      <c r="F109" s="33" t="inlineStr"/>
+      <c r="G109" s="23" t="inlineStr">
+        <is>
+          <t>Shoptech</t>
+        </is>
+      </c>
+      <c r="H109" s="23" t="inlineStr">
+        <is>
+          <t>PC1000</t>
+        </is>
+      </c>
+      <c r="I109" s="33" t="inlineStr"/>
+      <c r="J109" s="33" t="inlineStr"/>
+      <c r="K109" s="33" t="inlineStr"/>
+      <c r="L109" s="23" t="inlineStr">
+        <is>
+          <t>vinyl</t>
+        </is>
+      </c>
+      <c r="M109" s="33" t="inlineStr"/>
+      <c r="N109" s="23" t="inlineStr">
+        <is>
+          <t>Features Height adjustable gas lift action Seat and backrest covered in hardweari</t>
+        </is>
+      </c>
+      <c r="O109" s="33" t="inlineStr"/>
+      <c r="P109" s="33" t="inlineStr"/>
+      <c r="Q109" s="33" t="inlineStr"/>
+      <c r="R109" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S109" s="35" t="inlineStr"/>
+      <c r="T109" s="25" t="inlineStr"/>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="32" t="inlineStr">
+        <is>
+          <t>shoptech-2302-pc775</t>
+        </is>
+      </c>
+      <c r="B110" s="32" t="inlineStr">
+        <is>
+          <t>Shoptech 2302– — PC775</t>
+        </is>
+      </c>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D110" s="32" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E110" s="32" t="inlineStr">
+        <is>
+          <t>363.0</t>
+        </is>
+      </c>
+      <c r="F110" s="33" t="inlineStr"/>
+      <c r="G110" s="23" t="inlineStr">
+        <is>
+          <t>Shoptech</t>
+        </is>
+      </c>
+      <c r="H110" s="23" t="inlineStr">
+        <is>
+          <t>PC775</t>
+        </is>
+      </c>
+      <c r="I110" s="33" t="inlineStr"/>
+      <c r="J110" s="23" t="inlineStr">
+        <is>
+          <t>25 lbs</t>
+        </is>
+      </c>
+      <c r="K110" s="33" t="inlineStr"/>
+      <c r="L110" s="23" t="inlineStr">
+        <is>
+          <t>polyurethane</t>
+        </is>
+      </c>
+      <c r="M110" s="33" t="inlineStr"/>
+      <c r="N110" s="23" t="inlineStr">
+        <is>
+          <t>Features Ergonomically designed seat that both straightens and strengthens the sp</t>
+        </is>
+      </c>
+      <c r="O110" s="33" t="inlineStr"/>
+      <c r="P110" s="33" t="inlineStr"/>
+      <c r="Q110" s="33" t="inlineStr"/>
+      <c r="R110" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S110" s="35" t="inlineStr"/>
+      <c r="T110" s="25" t="inlineStr"/>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t>shoptech-2500-pc550</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>Shoptech 2500– — PC550</t>
+        </is>
+      </c>
+      <c r="C111" s="27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D111" s="27" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E111" s="27" t="inlineStr">
+        <is>
+          <t>299.99</t>
+        </is>
+      </c>
+      <c r="F111" s="33" t="inlineStr"/>
+      <c r="G111" s="23" t="inlineStr">
+        <is>
+          <t>Shoptech</t>
+        </is>
+      </c>
+      <c r="H111" s="23" t="inlineStr">
+        <is>
+          <t>PC550</t>
+        </is>
+      </c>
+      <c r="I111" s="33" t="inlineStr"/>
+      <c r="J111" s="23" t="inlineStr">
+        <is>
+          <t>20 lbs</t>
+        </is>
+      </c>
+      <c r="K111" s="33" t="inlineStr"/>
+      <c r="L111" s="23" t="inlineStr">
+        <is>
+          <t>polyurethane</t>
+        </is>
+      </c>
+      <c r="M111" s="33" t="inlineStr"/>
+      <c r="N111" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Features Height adjustable gas lift action Seat covered in hardwearing cushioned </t>
+        </is>
+      </c>
+      <c r="O111" s="33" t="inlineStr"/>
+      <c r="P111" s="33" t="inlineStr"/>
+      <c r="Q111" s="33" t="inlineStr"/>
+      <c r="R111" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S111" s="35" t="inlineStr"/>
+      <c r="T111" s="25" t="inlineStr"/>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="32" t="inlineStr">
+        <is>
+          <t>ceiling-grids-sound-acoustic-dampeners-copy</t>
+        </is>
+      </c>
+      <c r="B112" s="32" t="inlineStr">
+        <is>
+          <t>Ceiling grids sound acoustic dampeners</t>
+        </is>
+      </c>
+      <c r="C112" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D112" s="32" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E112" s="32" t="inlineStr">
+        <is>
+          <t>608.0</t>
+        </is>
+      </c>
+      <c r="F112" s="33" t="inlineStr"/>
+      <c r="G112" s="33" t="inlineStr"/>
+      <c r="H112" s="33" t="inlineStr"/>
+      <c r="I112" s="33" t="inlineStr"/>
+      <c r="J112" s="33" t="inlineStr"/>
+      <c r="K112" s="33" t="inlineStr"/>
+      <c r="L112" s="33" t="inlineStr"/>
+      <c r="M112" s="33" t="inlineStr"/>
+      <c r="N112" s="23" t="inlineStr">
+        <is>
+          <t>We offer multiple solutions to dampen the sound in open area's</t>
+        </is>
+      </c>
+      <c r="O112" s="33" t="inlineStr"/>
+      <c r="P112" s="33" t="inlineStr"/>
+      <c r="Q112" s="33" t="inlineStr"/>
+      <c r="R112" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S112" s="35" t="inlineStr"/>
+      <c r="T112" s="25" t="inlineStr"/>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="27" t="inlineStr">
+        <is>
+          <t>halifax-typical-4</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>Halifax typical 4</t>
+        </is>
+      </c>
+      <c r="C113" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D113" s="27" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E113" s="27" t="inlineStr">
+        <is>
+          <t>4450.0</t>
+        </is>
+      </c>
+      <c r="F113" s="33" t="inlineStr"/>
+      <c r="G113" s="23" t="inlineStr">
+        <is>
+          <t>Halifax typical</t>
+        </is>
+      </c>
+      <c r="H113" s="33" t="inlineStr"/>
+      <c r="I113" s="33" t="inlineStr"/>
+      <c r="J113" s="33" t="inlineStr"/>
+      <c r="K113" s="33" t="inlineStr"/>
+      <c r="L113" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M113" s="33" t="inlineStr"/>
+      <c r="N113" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Halifax is a culmination of OCI's steadfast commitment to always raising the bar </t>
+        </is>
+      </c>
+      <c r="O113" s="33" t="inlineStr"/>
+      <c r="P113" s="33" t="inlineStr"/>
+      <c r="Q113" s="33" t="inlineStr"/>
+      <c r="R113" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S113" s="35" t="inlineStr"/>
+      <c r="T113" s="25" t="inlineStr"/>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="32" t="inlineStr">
+        <is>
+          <t>partitions-66-high-2-offices-1</t>
+        </is>
+      </c>
+      <c r="B114" s="32" t="inlineStr">
+        <is>
+          <t>Partitions 66" high 2 offices — 66"</t>
+        </is>
+      </c>
+      <c r="C114" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D114" s="32" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E114" s="32" t="inlineStr">
+        <is>
+          <t>2099.99</t>
+        </is>
+      </c>
+      <c r="F114" s="33" t="inlineStr"/>
+      <c r="G114" s="23" t="inlineStr">
+        <is>
+          <t>Partitions</t>
+        </is>
+      </c>
+      <c r="H114" s="33" t="inlineStr"/>
+      <c r="I114" s="33" t="inlineStr"/>
+      <c r="J114" s="33" t="inlineStr"/>
+      <c r="K114" s="33" t="inlineStr"/>
+      <c r="L114" s="23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="M114" s="33" t="inlineStr"/>
+      <c r="N114" s="33" t="inlineStr"/>
+      <c r="O114" s="33" t="inlineStr"/>
+      <c r="P114" s="33" t="inlineStr"/>
+      <c r="Q114" s="33" t="inlineStr"/>
+      <c r="R114" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S114" s="35" t="inlineStr"/>
+      <c r="T114" s="25" t="inlineStr"/>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="27" t="inlineStr">
+        <is>
+          <t>partitions-66-high-3-offices-1</t>
+        </is>
+      </c>
+      <c r="B115" s="27" t="inlineStr">
+        <is>
+          <t>Partitions 66" high 3 offices — 66"</t>
+        </is>
+      </c>
+      <c r="C115" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D115" s="27" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E115" s="27" t="inlineStr">
+        <is>
+          <t>2999.0</t>
+        </is>
+      </c>
+      <c r="F115" s="33" t="inlineStr"/>
+      <c r="G115" s="23" t="inlineStr">
+        <is>
+          <t>Partitions</t>
+        </is>
+      </c>
+      <c r="H115" s="33" t="inlineStr"/>
+      <c r="I115" s="33" t="inlineStr"/>
+      <c r="J115" s="33" t="inlineStr"/>
+      <c r="K115" s="33" t="inlineStr"/>
+      <c r="L115" s="23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="M115" s="33" t="inlineStr"/>
+      <c r="N115" s="33" t="inlineStr"/>
+      <c r="O115" s="33" t="inlineStr"/>
+      <c r="P115" s="33" t="inlineStr"/>
+      <c r="Q115" s="33" t="inlineStr"/>
+      <c r="R115" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S115" s="35" t="inlineStr"/>
+      <c r="T115" s="25" t="inlineStr"/>
+    </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="32" t="inlineStr">
+        <is>
+          <t>planter</t>
+        </is>
+      </c>
+      <c r="B116" s="32" t="inlineStr">
+        <is>
+          <t>Planter</t>
+        </is>
+      </c>
+      <c r="C116" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D116" s="32" t="inlineStr">
+        <is>
+          <t>accessories</t>
+        </is>
+      </c>
+      <c r="E116" s="32" t="inlineStr">
+        <is>
+          <t>1399.99</t>
+        </is>
+      </c>
+      <c r="F116" s="33" t="inlineStr"/>
+      <c r="G116" s="33" t="inlineStr"/>
+      <c r="H116" s="33" t="inlineStr"/>
+      <c r="I116" s="33" t="inlineStr"/>
+      <c r="J116" s="33" t="inlineStr"/>
+      <c r="K116" s="33" t="inlineStr"/>
+      <c r="L116" s="33" t="inlineStr"/>
+      <c r="M116" s="33" t="inlineStr"/>
+      <c r="N116" s="23" t="inlineStr">
+        <is>
+          <t>Made in Canada, this new planter is available in several sizes and colours</t>
+        </is>
+      </c>
+      <c r="O116" s="33" t="inlineStr"/>
+      <c r="P116" s="33" t="inlineStr"/>
+      <c r="Q116" s="33" t="inlineStr"/>
+      <c r="R116" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S116" s="35" t="inlineStr"/>
+      <c r="T116" s="25" t="inlineStr"/>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="27" t="inlineStr">
+        <is>
+          <t>adapt-high-back-synchro-tilter-mvl11724-mvl11725</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>Adapt | high back synchro-tilter MVL11724 — MVL11725</t>
+        </is>
+      </c>
+      <c r="C117" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D117" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E117" s="27" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F117" s="33" t="inlineStr"/>
+      <c r="G117" s="23" t="inlineStr">
+        <is>
+          <t>Adapt</t>
+        </is>
+      </c>
+      <c r="H117" s="23" t="inlineStr">
+        <is>
+          <t>MVL11725</t>
+        </is>
+      </c>
+      <c r="I117" s="33" t="inlineStr"/>
+      <c r="J117" s="33" t="inlineStr"/>
+      <c r="K117" s="33" t="inlineStr"/>
+      <c r="L117" s="23" t="inlineStr">
+        <is>
+          <t>mesh, nylon, glass, upholstered</t>
+        </is>
+      </c>
+      <c r="M117" s="33" t="inlineStr"/>
+      <c r="N117" s="23" t="inlineStr">
+        <is>
+          <t>MVL11724 OR MVL11725 Adapt | High Back Synchro-Tilter Experience unparalleled com</t>
+        </is>
+      </c>
+      <c r="O117" s="33" t="inlineStr"/>
+      <c r="P117" s="33" t="inlineStr"/>
+      <c r="Q117" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R117" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S117" s="35" t="inlineStr"/>
+      <c r="T117" s="25" t="inlineStr"/>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="32" t="inlineStr">
+        <is>
+          <t>adapt-high-back-synchro-tilter-mvl11725</t>
+        </is>
+      </c>
+      <c r="B118" s="32" t="inlineStr">
+        <is>
+          <t>Adapt | high back synchro-tilter — MVL11725</t>
+        </is>
+      </c>
+      <c r="C118" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D118" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E118" s="32" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F118" s="33" t="inlineStr"/>
+      <c r="G118" s="23" t="inlineStr">
+        <is>
+          <t>Adapt</t>
+        </is>
+      </c>
+      <c r="H118" s="23" t="inlineStr">
+        <is>
+          <t>MVL11725</t>
+        </is>
+      </c>
+      <c r="I118" s="33" t="inlineStr"/>
+      <c r="J118" s="33" t="inlineStr"/>
+      <c r="K118" s="33" t="inlineStr"/>
+      <c r="L118" s="23" t="inlineStr">
+        <is>
+          <t>mesh, nylon, glass</t>
+        </is>
+      </c>
+      <c r="M118" s="33" t="inlineStr"/>
+      <c r="N118" s="23" t="inlineStr">
+        <is>
+          <t>Loop Arms Black frame with a Black 5-prong, injection molded, fiberglass reinforc</t>
+        </is>
+      </c>
+      <c r="O118" s="33" t="inlineStr"/>
+      <c r="P118" s="33" t="inlineStr"/>
+      <c r="Q118" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R118" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S118" s="35" t="inlineStr"/>
+      <c r="T118" s="25" t="inlineStr"/>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="27" t="inlineStr">
+        <is>
+          <t>bar-stool-for-42-high-tables</t>
+        </is>
+      </c>
+      <c r="B119" s="27" t="inlineStr">
+        <is>
+          <t>Bar stool for 42" high tables — 42"</t>
+        </is>
+      </c>
+      <c r="C119" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D119" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E119" s="27" t="inlineStr">
+        <is>
+          <t>286.0</t>
+        </is>
+      </c>
+      <c r="F119" s="33" t="inlineStr"/>
+      <c r="G119" s="23" t="inlineStr">
+        <is>
+          <t>Bar stool for</t>
+        </is>
+      </c>
+      <c r="H119" s="33" t="inlineStr"/>
+      <c r="I119" s="33" t="inlineStr"/>
+      <c r="J119" s="33" t="inlineStr"/>
+      <c r="K119" s="33" t="inlineStr"/>
+      <c r="L119" s="23" t="inlineStr">
+        <is>
+          <t>polypropylene, steel, upholstered</t>
+        </is>
+      </c>
+      <c r="M119" s="33" t="inlineStr"/>
+      <c r="N119" s="23" t="inlineStr">
+        <is>
+          <t>Popcorn™ Popcorn, designed by Zooey Chu, is ideal for conference areas, cafeteria</t>
+        </is>
+      </c>
+      <c r="O119" s="33" t="inlineStr"/>
+      <c r="P119" s="33" t="inlineStr"/>
+      <c r="Q119" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R119" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S119" s="35" t="inlineStr"/>
+      <c r="T119" s="25" t="inlineStr"/>
+    </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="32" t="inlineStr">
+        <is>
+          <t>basics-comfort-time-ultra-multi-tilter-chair-with-headrest</t>
+        </is>
+      </c>
+      <c r="B120" s="32" t="inlineStr">
+        <is>
+          <t>Basics comfort-time ultra multi-tilter chair with headrest</t>
+        </is>
+      </c>
+      <c r="C120" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D120" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E120" s="32" t="inlineStr">
+        <is>
+          <t>664.99</t>
+        </is>
+      </c>
+      <c r="F120" s="33" t="inlineStr"/>
+      <c r="G120" s="33" t="inlineStr"/>
+      <c r="H120" s="33" t="inlineStr"/>
+      <c r="I120" s="33" t="inlineStr"/>
+      <c r="J120" s="33" t="inlineStr"/>
+      <c r="K120" s="33" t="inlineStr"/>
+      <c r="L120" s="23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="M120" s="33" t="inlineStr"/>
+      <c r="N120" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Basics® Comfort-Time™ Ultra Multi-Tilter Chair with Headrest ; Pneumatic seat height adjustment ; Seat depth adjustment </t>
+        </is>
+      </c>
+      <c r="O120" s="33" t="inlineStr"/>
+      <c r="P120" s="33" t="inlineStr"/>
+      <c r="Q120" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R120" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S120" s="35" t="inlineStr"/>
+      <c r="T120" s="25" t="inlineStr"/>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="27" t="inlineStr">
+        <is>
+          <t>cluster-seating-2</t>
+        </is>
+      </c>
+      <c r="B121" s="27" t="inlineStr">
+        <is>
+          <t>Cluster seating 2</t>
+        </is>
+      </c>
+      <c r="C121" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D121" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E121" s="27" t="inlineStr">
+        <is>
+          <t>1388.0</t>
+        </is>
+      </c>
+      <c r="F121" s="33" t="inlineStr"/>
+      <c r="G121" s="23" t="inlineStr">
+        <is>
+          <t>Cluster seating</t>
+        </is>
+      </c>
+      <c r="H121" s="33" t="inlineStr"/>
+      <c r="I121" s="33" t="inlineStr"/>
+      <c r="J121" s="33" t="inlineStr"/>
+      <c r="K121" s="33" t="inlineStr"/>
+      <c r="L121" s="23" t="inlineStr">
+        <is>
+          <t>steel, laminate, powder coat</t>
+        </is>
+      </c>
+      <c r="M121" s="33" t="inlineStr"/>
+      <c r="N121" s="23" t="inlineStr">
+        <is>
+          <t>Comfortably seats 2 adults 1" thick industrial grade particle board High pressure</t>
+        </is>
+      </c>
+      <c r="O121" s="33" t="inlineStr"/>
+      <c r="P121" s="23" t="inlineStr">
+        <is>
+          <t>Lifetime warranty</t>
+        </is>
+      </c>
+      <c r="Q121" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R121" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S121" s="35" t="inlineStr"/>
+      <c r="T121" s="25" t="inlineStr"/>
+    </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="32" t="inlineStr">
+        <is>
+          <t>concorde-high-back-24hr-executive-synchro-tilter-deep-seat-2424-18</t>
+        </is>
+      </c>
+      <c r="B122" s="32" t="inlineStr">
+        <is>
+          <t>Concorde high back 24HR executive synchro-tilter, deep seat (2424-18) — 2424-18</t>
+        </is>
+      </c>
+      <c r="C122" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D122" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E122" s="32" t="inlineStr">
+        <is>
+          <t>2337.0</t>
+        </is>
+      </c>
+      <c r="F122" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G122" s="23" t="inlineStr">
+        <is>
+          <t>Concorde high back</t>
+        </is>
+      </c>
+      <c r="H122" s="33" t="inlineStr"/>
+      <c r="I122" s="33" t="inlineStr"/>
+      <c r="J122" s="33" t="inlineStr"/>
+      <c r="K122" s="33" t="inlineStr"/>
+      <c r="L122" s="33" t="inlineStr"/>
+      <c r="M122" s="33" t="inlineStr"/>
+      <c r="N122" s="23" t="inlineStr">
+        <is>
+          <t>Concorde provides unique push-button control from the arm of the chair</t>
+        </is>
+      </c>
+      <c r="O122" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA; ANSI</t>
+        </is>
+      </c>
+      <c r="P122" s="23" t="inlineStr">
+        <is>
+          <t>Lifetime warranty</t>
+        </is>
+      </c>
+      <c r="Q122" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R122" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S122" s="35" t="inlineStr"/>
+      <c r="T122" s="25" t="inlineStr"/>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="27" t="inlineStr">
+        <is>
+          <t>elora-multi-tilter-high-back-chair-black-petite-seat-baomvl1894</t>
+        </is>
+      </c>
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>Elora multi-tilter high back chair black petite seat — BAOMVL1894</t>
+        </is>
+      </c>
+      <c r="C123" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D123" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E123" s="27" t="inlineStr">
+        <is>
+          <t>569.99</t>
+        </is>
+      </c>
+      <c r="F123" s="33" t="inlineStr"/>
+      <c r="G123" s="33" t="inlineStr"/>
+      <c r="H123" s="23" t="inlineStr">
+        <is>
+          <t>BAOMVL1894</t>
+        </is>
+      </c>
+      <c r="I123" s="33" t="inlineStr"/>
+      <c r="J123" s="33" t="inlineStr"/>
+      <c r="K123" s="33" t="inlineStr"/>
+      <c r="L123" s="23" t="inlineStr">
+        <is>
+          <t>mesh</t>
+        </is>
+      </c>
+      <c r="M123" s="33" t="inlineStr"/>
+      <c r="N123" s="23" t="inlineStr">
+        <is>
+          <t>Seat Size: Petite Seat (for small set individuals) Multi-tilt feature makes the c</t>
+        </is>
+      </c>
+      <c r="O123" s="33" t="inlineStr"/>
+      <c r="P123" s="33" t="inlineStr"/>
+      <c r="Q123" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R123" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S123" s="35" t="inlineStr"/>
+      <c r="T123" s="25" t="inlineStr"/>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="32" t="inlineStr">
+        <is>
+          <t>factor-mesh-seating-stool</t>
+        </is>
+      </c>
+      <c r="B124" s="32" t="inlineStr">
+        <is>
+          <t>Factor mesh seating stool</t>
+        </is>
+      </c>
+      <c r="C124" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D124" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E124" s="32" t="inlineStr">
+        <is>
+          <t>599.99</t>
+        </is>
+      </c>
+      <c r="F124" s="33" t="inlineStr"/>
+      <c r="G124" s="33" t="inlineStr"/>
+      <c r="H124" s="33" t="inlineStr"/>
+      <c r="I124" s="33" t="inlineStr"/>
+      <c r="J124" s="33" t="inlineStr"/>
+      <c r="K124" s="33" t="inlineStr"/>
+      <c r="L124" s="23" t="inlineStr">
+        <is>
+          <t>mesh</t>
+        </is>
+      </c>
+      <c r="M124" s="33" t="inlineStr"/>
+      <c r="N124" s="23" t="inlineStr">
+        <is>
+          <t>Mesh Back Ergo Stool Arms: Non Height Adjustable Mechanism: Task Basic Swivel Dim</t>
+        </is>
+      </c>
+      <c r="O124" s="33" t="inlineStr"/>
+      <c r="P124" s="33" t="inlineStr"/>
+      <c r="Q124" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R124" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S124" s="35" t="inlineStr"/>
+      <c r="T124" s="25" t="inlineStr"/>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="27" t="inlineStr">
+        <is>
+          <t>high-back-weight-sensing-synchro-tilter</t>
+        </is>
+      </c>
+      <c r="B125" s="27" t="inlineStr">
+        <is>
+          <t>High back weight sensing synchro-tilter</t>
+        </is>
+      </c>
+      <c r="C125" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D125" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E125" s="27" t="inlineStr">
+        <is>
+          <t>659.0</t>
+        </is>
+      </c>
+      <c r="F125" s="33" t="inlineStr"/>
+      <c r="G125" s="33" t="inlineStr"/>
+      <c r="H125" s="33" t="inlineStr"/>
+      <c r="I125" s="33" t="inlineStr"/>
+      <c r="J125" s="33" t="inlineStr"/>
+      <c r="K125" s="33" t="inlineStr"/>
+      <c r="L125" s="23" t="inlineStr">
+        <is>
+          <t>mesh</t>
+        </is>
+      </c>
+      <c r="M125" s="33" t="inlineStr"/>
+      <c r="N125" s="23" t="inlineStr">
+        <is>
+          <t>Sora™ responds to your movements while you work</t>
+        </is>
+      </c>
+      <c r="O125" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA</t>
+        </is>
+      </c>
+      <c r="P125" s="33" t="inlineStr"/>
+      <c r="Q125" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R125" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S125" s="35" t="inlineStr"/>
+      <c r="T125" s="25" t="inlineStr"/>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="32" t="inlineStr">
+        <is>
+          <t>ibex-upholstered-seat-back-guest-chair-mvl2832</t>
+        </is>
+      </c>
+      <c r="B126" s="32" t="inlineStr">
+        <is>
+          <t>Ibex | upholstered seat &amp; back guest chair — MVL2832</t>
+        </is>
+      </c>
+      <c r="C126" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D126" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E126" s="32" t="inlineStr">
+        <is>
+          <t>335.99</t>
+        </is>
+      </c>
+      <c r="F126" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G126" s="23" t="inlineStr">
+        <is>
+          <t>Ibex</t>
+        </is>
+      </c>
+      <c r="H126" s="23" t="inlineStr">
+        <is>
+          <t>MVL2832</t>
+        </is>
+      </c>
+      <c r="I126" s="33" t="inlineStr"/>
+      <c r="J126" s="33" t="inlineStr"/>
+      <c r="K126" s="33" t="inlineStr"/>
+      <c r="L126" s="23" t="inlineStr">
+        <is>
+          <t>upholstered</t>
+        </is>
+      </c>
+      <c r="M126" s="33" t="inlineStr"/>
+      <c r="N126" s="23" t="inlineStr">
+        <is>
+          <t>Ibex | Upholstered Seat &amp; Back Armless Guest Chair Elevate your office experience</t>
+        </is>
+      </c>
+      <c r="O126" s="33" t="inlineStr"/>
+      <c r="P126" s="33" t="inlineStr"/>
+      <c r="Q126" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R126" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S126" s="35" t="inlineStr"/>
+      <c r="T126" s="25" t="inlineStr"/>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="27" t="inlineStr">
+        <is>
+          <t>low-back-stacking-chair-mvl2747</t>
+        </is>
+      </c>
+      <c r="B127" s="27" t="inlineStr">
+        <is>
+          <t>Low back stacking chair — MVL2747</t>
+        </is>
+      </c>
+      <c r="C127" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D127" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E127" s="27" t="inlineStr">
+        <is>
+          <t>159.99</t>
+        </is>
+      </c>
+      <c r="F127" s="33" t="inlineStr"/>
+      <c r="G127" s="23" t="inlineStr">
+        <is>
+          <t>Low back stacking chair</t>
+        </is>
+      </c>
+      <c r="H127" s="23" t="inlineStr">
+        <is>
+          <t>MVL2747</t>
+        </is>
+      </c>
+      <c r="I127" s="33" t="inlineStr"/>
+      <c r="J127" s="33" t="inlineStr"/>
+      <c r="K127" s="33" t="inlineStr"/>
+      <c r="L127" s="23" t="inlineStr">
+        <is>
+          <t>steel, upholstered</t>
+        </is>
+      </c>
+      <c r="M127" s="33" t="inlineStr"/>
+      <c r="N127" s="23" t="inlineStr">
+        <is>
+          <t>MVL2748 Minto | Low Back Stacking Chair Stacking chair Fully upholstered seat and</t>
+        </is>
+      </c>
+      <c r="O127" s="33" t="inlineStr"/>
+      <c r="P127" s="33" t="inlineStr"/>
+      <c r="Q127" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R127" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S127" s="35" t="inlineStr"/>
+      <c r="T127" s="25" t="inlineStr"/>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="32" t="inlineStr">
+        <is>
+          <t>marche-guest-chair-8622</t>
+        </is>
+      </c>
+      <c r="B128" s="32" t="inlineStr">
+        <is>
+          <t>Marche guest chair — 8622</t>
+        </is>
+      </c>
+      <c r="C128" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D128" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E128" s="32" t="inlineStr">
+        <is>
+          <t>570.99</t>
+        </is>
+      </c>
+      <c r="F128" s="33" t="inlineStr"/>
+      <c r="G128" s="23" t="inlineStr">
+        <is>
+          <t>Marche guest chair</t>
+        </is>
+      </c>
+      <c r="H128" s="33" t="inlineStr"/>
+      <c r="I128" s="33" t="inlineStr"/>
+      <c r="J128" s="33" t="inlineStr"/>
+      <c r="K128" s="33" t="inlineStr"/>
+      <c r="L128" s="23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="M128" s="33" t="inlineStr"/>
+      <c r="N128" s="23" t="inlineStr">
+        <is>
+          <t>Other fabrics available</t>
+        </is>
+      </c>
+      <c r="O128" s="33" t="inlineStr"/>
+      <c r="P128" s="33" t="inlineStr"/>
+      <c r="Q128" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R128" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S128" s="35" t="inlineStr"/>
+      <c r="T128" s="25" t="inlineStr"/>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="27" t="inlineStr">
+        <is>
+          <t>marche-guest-chair-copy</t>
+        </is>
+      </c>
+      <c r="B129" s="27" t="inlineStr">
+        <is>
+          <t>Marche guest chair</t>
+        </is>
+      </c>
+      <c r="C129" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D129" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E129" s="27" t="inlineStr">
+        <is>
+          <t>670.64</t>
+        </is>
+      </c>
+      <c r="F129" s="33" t="inlineStr"/>
+      <c r="G129" s="33" t="inlineStr"/>
+      <c r="H129" s="33" t="inlineStr"/>
+      <c r="I129" s="33" t="inlineStr"/>
+      <c r="J129" s="33" t="inlineStr"/>
+      <c r="K129" s="33" t="inlineStr"/>
+      <c r="L129" s="23" t="inlineStr">
+        <is>
+          <t>fabric</t>
+        </is>
+      </c>
+      <c r="M129" s="33" t="inlineStr"/>
+      <c r="N129" s="23" t="inlineStr">
+        <is>
+          <t>Other fabrics available</t>
+        </is>
+      </c>
+      <c r="O129" s="33" t="inlineStr"/>
+      <c r="P129" s="33" t="inlineStr"/>
+      <c r="Q129" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R129" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S129" s="35" t="inlineStr"/>
+      <c r="T129" s="25" t="inlineStr"/>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="32" t="inlineStr">
+        <is>
+          <t>obusforme-comfort-high-back-chair-1260-3-schukra</t>
+        </is>
+      </c>
+      <c r="B130" s="32" t="inlineStr">
+        <is>
+          <t>ObusForme Comfort high back chair 1260-3 schukra</t>
+        </is>
+      </c>
+      <c r="C130" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D130" s="32" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E130" s="32" t="inlineStr">
+        <is>
+          <t>769.99</t>
+        </is>
+      </c>
+      <c r="F130" s="23" t="inlineStr">
+        <is>
+          <t>ObusForme</t>
+        </is>
+      </c>
+      <c r="G130" s="23" t="inlineStr">
+        <is>
+          <t>ObusForme Comfort high back chair</t>
+        </is>
+      </c>
+      <c r="H130" s="33" t="inlineStr"/>
+      <c r="I130" s="33" t="inlineStr"/>
+      <c r="J130" s="33" t="inlineStr"/>
+      <c r="K130" s="33" t="inlineStr"/>
+      <c r="L130" s="23" t="inlineStr">
+        <is>
+          <t>aluminum, nylon</t>
+        </is>
+      </c>
+      <c r="M130" s="33" t="inlineStr"/>
+      <c r="N130" s="33" t="inlineStr"/>
+      <c r="O130" s="33" t="inlineStr"/>
+      <c r="P130" s="33" t="inlineStr"/>
+      <c r="Q130" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R130" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S130" s="35" t="inlineStr"/>
+      <c r="T130" s="25" t="inlineStr"/>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="27" t="inlineStr">
+        <is>
+          <t>tl-high-back-synchro-tilter</t>
+        </is>
+      </c>
+      <c r="B131" s="27" t="inlineStr">
+        <is>
+          <t>Tl | high back synchro-tilter</t>
+        </is>
+      </c>
+      <c r="C131" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D131" s="27" t="inlineStr">
+        <is>
+          <t>chairs</t>
+        </is>
+      </c>
+      <c r="E131" s="27" t="inlineStr">
+        <is>
+          <t>679.99</t>
+        </is>
+      </c>
+      <c r="F131" s="33" t="inlineStr"/>
+      <c r="G131" s="33" t="inlineStr"/>
+      <c r="H131" s="33" t="inlineStr"/>
+      <c r="I131" s="33" t="inlineStr"/>
+      <c r="J131" s="33" t="inlineStr"/>
+      <c r="K131" s="23" t="inlineStr">
+        <is>
+          <t>300 lbs</t>
+        </is>
+      </c>
+      <c r="L131" s="23" t="inlineStr">
+        <is>
+          <t>mesh, fabric</t>
+        </is>
+      </c>
+      <c r="M131" s="33" t="inlineStr"/>
+      <c r="N131" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canadian designed and manufactured ergonomic chair; Pneumatic seat height adjustment ; Upright position tilt lock </t>
+        </is>
+      </c>
+      <c r="O131" s="33" t="inlineStr"/>
+      <c r="P131" s="33" t="inlineStr"/>
+      <c r="Q131" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R131" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S131" s="35" t="inlineStr"/>
+      <c r="T131" s="25" t="inlineStr"/>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="32" t="inlineStr">
+        <is>
+          <t>desk-top-dividers</t>
+        </is>
+      </c>
+      <c r="B132" s="32" t="inlineStr">
+        <is>
+          <t>Desk top dividers</t>
+        </is>
+      </c>
+      <c r="C132" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D132" s="32" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E132" s="32" t="inlineStr">
+        <is>
+          <t>199.99</t>
+        </is>
+      </c>
+      <c r="F132" s="33" t="inlineStr"/>
+      <c r="G132" s="33" t="inlineStr"/>
+      <c r="H132" s="33" t="inlineStr"/>
+      <c r="I132" s="33" t="inlineStr"/>
+      <c r="J132" s="33" t="inlineStr"/>
+      <c r="K132" s="33" t="inlineStr"/>
+      <c r="L132" s="23" t="inlineStr">
+        <is>
+          <t>glass</t>
+        </is>
+      </c>
+      <c r="M132" s="33" t="inlineStr"/>
+      <c r="N132" s="23" t="inlineStr">
+        <is>
+          <t>Features Brackets available in Silver (SL) finish Frosted plexiglass panel</t>
+        </is>
+      </c>
+      <c r="O132" s="33" t="inlineStr"/>
+      <c r="P132" s="33" t="inlineStr"/>
+      <c r="Q132" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R132" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S132" s="35" t="inlineStr"/>
+      <c r="T132" s="25" t="inlineStr"/>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="27" t="inlineStr">
+        <is>
+          <t>l-shape-desk-with-36h-privacy-panel-1</t>
+        </is>
+      </c>
+      <c r="B133" s="27" t="inlineStr">
+        <is>
+          <t>L-shape desk with 36"h privacy panel — 36"</t>
+        </is>
+      </c>
+      <c r="C133" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D133" s="27" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E133" s="27" t="inlineStr">
+        <is>
+          <t>4199.99</t>
+        </is>
+      </c>
+      <c r="F133" s="33" t="inlineStr"/>
+      <c r="G133" s="23" t="inlineStr">
+        <is>
+          <t>L-shape desk with</t>
+        </is>
+      </c>
+      <c r="H133" s="33" t="inlineStr"/>
+      <c r="I133" s="33" t="inlineStr"/>
+      <c r="J133" s="33" t="inlineStr"/>
+      <c r="K133" s="33" t="inlineStr"/>
+      <c r="L133" s="33" t="inlineStr"/>
+      <c r="M133" s="33" t="inlineStr"/>
+      <c r="N133" s="23" t="inlineStr">
+        <is>
+          <t>L-Shape Desk with 36"H Privacy Panel Desk Size: 72" 72" Panel Height: 36" off the</t>
+        </is>
+      </c>
+      <c r="O133" s="33" t="inlineStr"/>
+      <c r="P133" s="33" t="inlineStr"/>
+      <c r="Q133" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R133" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S133" s="35" t="inlineStr"/>
+      <c r="T133" s="25" t="inlineStr"/>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="32" t="inlineStr">
+        <is>
+          <t>management-u-shaped-suite-72w-x-102d</t>
+        </is>
+      </c>
+      <c r="B134" s="32" t="inlineStr">
+        <is>
+          <t>Management "u" shaped suite - 72"w x 102"d — 102"</t>
+        </is>
+      </c>
+      <c r="C134" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D134" s="32" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E134" s="32" t="inlineStr">
+        <is>
+          <t>1944.0</t>
+        </is>
+      </c>
+      <c r="F134" s="33" t="inlineStr"/>
+      <c r="G134" s="33" t="inlineStr"/>
+      <c r="H134" s="33" t="inlineStr"/>
+      <c r="I134" s="33" t="inlineStr"/>
+      <c r="J134" s="33" t="inlineStr"/>
+      <c r="K134" s="33" t="inlineStr"/>
+      <c r="L134" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M134" s="33" t="inlineStr"/>
+      <c r="N134" s="23" t="inlineStr">
+        <is>
+          <t>Management "U" Shaped Suite - 72"W x 102"D Simple and modular components combinin</t>
+        </is>
+      </c>
+      <c r="O134" s="33" t="inlineStr"/>
+      <c r="P134" s="33" t="inlineStr"/>
+      <c r="Q134" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R134" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S134" s="35" t="inlineStr"/>
+      <c r="T134" s="25" t="inlineStr"/>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="27" t="inlineStr">
+        <is>
+          <t>single-pedestal-desk-nlp232</t>
+        </is>
+      </c>
+      <c r="B135" s="27" t="inlineStr">
+        <is>
+          <t>Single pedestal desk — NLP232</t>
+        </is>
+      </c>
+      <c r="C135" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D135" s="27" t="inlineStr">
+        <is>
+          <t>desks</t>
+        </is>
+      </c>
+      <c r="E135" s="27" t="inlineStr">
+        <is>
+          <t>799.99</t>
+        </is>
+      </c>
+      <c r="F135" s="33" t="inlineStr"/>
+      <c r="G135" s="23" t="inlineStr">
+        <is>
+          <t>Single pedestal desk</t>
+        </is>
+      </c>
+      <c r="H135" s="23" t="inlineStr">
+        <is>
+          <t>NLP232</t>
+        </is>
+      </c>
+      <c r="I135" s="33" t="inlineStr"/>
+      <c r="J135" s="33" t="inlineStr"/>
+      <c r="K135" s="33" t="inlineStr"/>
+      <c r="L135" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M135" s="33" t="inlineStr"/>
+      <c r="N135" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NLP232 Newland | Single Pedestal Desk - 60"W x 30"D Newland - simple and modular </t>
+        </is>
+      </c>
+      <c r="O135" s="33" t="inlineStr"/>
+      <c r="P135" s="33" t="inlineStr"/>
+      <c r="Q135" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R135" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S135" s="35" t="inlineStr"/>
+      <c r="T135" s="25" t="inlineStr"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="32" t="inlineStr">
+        <is>
+          <t>4-drawer-legal-width-vertical-file</t>
+        </is>
+      </c>
+      <c r="B136" s="32" t="inlineStr">
+        <is>
+          <t>4 drawer legal width vertical file — 4 drawer</t>
+        </is>
+      </c>
+      <c r="C136" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D136" s="32" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E136" s="32" t="inlineStr">
+        <is>
+          <t>489.99</t>
+        </is>
+      </c>
+      <c r="F136" s="33" t="inlineStr"/>
+      <c r="G136" s="33" t="inlineStr"/>
+      <c r="H136" s="33" t="inlineStr"/>
+      <c r="I136" s="23" t="inlineStr">
+        <is>
+          <t>18.15 x 25 x 52"</t>
+        </is>
+      </c>
+      <c r="J136" s="23" t="inlineStr">
+        <is>
+          <t>122 lbs</t>
+        </is>
+      </c>
+      <c r="K136" s="33" t="inlineStr"/>
+      <c r="L136" s="33" t="inlineStr"/>
+      <c r="M136" s="33" t="inlineStr"/>
+      <c r="N136" s="33" t="inlineStr"/>
+      <c r="O136" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA; ANSI</t>
+        </is>
+      </c>
+      <c r="P136" s="33" t="inlineStr"/>
+      <c r="Q136" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R136" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S136" s="35" t="inlineStr"/>
+      <c r="T136" s="25" t="inlineStr"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="27" t="inlineStr">
+        <is>
+          <t>fireking-storage-cabinet-44-high</t>
+        </is>
+      </c>
+      <c r="B137" s="27" t="inlineStr">
+        <is>
+          <t>Fireking storage cabinet 44" high — 44"</t>
+        </is>
+      </c>
+      <c r="C137" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D137" s="27" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E137" s="27" t="inlineStr">
+        <is>
+          <t>5299.79</t>
+        </is>
+      </c>
+      <c r="F137" s="33" t="inlineStr"/>
+      <c r="G137" s="23" t="inlineStr">
+        <is>
+          <t>Fireking storage cabinet</t>
+        </is>
+      </c>
+      <c r="H137" s="33" t="inlineStr"/>
+      <c r="I137" s="33" t="inlineStr"/>
+      <c r="J137" s="33" t="inlineStr"/>
+      <c r="K137" s="33" t="inlineStr"/>
+      <c r="L137" s="33" t="inlineStr"/>
+      <c r="M137" s="33" t="inlineStr"/>
+      <c r="N137" s="23" t="inlineStr">
+        <is>
+          <t>This Storage Cabinet features a U</t>
+        </is>
+      </c>
+      <c r="O137" s="33" t="inlineStr"/>
+      <c r="P137" s="33" t="inlineStr"/>
+      <c r="Q137" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R137" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S137" s="35" t="inlineStr"/>
+      <c r="T137" s="25" t="inlineStr"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="32" t="inlineStr">
+        <is>
+          <t>laminate-lockers-copy</t>
+        </is>
+      </c>
+      <c r="B138" s="32" t="inlineStr">
+        <is>
+          <t>Laminate lockers</t>
+        </is>
+      </c>
+      <c r="C138" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D138" s="32" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E138" s="32" t="inlineStr">
+        <is>
+          <t>1219.2</t>
+        </is>
+      </c>
+      <c r="F138" s="33" t="inlineStr"/>
+      <c r="G138" s="33" t="inlineStr"/>
+      <c r="H138" s="33" t="inlineStr"/>
+      <c r="I138" s="33" t="inlineStr"/>
+      <c r="J138" s="33" t="inlineStr"/>
+      <c r="K138" s="33" t="inlineStr"/>
+      <c r="L138" s="23" t="inlineStr">
+        <is>
+          <t>wood</t>
+        </is>
+      </c>
+      <c r="M138" s="33" t="inlineStr"/>
+      <c r="N138" s="23" t="inlineStr">
+        <is>
+          <t>Made in Canada Wood or solid colour lockers</t>
+        </is>
+      </c>
+      <c r="O138" s="33" t="inlineStr"/>
+      <c r="P138" s="33" t="inlineStr"/>
+      <c r="Q138" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R138" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S138" s="35" t="inlineStr"/>
+      <c r="T138" s="25" t="inlineStr"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="27" t="inlineStr">
+        <is>
+          <t>lateral-file-storage-cabinet-with-shelves</t>
+        </is>
+      </c>
+      <c r="B139" s="27" t="inlineStr">
+        <is>
+          <t>Lateral file &amp; storage cabinet with shelves</t>
+        </is>
+      </c>
+      <c r="C139" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D139" s="27" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="E139" s="27" t="inlineStr">
+        <is>
+          <t>1009.99</t>
+        </is>
+      </c>
+      <c r="F139" s="33" t="inlineStr"/>
+      <c r="G139" s="33" t="inlineStr"/>
+      <c r="H139" s="33" t="inlineStr"/>
+      <c r="I139" s="33" t="inlineStr"/>
+      <c r="J139" s="33" t="inlineStr"/>
+      <c r="K139" s="33" t="inlineStr"/>
+      <c r="L139" s="33" t="inlineStr"/>
+      <c r="M139" s="33" t="inlineStr"/>
+      <c r="N139" s="23" t="inlineStr">
+        <is>
+          <t>Made in Canada Framed with 1" thick construction with locking drawers and doors</t>
+        </is>
+      </c>
+      <c r="O139" s="33" t="inlineStr"/>
+      <c r="P139" s="33" t="inlineStr"/>
+      <c r="Q139" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R139" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S139" s="35" t="inlineStr"/>
+      <c r="T139" s="25" t="inlineStr"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="32" t="inlineStr">
+        <is>
+          <t>coffee-table</t>
+        </is>
+      </c>
+      <c r="B140" s="32" t="inlineStr">
+        <is>
+          <t>Coffee table</t>
+        </is>
+      </c>
+      <c r="C140" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D140" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E140" s="32" t="inlineStr">
+        <is>
+          <t>399.99</t>
+        </is>
+      </c>
+      <c r="F140" s="33" t="inlineStr"/>
+      <c r="G140" s="33" t="inlineStr"/>
+      <c r="H140" s="33" t="inlineStr"/>
+      <c r="I140" s="33" t="inlineStr"/>
+      <c r="J140" s="23" t="inlineStr">
+        <is>
+          <t>40 lbs</t>
+        </is>
+      </c>
+      <c r="K140" s="33" t="inlineStr"/>
+      <c r="L140" s="23" t="inlineStr">
+        <is>
+          <t>glass</t>
+        </is>
+      </c>
+      <c r="M140" s="33" t="inlineStr"/>
+      <c r="N140" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEATURES SPECS MG1242S-NB ; Rectangle clear temperd glass table top ; Metal frame in nickel brush </t>
+        </is>
+      </c>
+      <c r="O140" s="33" t="inlineStr"/>
+      <c r="P140" s="33" t="inlineStr"/>
+      <c r="Q140" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R140" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S140" s="35" t="inlineStr"/>
+      <c r="T140" s="25" t="inlineStr"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="27" t="inlineStr">
+        <is>
+          <t>folding-table-30-x-96-1</t>
+        </is>
+      </c>
+      <c r="B141" s="27" t="inlineStr">
+        <is>
+          <t>Folding table — 30" x 96"</t>
+        </is>
+      </c>
+      <c r="C141" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D141" s="27" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E141" s="27" t="inlineStr">
+        <is>
+          <t>195.38</t>
+        </is>
+      </c>
+      <c r="F141" s="33" t="inlineStr"/>
+      <c r="G141" s="23" t="inlineStr">
+        <is>
+          <t>Folding table</t>
+        </is>
+      </c>
+      <c r="H141" s="33" t="inlineStr"/>
+      <c r="I141" s="33" t="inlineStr"/>
+      <c r="J141" s="33" t="inlineStr"/>
+      <c r="K141" s="23" t="inlineStr">
+        <is>
+          <t>300 lbs</t>
+        </is>
+      </c>
+      <c r="L141" s="23" t="inlineStr">
+        <is>
+          <t>wood, powder coat</t>
+        </is>
+      </c>
+      <c r="M141" s="33" t="inlineStr"/>
+      <c r="N141" s="23" t="inlineStr">
+        <is>
+          <t>Category Panels/Partitions Manufacturer Heartwood Manufacturing Ltd Manufacturer ; R45-GN Brand HDL Item Code: HTWTLTR45GN Lightweight durable all weather polyethyl</t>
+        </is>
+      </c>
+      <c r="O141" s="33" t="inlineStr"/>
+      <c r="P141" s="33" t="inlineStr"/>
+      <c r="Q141" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R141" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S141" s="35" t="inlineStr"/>
+      <c r="T141" s="25" t="inlineStr"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="32" t="inlineStr">
+        <is>
+          <t>folding-table-30x-72</t>
+        </is>
+      </c>
+      <c r="B142" s="32" t="inlineStr">
+        <is>
+          <t>Folding table — 30"x 72"</t>
+        </is>
+      </c>
+      <c r="C142" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D142" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E142" s="32" t="inlineStr">
+        <is>
+          <t>164.67</t>
+        </is>
+      </c>
+      <c r="F142" s="33" t="inlineStr"/>
+      <c r="G142" s="23" t="inlineStr">
+        <is>
+          <t>Folding table</t>
+        </is>
+      </c>
+      <c r="H142" s="33" t="inlineStr"/>
+      <c r="I142" s="33" t="inlineStr"/>
+      <c r="J142" s="33" t="inlineStr"/>
+      <c r="K142" s="33" t="inlineStr"/>
+      <c r="L142" s="23" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="M142" s="33" t="inlineStr"/>
+      <c r="N142" s="33" t="inlineStr"/>
+      <c r="O142" s="33" t="inlineStr"/>
+      <c r="P142" s="33" t="inlineStr"/>
+      <c r="Q142" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R142" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S142" s="35" t="inlineStr"/>
+      <c r="T142" s="25" t="inlineStr"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="27" t="inlineStr">
+        <is>
+          <t>height-adjustable-base-pneumatic</t>
+        </is>
+      </c>
+      <c r="B143" s="27" t="inlineStr">
+        <is>
+          <t>Height adjustable base pneumatic (top sold separately)</t>
+        </is>
+      </c>
+      <c r="C143" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D143" s="27" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E143" s="27" t="inlineStr">
+        <is>
+          <t>699.99</t>
+        </is>
+      </c>
+      <c r="F143" s="33" t="inlineStr"/>
+      <c r="G143" s="33" t="inlineStr"/>
+      <c r="H143" s="33" t="inlineStr"/>
+      <c r="I143" s="33" t="inlineStr"/>
+      <c r="J143" s="33" t="inlineStr"/>
+      <c r="K143" s="33" t="inlineStr"/>
+      <c r="L143" s="23" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="M143" s="33" t="inlineStr"/>
+      <c r="N143" s="23" t="inlineStr">
+        <is>
+          <t>The Sudo series has a lightweight pneumatic base - Perfect for the user with mini; The Sudo pneumatic base will easily free float a work surface along with your lap; No power consumption means more savings</t>
+        </is>
+      </c>
+      <c r="O143" s="33" t="inlineStr"/>
+      <c r="P143" s="33" t="inlineStr"/>
+      <c r="Q143" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R143" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S143" s="35" t="inlineStr"/>
+      <c r="T143" s="25" t="inlineStr"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="32" t="inlineStr">
+        <is>
+          <t>management-u-shaped-suite-with-3-stage-height-adjustable-table</t>
+        </is>
+      </c>
+      <c r="B144" s="32" t="inlineStr">
+        <is>
+          <t>Management "u" shaped suite with 3-stage height adjustable table</t>
+        </is>
+      </c>
+      <c r="C144" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D144" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E144" s="32" t="inlineStr">
+        <is>
+          <t>2775.0</t>
+        </is>
+      </c>
+      <c r="F144" s="33" t="inlineStr"/>
+      <c r="G144" s="33" t="inlineStr"/>
+      <c r="H144" s="33" t="inlineStr"/>
+      <c r="I144" s="23" t="inlineStr">
+        <is>
+          <t>72 x 95 x 65.6"</t>
+        </is>
+      </c>
+      <c r="J144" s="33" t="inlineStr"/>
+      <c r="K144" s="33" t="inlineStr"/>
+      <c r="L144" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M144" s="33" t="inlineStr"/>
+      <c r="N144" s="23" t="inlineStr">
+        <is>
+          <t>Management "U" Shaped Suite with 3-Stage Height Adjustable Table Newland - simple</t>
+        </is>
+      </c>
+      <c r="O144" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA; Greenguard; ANSI</t>
+        </is>
+      </c>
+      <c r="P144" s="23" t="inlineStr">
+        <is>
+          <t>Lifetime warranty</t>
+        </is>
+      </c>
+      <c r="Q144" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R144" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S144" s="35" t="inlineStr"/>
+      <c r="T144" s="25" t="inlineStr"/>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="27" t="inlineStr">
+        <is>
+          <t>quick-assembly-electric-height-adjustable-base</t>
+        </is>
+      </c>
+      <c r="B145" s="27" t="inlineStr">
+        <is>
+          <t>Quick assembly electric height adjustable base</t>
+        </is>
+      </c>
+      <c r="C145" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D145" s="27" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E145" s="27" t="inlineStr">
+        <is>
+          <t>999.99</t>
+        </is>
+      </c>
+      <c r="F145" s="33" t="inlineStr"/>
+      <c r="G145" s="33" t="inlineStr"/>
+      <c r="H145" s="33" t="inlineStr"/>
+      <c r="I145" s="33" t="inlineStr"/>
+      <c r="J145" s="33" t="inlineStr"/>
+      <c r="K145" s="33" t="inlineStr"/>
+      <c r="L145" s="33" t="inlineStr"/>
+      <c r="M145" s="33" t="inlineStr"/>
+      <c r="N145" s="23" t="inlineStr">
+        <is>
+          <t>Quick Assembly Electric Height Adjustable Base quick assembly 2-leg, 3-stage elec</t>
+        </is>
+      </c>
+      <c r="O145" s="33" t="inlineStr"/>
+      <c r="P145" s="33" t="inlineStr"/>
+      <c r="Q145" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R145" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S145" s="35" t="inlineStr"/>
+      <c r="T145" s="25" t="inlineStr"/>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="32" t="inlineStr">
+        <is>
+          <t>quick-assembly-height-adjustable-base</t>
+        </is>
+      </c>
+      <c r="B146" s="32" t="inlineStr">
+        <is>
+          <t>Quick assembly height adjustable base</t>
+        </is>
+      </c>
+      <c r="C146" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D146" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E146" s="32" t="inlineStr">
+        <is>
+          <t>944.49</t>
+        </is>
+      </c>
+      <c r="F146" s="33" t="inlineStr"/>
+      <c r="G146" s="33" t="inlineStr"/>
+      <c r="H146" s="33" t="inlineStr"/>
+      <c r="I146" s="33" t="inlineStr"/>
+      <c r="J146" s="33" t="inlineStr"/>
+      <c r="K146" s="33" t="inlineStr"/>
+      <c r="L146" s="23" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="M146" s="33" t="inlineStr"/>
+      <c r="N146" s="23" t="inlineStr">
+        <is>
+          <t>CONSTRUCTION Fold out leg for quick assembly Sturdy, 3-stage, steel frame constru</t>
+        </is>
+      </c>
+      <c r="O146" s="23" t="inlineStr">
+        <is>
+          <t>BIFMA</t>
+        </is>
+      </c>
+      <c r="P146" s="33" t="inlineStr"/>
+      <c r="Q146" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R146" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S146" s="35" t="inlineStr"/>
+      <c r="T146" s="25" t="inlineStr"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="27" t="inlineStr">
+        <is>
+          <t>round-table-glass-top</t>
+        </is>
+      </c>
+      <c r="B147" s="27" t="inlineStr">
+        <is>
+          <t>Round table glass top</t>
+        </is>
+      </c>
+      <c r="C147" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D147" s="27" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E147" s="27" t="inlineStr">
+        <is>
+          <t>420.0</t>
+        </is>
+      </c>
+      <c r="F147" s="33" t="inlineStr"/>
+      <c r="G147" s="33" t="inlineStr"/>
+      <c r="H147" s="33" t="inlineStr"/>
+      <c r="I147" s="33" t="inlineStr"/>
+      <c r="J147" s="23" t="inlineStr">
+        <is>
+          <t>31 lbs</t>
+        </is>
+      </c>
+      <c r="K147" s="33" t="inlineStr"/>
+      <c r="L147" s="23" t="inlineStr">
+        <is>
+          <t>glass</t>
+        </is>
+      </c>
+      <c r="M147" s="33" t="inlineStr"/>
+      <c r="N147" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FEATURES SPECS MG1230R-NB ; Round clear tempered glass table top ; Metal frame in nickel brush </t>
+        </is>
+      </c>
+      <c r="O147" s="33" t="inlineStr"/>
+      <c r="P147" s="33" t="inlineStr"/>
+      <c r="Q147" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R147" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S147" s="35" t="inlineStr"/>
+      <c r="T147" s="25" t="inlineStr"/>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="32" t="inlineStr">
+        <is>
+          <t>table-29-x-28-4</t>
+        </is>
+      </c>
+      <c r="B148" s="32" t="inlineStr">
+        <is>
+          <t>Table — 29" x 28"</t>
+        </is>
+      </c>
+      <c r="C148" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D148" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E148" s="32" t="inlineStr">
+        <is>
+          <t>350.19</t>
+        </is>
+      </c>
+      <c r="F148" s="33" t="inlineStr"/>
+      <c r="G148" s="23" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H148" s="33" t="inlineStr"/>
+      <c r="I148" s="33" t="inlineStr"/>
+      <c r="J148" s="33" t="inlineStr"/>
+      <c r="K148" s="33" t="inlineStr"/>
+      <c r="L148" s="33" t="inlineStr"/>
+      <c r="M148" s="33" t="inlineStr"/>
+      <c r="N148" s="23" t="inlineStr">
+        <is>
+          <t>Category Cafeteria &amp; Breakroom Tables Manufacturer Global Upholstery Co</t>
+        </is>
+      </c>
+      <c r="O148" s="23" t="inlineStr">
+        <is>
+          <t>ansi</t>
+        </is>
+      </c>
+      <c r="P148" s="33" t="inlineStr"/>
+      <c r="Q148" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R148" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S148" s="35" t="inlineStr"/>
+      <c r="T148" s="25" t="inlineStr"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="27" t="inlineStr">
+        <is>
+          <t>table-29-x-28-5</t>
+        </is>
+      </c>
+      <c r="B149" s="27" t="inlineStr">
+        <is>
+          <t>Table — 29" x 28"</t>
+        </is>
+      </c>
+      <c r="C149" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D149" s="27" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E149" s="27" t="inlineStr">
+        <is>
+          <t>350.19</t>
+        </is>
+      </c>
+      <c r="F149" s="33" t="inlineStr"/>
+      <c r="G149" s="23" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="H149" s="33" t="inlineStr"/>
+      <c r="I149" s="33" t="inlineStr"/>
+      <c r="J149" s="33" t="inlineStr"/>
+      <c r="K149" s="33" t="inlineStr"/>
+      <c r="L149" s="23" t="inlineStr">
+        <is>
+          <t>polypropylene</t>
+        </is>
+      </c>
+      <c r="M149" s="33" t="inlineStr"/>
+      <c r="N149" s="23" t="inlineStr">
+        <is>
+          <t>Category Student Desks Manufacturer Global Upholstery Co</t>
+        </is>
+      </c>
+      <c r="O149" s="33" t="inlineStr"/>
+      <c r="P149" s="33" t="inlineStr"/>
+      <c r="Q149" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R149" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S149" s="35" t="inlineStr"/>
+      <c r="T149" s="25" t="inlineStr"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="32" t="inlineStr">
+        <is>
+          <t>tables-dolly-7</t>
+        </is>
+      </c>
+      <c r="B150" s="32" t="inlineStr">
+        <is>
+          <t>Tables dolly</t>
+        </is>
+      </c>
+      <c r="C150" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D150" s="32" t="inlineStr">
+        <is>
+          <t>tables</t>
+        </is>
+      </c>
+      <c r="E150" s="32" t="inlineStr">
+        <is>
+          <t>536.55</t>
+        </is>
+      </c>
+      <c r="F150" s="33" t="inlineStr"/>
+      <c r="G150" s="33" t="inlineStr"/>
+      <c r="H150" s="33" t="inlineStr"/>
+      <c r="I150" s="33" t="inlineStr"/>
+      <c r="J150" s="33" t="inlineStr"/>
+      <c r="K150" s="23" t="inlineStr">
+        <is>
+          <t>300 lbs</t>
+        </is>
+      </c>
+      <c r="L150" s="23" t="inlineStr">
+        <is>
+          <t>steel</t>
+        </is>
+      </c>
+      <c r="M150" s="33" t="inlineStr"/>
+      <c r="N150" s="23" t="inlineStr">
+        <is>
+          <t>Category Utility/Service Carts Manufacturer Global Upholstery Co</t>
+        </is>
+      </c>
+      <c r="O150" s="33" t="inlineStr"/>
+      <c r="P150" s="33" t="inlineStr"/>
+      <c r="Q150" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R150" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S150" s="35" t="inlineStr"/>
+      <c r="T150" s="25" t="inlineStr"/>
+    </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="27" t="inlineStr">
+        <is>
+          <t>carpeted-floor-48-x-36-6</t>
+        </is>
+      </c>
+      <c r="B151" s="27" t="inlineStr">
+        <is>
+          <t>Carpeted floor — 48" x 36"</t>
+        </is>
+      </c>
+      <c r="C151" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D151" s="27" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E151" s="27" t="inlineStr">
+        <is>
+          <t>89.99</t>
+        </is>
+      </c>
+      <c r="F151" s="33" t="inlineStr"/>
+      <c r="G151" s="23" t="inlineStr">
+        <is>
+          <t>Carpeted floor</t>
+        </is>
+      </c>
+      <c r="H151" s="33" t="inlineStr"/>
+      <c r="I151" s="33" t="inlineStr"/>
+      <c r="J151" s="33" t="inlineStr"/>
+      <c r="K151" s="33" t="inlineStr"/>
+      <c r="L151" s="33" t="inlineStr"/>
+      <c r="M151" s="33" t="inlineStr"/>
+      <c r="N151" s="23" t="inlineStr">
+        <is>
+          <t>Category Carpet Chair Mats Manufacturer Deflecto, LLC Manufacturer Ref CM13113 Br</t>
+        </is>
+      </c>
+      <c r="O151" s="33" t="inlineStr"/>
+      <c r="P151" s="33" t="inlineStr"/>
+      <c r="Q151" s="33" t="inlineStr"/>
+      <c r="R151" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S151" s="35" t="inlineStr"/>
+      <c r="T151" s="25" t="inlineStr"/>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="32" t="inlineStr">
+        <is>
+          <t>carpeted-floor-48-x-60</t>
+        </is>
+      </c>
+      <c r="B152" s="32" t="inlineStr">
+        <is>
+          <t>Carpeted floor — 48" x 60"</t>
+        </is>
+      </c>
+      <c r="C152" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D152" s="32" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E152" s="32" t="inlineStr">
+        <is>
+          <t>139.99</t>
+        </is>
+      </c>
+      <c r="F152" s="33" t="inlineStr"/>
+      <c r="G152" s="23" t="inlineStr">
+        <is>
+          <t>Carpeted floor</t>
+        </is>
+      </c>
+      <c r="H152" s="33" t="inlineStr"/>
+      <c r="I152" s="33" t="inlineStr"/>
+      <c r="J152" s="33" t="inlineStr"/>
+      <c r="K152" s="33" t="inlineStr"/>
+      <c r="L152" s="33" t="inlineStr"/>
+      <c r="M152" s="33" t="inlineStr"/>
+      <c r="N152" s="23" t="inlineStr">
+        <is>
+          <t>Category Carpet Chair Mats Manufacturer Deflecto, LLC Manufacturer Ref CM13433F B</t>
+        </is>
+      </c>
+      <c r="O152" s="33" t="inlineStr"/>
+      <c r="P152" s="33" t="inlineStr"/>
+      <c r="Q152" s="33" t="inlineStr"/>
+      <c r="R152" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S152" s="35" t="inlineStr"/>
+      <c r="T152" s="25" t="inlineStr"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="27" t="inlineStr">
+        <is>
+          <t>carpeted-floor-48-x-60-1</t>
+        </is>
+      </c>
+      <c r="B153" s="27" t="inlineStr">
+        <is>
+          <t>Carpeted floor — 48" x 60"</t>
+        </is>
+      </c>
+      <c r="C153" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D153" s="27" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E153" s="27" t="inlineStr">
+        <is>
+          <t>139.99</t>
+        </is>
+      </c>
+      <c r="F153" s="33" t="inlineStr"/>
+      <c r="G153" s="23" t="inlineStr">
+        <is>
+          <t>Carpeted floor</t>
+        </is>
+      </c>
+      <c r="H153" s="33" t="inlineStr"/>
+      <c r="I153" s="33" t="inlineStr"/>
+      <c r="J153" s="33" t="inlineStr"/>
+      <c r="K153" s="33" t="inlineStr"/>
+      <c r="L153" s="33" t="inlineStr"/>
+      <c r="M153" s="33" t="inlineStr"/>
+      <c r="N153" s="23" t="inlineStr">
+        <is>
+          <t>Category Carpet Chair Mats Manufacturer Deflecto, LLC Manufacturer Ref CM13433F B</t>
+        </is>
+      </c>
+      <c r="O153" s="33" t="inlineStr"/>
+      <c r="P153" s="33" t="inlineStr"/>
+      <c r="Q153" s="33" t="inlineStr"/>
+      <c r="R153" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S153" s="35" t="inlineStr"/>
+      <c r="T153" s="25" t="inlineStr"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="32" t="inlineStr">
+        <is>
+          <t>delivery-charge-175-00</t>
+        </is>
+      </c>
+      <c r="B154" s="32" t="inlineStr">
+        <is>
+          <t>Delivery charge 175. — 00</t>
+        </is>
+      </c>
+      <c r="C154" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D154" s="32" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E154" s="32" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
+      <c r="F154" s="33" t="inlineStr"/>
+      <c r="G154" s="23" t="inlineStr">
+        <is>
+          <t>Delivery charge</t>
+        </is>
+      </c>
+      <c r="H154" s="33" t="inlineStr"/>
+      <c r="I154" s="33" t="inlineStr"/>
+      <c r="J154" s="33" t="inlineStr"/>
+      <c r="K154" s="33" t="inlineStr"/>
+      <c r="L154" s="33" t="inlineStr"/>
+      <c r="M154" s="33" t="inlineStr"/>
+      <c r="N154" s="23" t="inlineStr">
+        <is>
+          <t>Due to the location of your delivery address, the charge is $175</t>
+        </is>
+      </c>
+      <c r="O154" s="33" t="inlineStr"/>
+      <c r="P154" s="33" t="inlineStr"/>
+      <c r="Q154" s="33" t="inlineStr"/>
+      <c r="R154" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S154" s="35" t="inlineStr"/>
+      <c r="T154" s="25" t="inlineStr"/>
+    </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="27" t="inlineStr">
+        <is>
+          <t>delivery-charge-85-00</t>
+        </is>
+      </c>
+      <c r="B155" s="27" t="inlineStr">
+        <is>
+          <t>Delivery charge $85. — 00</t>
+        </is>
+      </c>
+      <c r="C155" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D155" s="27" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E155" s="27" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="F155" s="33" t="inlineStr"/>
+      <c r="G155" s="33" t="inlineStr"/>
+      <c r="H155" s="33" t="inlineStr"/>
+      <c r="I155" s="33" t="inlineStr"/>
+      <c r="J155" s="33" t="inlineStr"/>
+      <c r="K155" s="33" t="inlineStr"/>
+      <c r="L155" s="33" t="inlineStr"/>
+      <c r="M155" s="33" t="inlineStr"/>
+      <c r="N155" s="23" t="inlineStr">
+        <is>
+          <t>This price includes delivery only</t>
+        </is>
+      </c>
+      <c r="O155" s="33" t="inlineStr"/>
+      <c r="P155" s="33" t="inlineStr"/>
+      <c r="Q155" s="33" t="inlineStr"/>
+      <c r="R155" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S155" s="35" t="inlineStr"/>
+      <c r="T155" s="25" t="inlineStr"/>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="32" t="inlineStr">
+        <is>
+          <t>newland-16w-box-box-file-mobile-pedestal</t>
+        </is>
+      </c>
+      <c r="B156" s="32" t="inlineStr">
+        <is>
+          <t>Newland | 16"W Box/Box/File Mobile Pedestal</t>
+        </is>
+      </c>
+      <c r="C156" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D156" s="32" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E156" s="32" t="inlineStr">
+        <is>
+          <t>589.99</t>
+        </is>
+      </c>
+      <c r="F156" s="23" t="inlineStr">
+        <is>
+          <t>Global Furniture Group / Teknion</t>
+        </is>
+      </c>
+      <c r="G156" s="23" t="inlineStr">
+        <is>
+          <t>Newland</t>
+        </is>
+      </c>
+      <c r="H156" s="33" t="inlineStr"/>
+      <c r="I156" s="23" t="inlineStr">
+        <is>
+          <t>16 x 22.7 x 28"</t>
+        </is>
+      </c>
+      <c r="J156" s="23" t="inlineStr">
+        <is>
+          <t>93 lbs</t>
+        </is>
+      </c>
+      <c r="K156" s="33" t="inlineStr"/>
+      <c r="L156" s="23" t="inlineStr">
+        <is>
+          <t>laminate</t>
+        </is>
+      </c>
+      <c r="M156" s="33" t="inlineStr"/>
+      <c r="N156" s="23" t="inlineStr">
+        <is>
+          <t>Mobile Pedestal Thermally fused laminate Pedestal top features 1" overhang with b</t>
+        </is>
+      </c>
+      <c r="O156" s="33" t="inlineStr"/>
+      <c r="P156" s="33" t="inlineStr"/>
+      <c r="Q156" s="23" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="R156" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S156" s="35" t="inlineStr"/>
+      <c r="T156" s="25" t="inlineStr"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="27" t="inlineStr">
+        <is>
+          <t>shoptech-081</t>
+        </is>
+      </c>
+      <c r="B157" s="27" t="inlineStr">
+        <is>
+          <t>Shoptech — 081</t>
+        </is>
+      </c>
+      <c r="C157" s="27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D157" s="27" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E157" s="27" t="inlineStr">
+        <is>
+          <t>335.0</t>
+        </is>
+      </c>
+      <c r="F157" s="33" t="inlineStr"/>
+      <c r="G157" s="23" t="inlineStr">
+        <is>
+          <t>Shoptech</t>
+        </is>
+      </c>
+      <c r="H157" s="33" t="inlineStr"/>
+      <c r="I157" s="33" t="inlineStr"/>
+      <c r="J157" s="33" t="inlineStr"/>
+      <c r="K157" s="33" t="inlineStr"/>
+      <c r="L157" s="23" t="inlineStr">
+        <is>
+          <t>polyurethane, steel</t>
+        </is>
+      </c>
+      <c r="M157" s="33" t="inlineStr"/>
+      <c r="N157" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Features Injection molded polyurethane seat cushion Black steel heavy duty frame </t>
+        </is>
+      </c>
+      <c r="O157" s="33" t="inlineStr"/>
+      <c r="P157" s="33" t="inlineStr"/>
+      <c r="Q157" s="33" t="inlineStr"/>
+      <c r="R157" s="36" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="S157" s="35" t="inlineStr"/>
+      <c r="T157" s="25" t="inlineStr"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="32" t="inlineStr">
+        <is>
+          <t>shoptech-2300-pc775</t>
+        </is>
+      </c>
+      <c r="B158" s="32" t="inlineStr">
+        <is>
+          <t>Shoptech 2300– — PC775</t>
+        </is>
+      </c>
+      <c r="C158" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D158" s="32" t="inlineStr">
+        <is>
+          <t>uncategorized</t>
+        </is>
+      </c>
+      <c r="E158" s="32" t="inlineStr">
+        <is>
+          <t>369.0</t>
+        </is>
+      </c>
+      <c r="F158" s="33" t="inlineStr"/>
+      <c r="G158" s="23" t="inlineStr">
+        <is>
+          <t>Shoptech</t>
+        </is>
+      </c>
+      <c r="H158" s="23" t="inlineStr">
+        <is>
+          <t>PC775</t>
+        </is>
+      </c>
+      <c r="I158" s="33" t="inlineStr"/>
+      <c r="J158" s="33" t="inlineStr"/>
+      <c r="K158" s="33" t="inlineStr"/>
+      <c r="L158" s="23" t="inlineStr">
+        <is>
+          <t>polyurethane</t>
+        </is>
+      </c>
+      <c r="M158" s="33" t="inlineStr"/>
+      <c r="N158" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Features Sit to stand application Height adjustable gas lift action Seat covered </t>
+        </is>
+      </c>
+      <c r="O158" s="33" t="inlineStr"/>
+      <c r="P158" s="33" t="inlineStr"/>
+      <c r="Q158" s="33" t="inlineStr"/>
+      <c r="R158" s="34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="S158" s="35" t="inlineStr"/>
+      <c r="T158" s="25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:T1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>